--- a/routes/route_b_cvf_ae/results/cvf_ae_paper_results_package_20260624_from_formal_results/CVF_AE_PAPER_RESULTS_PACKAGE.xlsx
+++ b/routes/route_b_cvf_ae/results/cvf_ae_paper_results_package_20260624_from_formal_results/CVF_AE_PAPER_RESULTS_PACKAGE.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R843041b4d6054889"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main Compact" sheetId="2" r:id="Rfb000aa5f6684795"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main Long" sheetId="3" r:id="R4f889e31893c4084"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Significance" sheetId="4" r:id="R184ebe5c19d844e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ablation" sheetId="5" r:id="R547da5a2a55e4afa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ablation Sig" sheetId="6" r:id="R0990901f86aa4394"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="7" r:id="R90e115a5db75403a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overhead" sheetId="8" r:id="R5fa7fd9df60e4acd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trajectory" sheetId="9" r:id="R44bc94e349a54c9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure Index" sheetId="10" r:id="R3be0988dda0c40e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R4881aa6a29dc4afb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main Compact" sheetId="2" r:id="R85d6548b381049f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main Long" sheetId="3" r:id="R2927547773f6492a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Significance" sheetId="4" r:id="R7c51ae55261c4639"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ablation" sheetId="5" r:id="Ra96db164ebe94785"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ablation Sig" sheetId="6" r:id="R63f3d778d839466d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="7" r:id="R310f592c1ee04274"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overhead" sheetId="8" r:id="R0eb31390b12549bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trajectory" sheetId="9" r:id="R3db9fdf456e44068"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure Index" sheetId="10" r:id="R5df5d6ac55f44b49"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -65,7 +65,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="8">
+  <x:fills count="14">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -100,6 +100,36 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF3F6F9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -174,7 +204,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="99">
+  <x:cellXfs count="121">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -428,6 +458,72 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="11" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -603,14 +699,14 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="FigureIndexTable" displayName="FigureIndexTable" ref="A1:I22" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="FigureIndexTable" displayName="FigureIndexTable" ref="A1:I26" headerRowCount="1">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="FigureId"/>
     <x:tableColumn id="2" name="Group"/>
     <x:tableColumn id="3" name="Scene"/>
     <x:tableColumn id="4" name="View"/>
     <x:tableColumn id="5" name="FileName"/>
-    <x:tableColumn id="6" name="Placement"/>
+    <x:tableColumn id="6" name="SuggestedPlacement"/>
     <x:tableColumn id="7" name="Purpose"/>
     <x:tableColumn id="8" name="Status"/>
     <x:tableColumn id="9" name="RelativePath"/>
@@ -1023,78 +1119,78 @@
     <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="11" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="36" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="11" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="42" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="45" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="13" t="str">
+    <x:row r="1" ht="30" hidden="0" customHeight="1">
+      <x:c r="A1" s="114" t="str">
         <x:v>FigureId</x:v>
       </x:c>
-      <x:c r="B1" s="13" t="str">
+      <x:c r="B1" s="114" t="str">
         <x:v>Group</x:v>
       </x:c>
-      <x:c r="C1" s="13" t="str">
+      <x:c r="C1" s="114" t="str">
         <x:v>Scene</x:v>
       </x:c>
-      <x:c r="D1" s="13" t="str">
+      <x:c r="D1" s="114" t="str">
         <x:v>View</x:v>
       </x:c>
-      <x:c r="E1" s="13" t="str">
+      <x:c r="E1" s="114" t="str">
         <x:v>FileName</x:v>
       </x:c>
-      <x:c r="F1" s="13" t="str">
-        <x:v>Placement</x:v>
-      </x:c>
-      <x:c r="G1" s="13" t="str">
+      <x:c r="F1" s="114" t="str">
+        <x:v>SuggestedPlacement</x:v>
+      </x:c>
+      <x:c r="G1" s="114" t="str">
         <x:v>Purpose</x:v>
       </x:c>
-      <x:c r="H1" s="13" t="str">
+      <x:c r="H1" s="114" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="I1" s="13" t="str">
+      <x:c r="I1" s="114" t="str">
         <x:v>RelativePath</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="42" hidden="0" customHeight="1">
-      <x:c r="A2" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="8" t="str">
+      <x:c r="A2" s="115" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="115" t="str">
         <x:v>ablation-path</x:v>
       </x:c>
-      <x:c r="C2" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="8" t="str">
+      <x:c r="C2" s="115" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D2" s="115" t="str">
         <x:v>3d</x:v>
       </x:c>
-      <x:c r="E2" s="14" t="str">
+      <x:c r="E2" s="116" t="str">
         <x:v>ablation_scene1_representative_3d.png</x:v>
       </x:c>
-      <x:c r="F2" s="8" t="str">
+      <x:c r="F2" s="116" t="str">
         <x:v>supplement</x:v>
       </x:c>
-      <x:c r="G2" s="14" t="str">
+      <x:c r="G2" s="116" t="str">
         <x:v>Visualize module contribution and failure cases</x:v>
       </x:c>
-      <x:c r="H2" s="8" t="str">
+      <x:c r="H2" s="116" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I2" s="14" t="str">
+      <x:c r="I2" s="116" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\ablation\ablation_scene1_representative_3d.png</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="42" hidden="0" customHeight="1">
-      <x:c r="A3" s="17" t="n">
+      <x:c r="A3" s="8" t="str">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="8" t="str">
         <x:v>ablation-path</x:v>
       </x:c>
-      <x:c r="C3" s="17" t="n">
+      <x:c r="C3" s="8" t="str">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D3" s="8" t="str">
@@ -1103,13 +1199,13 @@
       <x:c r="E3" s="14" t="str">
         <x:v>ablation_scene1_representative_top.png</x:v>
       </x:c>
-      <x:c r="F3" s="8" t="str">
+      <x:c r="F3" s="14" t="str">
         <x:v>supplement</x:v>
       </x:c>
       <x:c r="G3" s="14" t="str">
         <x:v>Visualize module contribution and failure cases</x:v>
       </x:c>
-      <x:c r="H3" s="8" t="str">
+      <x:c r="H3" s="14" t="str">
         <x:v>ready</x:v>
       </x:c>
       <x:c r="I3" s="14" t="str">
@@ -1117,560 +1213,668 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="42" hidden="0" customHeight="1">
-      <x:c r="A4" s="17" t="n">
+      <x:c r="A4" s="115" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B4" s="8" t="str">
+      <x:c r="B4" s="115" t="str">
         <x:v>ablation-path</x:v>
       </x:c>
-      <x:c r="C4" s="17" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="8" t="str">
+      <x:c r="C4" s="115" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D4" s="115" t="str">
         <x:v>3d</x:v>
       </x:c>
-      <x:c r="E4" s="14" t="str">
+      <x:c r="E4" s="116" t="str">
         <x:v>ablation_scene2_representative_3d.png</x:v>
       </x:c>
-      <x:c r="F4" s="8" t="str">
+      <x:c r="F4" s="116" t="str">
         <x:v>supplement</x:v>
       </x:c>
-      <x:c r="G4" s="14" t="str">
+      <x:c r="G4" s="116" t="str">
         <x:v>Visualize module contribution and failure cases</x:v>
       </x:c>
-      <x:c r="H4" s="8" t="str">
+      <x:c r="H4" s="116" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I4" s="14" t="str">
+      <x:c r="I4" s="116" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\ablation\ablation_scene2_representative_3d.png</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="42" hidden="0" customHeight="1">
-      <x:c r="A5" s="63" t="n">
+      <x:c r="A5" s="119" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B5" s="55" t="str">
+      <x:c r="B5" s="119" t="str">
         <x:v>ablation-path</x:v>
       </x:c>
-      <x:c r="C5" s="63" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="55" t="str">
+      <x:c r="C5" s="119" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D5" s="119" t="str">
         <x:v>top</x:v>
       </x:c>
-      <x:c r="E5" s="64" t="str">
+      <x:c r="E5" s="120" t="str">
         <x:v>ablation_scene2_representative_top.png</x:v>
       </x:c>
-      <x:c r="F5" s="55" t="str">
+      <x:c r="F5" s="120" t="str">
         <x:v>main-text</x:v>
       </x:c>
-      <x:c r="G5" s="64" t="str">
+      <x:c r="G5" s="120" t="str">
         <x:v>Visualize module contribution and failure cases</x:v>
       </x:c>
-      <x:c r="H5" s="55" t="str">
+      <x:c r="H5" s="120" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I5" s="64" t="str">
+      <x:c r="I5" s="120" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\ablation\ablation_scene2_representative_top.png</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="42" hidden="0" customHeight="1">
-      <x:c r="A6" s="17" t="n">
+      <x:c r="A6" s="115" t="str">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B6" s="8" t="str">
+      <x:c r="B6" s="115" t="str">
         <x:v>ablation-path</x:v>
       </x:c>
-      <x:c r="C6" s="17" t="n">
+      <x:c r="C6" s="115" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D6" s="8" t="str">
+      <x:c r="D6" s="115" t="str">
         <x:v>3d</x:v>
       </x:c>
-      <x:c r="E6" s="14" t="str">
+      <x:c r="E6" s="116" t="str">
         <x:v>ablation_scene4_representative_3d.png</x:v>
       </x:c>
-      <x:c r="F6" s="8" t="str">
+      <x:c r="F6" s="116" t="str">
         <x:v>supplement</x:v>
       </x:c>
-      <x:c r="G6" s="14" t="str">
+      <x:c r="G6" s="116" t="str">
         <x:v>Visualize module contribution and failure cases</x:v>
       </x:c>
-      <x:c r="H6" s="8" t="str">
+      <x:c r="H6" s="116" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I6" s="14" t="str">
+      <x:c r="I6" s="116" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\ablation\ablation_scene4_representative_3d.png</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="42" hidden="0" customHeight="1">
-      <x:c r="A7" s="63" t="n">
+      <x:c r="A7" s="119" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B7" s="55" t="str">
+      <x:c r="B7" s="119" t="str">
         <x:v>ablation-path</x:v>
       </x:c>
-      <x:c r="C7" s="63" t="n">
+      <x:c r="C7" s="119" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D7" s="55" t="str">
+      <x:c r="D7" s="119" t="str">
         <x:v>top</x:v>
       </x:c>
-      <x:c r="E7" s="64" t="str">
+      <x:c r="E7" s="120" t="str">
         <x:v>ablation_scene4_representative_top.png</x:v>
       </x:c>
-      <x:c r="F7" s="55" t="str">
+      <x:c r="F7" s="120" t="str">
         <x:v>main-text</x:v>
       </x:c>
-      <x:c r="G7" s="64" t="str">
+      <x:c r="G7" s="120" t="str">
         <x:v>Visualize module contribution and failure cases</x:v>
       </x:c>
-      <x:c r="H7" s="55" t="str">
+      <x:c r="H7" s="120" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I7" s="64" t="str">
+      <x:c r="I7" s="120" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\ablation\ablation_scene4_representative_top.png</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="42" hidden="0" customHeight="1">
-      <x:c r="A8" s="63" t="n">
+      <x:c r="A8" s="115" t="str">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="B8" s="55" t="str">
+      <x:c r="B8" s="115" t="str">
+        <x:v>boxplot</x:v>
+      </x:c>
+      <x:c r="C8" s="115" t="str"/>
+      <x:c r="D8" s="115" t="str">
+        <x:v>all-log</x:v>
+      </x:c>
+      <x:c r="E8" s="116" t="str">
+        <x:v>cvf_ae_boxplots_all_algorithms_log.png</x:v>
+      </x:c>
+      <x:c r="F8" s="116" t="str">
+        <x:v>supplement</x:v>
+      </x:c>
+      <x:c r="G8" s="116" t="str">
+        <x:v>Compare run distributions of all eleven algorithms</x:v>
+      </x:c>
+      <x:c r="H8" s="116" t="str">
+        <x:v>ready</x:v>
+      </x:c>
+      <x:c r="I8" s="116" t="str">
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_paper_completion_figures_20260624_from_formal_results\cvf_ae_boxplots_all_algorithms_log.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="42" hidden="0" customHeight="1">
+      <x:c r="A9" s="119" t="str">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="119" t="str">
+        <x:v>boxplot</x:v>
+      </x:c>
+      <x:c r="C9" s="119" t="str"/>
+      <x:c r="D9" s="119" t="str">
+        <x:v>strong-linear</x:v>
+      </x:c>
+      <x:c r="E9" s="120" t="str">
+        <x:v>cvf_ae_boxplots_strong_algorithms.png</x:v>
+      </x:c>
+      <x:c r="F9" s="120" t="str">
+        <x:v>main-text</x:v>
+      </x:c>
+      <x:c r="G9" s="120" t="str">
+        <x:v>Compare run distributions of six strong algorithms</x:v>
+      </x:c>
+      <x:c r="H9" s="120" t="str">
+        <x:v>ready</x:v>
+      </x:c>
+      <x:c r="I9" s="120" t="str">
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_paper_completion_figures_20260624_from_formal_results\cvf_ae_boxplots_strong_algorithms.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="42" hidden="0" customHeight="1">
+      <x:c r="A10" s="119" t="str">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B10" s="119" t="str">
         <x:v>convergence</x:v>
       </x:c>
-      <x:c r="C8" s="63" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="55" t="str">
+      <x:c r="C10" s="119" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D10" s="119" t="str">
         <x:v>mean-std</x:v>
       </x:c>
-      <x:c r="E8" s="64" t="str">
+      <x:c r="E10" s="120" t="str">
         <x:v>scene1_convergence_mean_std.png</x:v>
       </x:c>
-      <x:c r="F8" s="55" t="str">
+      <x:c r="F10" s="120" t="str">
         <x:v>main-text</x:v>
       </x:c>
-      <x:c r="G8" s="64" t="str">
+      <x:c r="G10" s="120" t="str">
         <x:v>Compare feasible-aware convergence behavior</x:v>
       </x:c>
-      <x:c r="H8" s="55" t="str">
+      <x:c r="H10" s="120" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I8" s="64" t="str">
+      <x:c r="I10" s="120" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_convergence_curves_20260623_from_main_comparison\scene1_convergence_mean_std.png</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="42" hidden="0" customHeight="1">
-      <x:c r="A9" s="63" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B9" s="55" t="str">
+    <x:row r="11" ht="42" hidden="0" customHeight="1">
+      <x:c r="A11" s="119" t="str">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B11" s="119" t="str">
         <x:v>convergence</x:v>
       </x:c>
-      <x:c r="C9" s="63" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="55" t="str">
+      <x:c r="C11" s="119" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D11" s="119" t="str">
         <x:v>mean-std</x:v>
       </x:c>
-      <x:c r="E9" s="64" t="str">
+      <x:c r="E11" s="120" t="str">
         <x:v>scene2_convergence_mean_std.png</x:v>
       </x:c>
-      <x:c r="F9" s="55" t="str">
+      <x:c r="F11" s="120" t="str">
         <x:v>main-text</x:v>
       </x:c>
-      <x:c r="G9" s="64" t="str">
+      <x:c r="G11" s="120" t="str">
         <x:v>Compare feasible-aware convergence behavior</x:v>
       </x:c>
-      <x:c r="H9" s="55" t="str">
+      <x:c r="H11" s="120" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I9" s="64" t="str">
+      <x:c r="I11" s="120" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_convergence_curves_20260623_from_main_comparison\scene2_convergence_mean_std.png</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="42" hidden="0" customHeight="1">
-      <x:c r="A10" s="63" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B10" s="55" t="str">
+    <x:row r="12" ht="42" hidden="0" customHeight="1">
+      <x:c r="A12" s="119" t="str">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B12" s="119" t="str">
         <x:v>convergence</x:v>
       </x:c>
-      <x:c r="C10" s="63" t="n">
+      <x:c r="C12" s="119" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D10" s="55" t="str">
+      <x:c r="D12" s="119" t="str">
         <x:v>mean-std</x:v>
       </x:c>
-      <x:c r="E10" s="64" t="str">
+      <x:c r="E12" s="120" t="str">
         <x:v>scene4_convergence_mean_std.png</x:v>
       </x:c>
-      <x:c r="F10" s="55" t="str">
+      <x:c r="F12" s="120" t="str">
         <x:v>main-text</x:v>
       </x:c>
-      <x:c r="G10" s="64" t="str">
+      <x:c r="G12" s="120" t="str">
         <x:v>Compare feasible-aware convergence behavior</x:v>
       </x:c>
-      <x:c r="H10" s="55" t="str">
+      <x:c r="H12" s="120" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I10" s="64" t="str">
+      <x:c r="I12" s="120" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_convergence_curves_20260623_from_main_comparison\scene4_convergence_mean_std.png</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="42" hidden="0" customHeight="1">
-      <x:c r="A11" s="17" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B11" s="8" t="str">
-        <x:v>extended-path</x:v>
-      </x:c>
-      <x:c r="C11" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D11" s="8" t="str">
-        <x:v>3d</x:v>
-      </x:c>
-      <x:c r="E11" s="14" t="str">
-        <x:v>extended_scene1_representative_3d.png</x:v>
-      </x:c>
-      <x:c r="F11" s="8" t="str">
-        <x:v>supplement</x:v>
-      </x:c>
-      <x:c r="G11" s="14" t="str">
-        <x:v>Compare CVF-AE with strong and recent improved methods</x:v>
-      </x:c>
-      <x:c r="H11" s="8" t="str">
-        <x:v>ready</x:v>
-      </x:c>
-      <x:c r="I11" s="14" t="str">
-        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\extended\extended_scene1_representative_3d.png</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="42" hidden="0" customHeight="1">
-      <x:c r="A12" s="63" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B12" s="55" t="str">
-        <x:v>extended-path</x:v>
-      </x:c>
-      <x:c r="C12" s="63" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D12" s="55" t="str">
-        <x:v>top</x:v>
-      </x:c>
-      <x:c r="E12" s="64" t="str">
-        <x:v>extended_scene1_representative_top.png</x:v>
-      </x:c>
-      <x:c r="F12" s="55" t="str">
-        <x:v>main-text</x:v>
-      </x:c>
-      <x:c r="G12" s="64" t="str">
-        <x:v>Compare CVF-AE with strong and recent improved methods</x:v>
-      </x:c>
-      <x:c r="H12" s="55" t="str">
-        <x:v>ready</x:v>
-      </x:c>
-      <x:c r="I12" s="64" t="str">
-        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\extended\extended_scene1_representative_top.png</x:v>
-      </x:c>
-    </x:row>
     <x:row r="13" ht="42" hidden="0" customHeight="1">
-      <x:c r="A13" s="17" t="n">
+      <x:c r="A13" s="8" t="str">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="8" t="str">
         <x:v>extended-path</x:v>
       </x:c>
-      <x:c r="C13" s="17" t="n">
-        <x:v>2</x:v>
+      <x:c r="C13" s="8" t="str">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D13" s="8" t="str">
         <x:v>3d</x:v>
       </x:c>
       <x:c r="E13" s="14" t="str">
-        <x:v>extended_scene2_representative_3d.png</x:v>
-      </x:c>
-      <x:c r="F13" s="8" t="str">
+        <x:v>extended_scene1_representative_3d.png</x:v>
+      </x:c>
+      <x:c r="F13" s="14" t="str">
         <x:v>supplement</x:v>
       </x:c>
       <x:c r="G13" s="14" t="str">
         <x:v>Compare CVF-AE with strong and recent improved methods</x:v>
       </x:c>
-      <x:c r="H13" s="8" t="str">
+      <x:c r="H13" s="14" t="str">
         <x:v>ready</x:v>
       </x:c>
       <x:c r="I13" s="14" t="str">
-        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\extended\extended_scene2_representative_3d.png</x:v>
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\extended\extended_scene1_representative_3d.png</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="42" hidden="0" customHeight="1">
-      <x:c r="A14" s="63" t="n">
+      <x:c r="A14" s="119" t="str">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B14" s="55" t="str">
+      <x:c r="B14" s="119" t="str">
         <x:v>extended-path</x:v>
       </x:c>
-      <x:c r="C14" s="63" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D14" s="55" t="str">
+      <x:c r="C14" s="119" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D14" s="119" t="str">
         <x:v>top</x:v>
       </x:c>
-      <x:c r="E14" s="64" t="str">
-        <x:v>extended_scene2_representative_top.png</x:v>
-      </x:c>
-      <x:c r="F14" s="55" t="str">
+      <x:c r="E14" s="120" t="str">
+        <x:v>extended_scene1_representative_top.png</x:v>
+      </x:c>
+      <x:c r="F14" s="120" t="str">
         <x:v>main-text</x:v>
       </x:c>
-      <x:c r="G14" s="64" t="str">
+      <x:c r="G14" s="120" t="str">
         <x:v>Compare CVF-AE with strong and recent improved methods</x:v>
       </x:c>
-      <x:c r="H14" s="55" t="str">
+      <x:c r="H14" s="120" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I14" s="64" t="str">
-        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\extended\extended_scene2_representative_top.png</x:v>
+      <x:c r="I14" s="120" t="str">
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\extended\extended_scene1_representative_top.png</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="42" hidden="0" customHeight="1">
-      <x:c r="A15" s="17" t="n">
+      <x:c r="A15" s="8" t="str">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="8" t="str">
         <x:v>extended-path</x:v>
       </x:c>
-      <x:c r="C15" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="C15" s="8" t="str">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D15" s="8" t="str">
         <x:v>3d</x:v>
       </x:c>
       <x:c r="E15" s="14" t="str">
-        <x:v>extended_scene4_representative_3d.png</x:v>
-      </x:c>
-      <x:c r="F15" s="8" t="str">
+        <x:v>extended_scene2_representative_3d.png</x:v>
+      </x:c>
+      <x:c r="F15" s="14" t="str">
         <x:v>supplement</x:v>
       </x:c>
       <x:c r="G15" s="14" t="str">
         <x:v>Compare CVF-AE with strong and recent improved methods</x:v>
       </x:c>
-      <x:c r="H15" s="8" t="str">
+      <x:c r="H15" s="14" t="str">
         <x:v>ready</x:v>
       </x:c>
       <x:c r="I15" s="14" t="str">
-        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\extended\extended_scene4_representative_3d.png</x:v>
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\extended\extended_scene2_representative_3d.png</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="42" hidden="0" customHeight="1">
-      <x:c r="A16" s="63" t="n">
+      <x:c r="A16" s="119" t="str">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B16" s="55" t="str">
+      <x:c r="B16" s="119" t="str">
         <x:v>extended-path</x:v>
       </x:c>
-      <x:c r="C16" s="63" t="n">
+      <x:c r="C16" s="119" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D16" s="119" t="str">
+        <x:v>top</x:v>
+      </x:c>
+      <x:c r="E16" s="120" t="str">
+        <x:v>extended_scene2_representative_top.png</x:v>
+      </x:c>
+      <x:c r="F16" s="120" t="str">
+        <x:v>main-text</x:v>
+      </x:c>
+      <x:c r="G16" s="120" t="str">
+        <x:v>Compare CVF-AE with strong and recent improved methods</x:v>
+      </x:c>
+      <x:c r="H16" s="120" t="str">
+        <x:v>ready</x:v>
+      </x:c>
+      <x:c r="I16" s="120" t="str">
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\extended\extended_scene2_representative_top.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="42" hidden="0" customHeight="1">
+      <x:c r="A17" s="8" t="str">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B17" s="8" t="str">
+        <x:v>extended-path</x:v>
+      </x:c>
+      <x:c r="C17" s="8" t="str">
         <x:v>4</x:v>
-      </x:c>
-      <x:c r="D16" s="55" t="str">
-        <x:v>top</x:v>
-      </x:c>
-      <x:c r="E16" s="64" t="str">
-        <x:v>extended_scene4_representative_top.png</x:v>
-      </x:c>
-      <x:c r="F16" s="55" t="str">
-        <x:v>main-text</x:v>
-      </x:c>
-      <x:c r="G16" s="64" t="str">
-        <x:v>Compare CVF-AE with strong and recent improved methods</x:v>
-      </x:c>
-      <x:c r="H16" s="55" t="str">
-        <x:v>ready</x:v>
-      </x:c>
-      <x:c r="I16" s="64" t="str">
-        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\extended\extended_scene4_representative_top.png</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="42" hidden="0" customHeight="1">
-      <x:c r="A17" s="17" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B17" s="8" t="str">
-        <x:v>main-path</x:v>
-      </x:c>
-      <x:c r="C17" s="17" t="n">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="8" t="str">
         <x:v>3d</x:v>
       </x:c>
       <x:c r="E17" s="14" t="str">
-        <x:v>main_scene1_representative_3d.png</x:v>
-      </x:c>
-      <x:c r="F17" s="8" t="str">
+        <x:v>extended_scene4_representative_3d.png</x:v>
+      </x:c>
+      <x:c r="F17" s="14" t="str">
         <x:v>supplement</x:v>
       </x:c>
       <x:c r="G17" s="14" t="str">
-        <x:v>Classic-baseline representative path comparison</x:v>
-      </x:c>
-      <x:c r="H17" s="8" t="str">
+        <x:v>Compare CVF-AE with strong and recent improved methods</x:v>
+      </x:c>
+      <x:c r="H17" s="14" t="str">
         <x:v>ready</x:v>
       </x:c>
       <x:c r="I17" s="14" t="str">
-        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\main\main_scene1_representative_3d.png</x:v>
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\extended\extended_scene4_representative_3d.png</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="42" hidden="0" customHeight="1">
-      <x:c r="A18" s="17" t="n">
+      <x:c r="A18" s="119" t="str">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B18" s="8" t="str">
-        <x:v>main-path</x:v>
-      </x:c>
-      <x:c r="C18" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D18" s="8" t="str">
+      <x:c r="B18" s="119" t="str">
+        <x:v>extended-path</x:v>
+      </x:c>
+      <x:c r="C18" s="119" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D18" s="119" t="str">
         <x:v>top</x:v>
       </x:c>
-      <x:c r="E18" s="14" t="str">
-        <x:v>main_scene1_representative_top.png</x:v>
-      </x:c>
-      <x:c r="F18" s="8" t="str">
-        <x:v>supplement</x:v>
-      </x:c>
-      <x:c r="G18" s="14" t="str">
-        <x:v>Classic-baseline representative path comparison</x:v>
-      </x:c>
-      <x:c r="H18" s="8" t="str">
+      <x:c r="E18" s="120" t="str">
+        <x:v>extended_scene4_representative_top.png</x:v>
+      </x:c>
+      <x:c r="F18" s="120" t="str">
+        <x:v>main-text</x:v>
+      </x:c>
+      <x:c r="G18" s="120" t="str">
+        <x:v>Compare CVF-AE with strong and recent improved methods</x:v>
+      </x:c>
+      <x:c r="H18" s="120" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I18" s="14" t="str">
-        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\main\main_scene1_representative_top.png</x:v>
+      <x:c r="I18" s="120" t="str">
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\extended\extended_scene4_representative_top.png</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="42" hidden="0" customHeight="1">
-      <x:c r="A19" s="17" t="n">
+      <x:c r="A19" s="8" t="str">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="8" t="str">
         <x:v>main-path</x:v>
       </x:c>
-      <x:c r="C19" s="17" t="n">
-        <x:v>2</x:v>
+      <x:c r="C19" s="8" t="str">
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D19" s="8" t="str">
         <x:v>3d</x:v>
       </x:c>
       <x:c r="E19" s="14" t="str">
-        <x:v>main_scene2_representative_3d.png</x:v>
-      </x:c>
-      <x:c r="F19" s="8" t="str">
+        <x:v>main_scene1_representative_3d.png</x:v>
+      </x:c>
+      <x:c r="F19" s="14" t="str">
         <x:v>supplement</x:v>
       </x:c>
       <x:c r="G19" s="14" t="str">
         <x:v>Classic-baseline representative path comparison</x:v>
       </x:c>
-      <x:c r="H19" s="8" t="str">
+      <x:c r="H19" s="14" t="str">
         <x:v>ready</x:v>
       </x:c>
       <x:c r="I19" s="14" t="str">
-        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\main\main_scene2_representative_3d.png</x:v>
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\main\main_scene1_representative_3d.png</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="42" hidden="0" customHeight="1">
-      <x:c r="A20" s="17" t="n">
+      <x:c r="A20" s="115" t="str">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B20" s="8" t="str">
+      <x:c r="B20" s="115" t="str">
         <x:v>main-path</x:v>
       </x:c>
-      <x:c r="C20" s="17" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D20" s="8" t="str">
+      <x:c r="C20" s="115" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D20" s="115" t="str">
         <x:v>top</x:v>
       </x:c>
-      <x:c r="E20" s="14" t="str">
-        <x:v>main_scene2_representative_top.png</x:v>
-      </x:c>
-      <x:c r="F20" s="8" t="str">
+      <x:c r="E20" s="116" t="str">
+        <x:v>main_scene1_representative_top.png</x:v>
+      </x:c>
+      <x:c r="F20" s="116" t="str">
         <x:v>supplement</x:v>
       </x:c>
-      <x:c r="G20" s="14" t="str">
+      <x:c r="G20" s="116" t="str">
         <x:v>Classic-baseline representative path comparison</x:v>
       </x:c>
-      <x:c r="H20" s="8" t="str">
+      <x:c r="H20" s="116" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I20" s="14" t="str">
-        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\main\main_scene2_representative_top.png</x:v>
+      <x:c r="I20" s="116" t="str">
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\main\main_scene1_representative_top.png</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="42" hidden="0" customHeight="1">
-      <x:c r="A21" s="17" t="n">
+      <x:c r="A21" s="8" t="str">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="8" t="str">
         <x:v>main-path</x:v>
       </x:c>
-      <x:c r="C21" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="C21" s="8" t="str">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D21" s="8" t="str">
         <x:v>3d</x:v>
       </x:c>
       <x:c r="E21" s="14" t="str">
-        <x:v>main_scene4_representative_3d.png</x:v>
-      </x:c>
-      <x:c r="F21" s="8" t="str">
+        <x:v>main_scene2_representative_3d.png</x:v>
+      </x:c>
+      <x:c r="F21" s="14" t="str">
         <x:v>supplement</x:v>
       </x:c>
       <x:c r="G21" s="14" t="str">
         <x:v>Classic-baseline representative path comparison</x:v>
       </x:c>
-      <x:c r="H21" s="8" t="str">
+      <x:c r="H21" s="14" t="str">
         <x:v>ready</x:v>
       </x:c>
       <x:c r="I21" s="14" t="str">
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\main\main_scene2_representative_3d.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="42" hidden="0" customHeight="1">
+      <x:c r="A22" s="115" t="str">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B22" s="115" t="str">
+        <x:v>main-path</x:v>
+      </x:c>
+      <x:c r="C22" s="115" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D22" s="115" t="str">
+        <x:v>top</x:v>
+      </x:c>
+      <x:c r="E22" s="116" t="str">
+        <x:v>main_scene2_representative_top.png</x:v>
+      </x:c>
+      <x:c r="F22" s="116" t="str">
+        <x:v>supplement</x:v>
+      </x:c>
+      <x:c r="G22" s="116" t="str">
+        <x:v>Classic-baseline representative path comparison</x:v>
+      </x:c>
+      <x:c r="H22" s="116" t="str">
+        <x:v>ready</x:v>
+      </x:c>
+      <x:c r="I22" s="116" t="str">
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\main\main_scene2_representative_top.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="42" customHeight="1">
+      <x:c r="A23" s="8" t="str">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B23" s="8" t="str">
+        <x:v>main-path</x:v>
+      </x:c>
+      <x:c r="C23" s="8" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D23" s="8" t="str">
+        <x:v>3d</x:v>
+      </x:c>
+      <x:c r="E23" s="14" t="str">
+        <x:v>main_scene4_representative_3d.png</x:v>
+      </x:c>
+      <x:c r="F23" s="14" t="str">
+        <x:v>supplement</x:v>
+      </x:c>
+      <x:c r="G23" s="14" t="str">
+        <x:v>Classic-baseline representative path comparison</x:v>
+      </x:c>
+      <x:c r="H23" s="14" t="str">
+        <x:v>ready</x:v>
+      </x:c>
+      <x:c r="I23" s="14" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\main\main_scene4_representative_3d.png</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="42" hidden="0" customHeight="1">
-      <x:c r="A22" s="17" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B22" s="8" t="str">
+    <x:row r="24" ht="42" customHeight="1">
+      <x:c r="A24" s="115" t="str">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B24" s="115" t="str">
         <x:v>main-path</x:v>
       </x:c>
-      <x:c r="C22" s="17" t="n">
+      <x:c r="C24" s="115" t="str">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D22" s="8" t="str">
+      <x:c r="D24" s="115" t="str">
         <x:v>top</x:v>
       </x:c>
-      <x:c r="E22" s="14" t="str">
+      <x:c r="E24" s="116" t="str">
         <x:v>main_scene4_representative_top.png</x:v>
       </x:c>
-      <x:c r="F22" s="8" t="str">
+      <x:c r="F24" s="116" t="str">
         <x:v>supplement</x:v>
       </x:c>
-      <x:c r="G22" s="14" t="str">
+      <x:c r="G24" s="116" t="str">
         <x:v>Classic-baseline representative path comparison</x:v>
       </x:c>
-      <x:c r="H22" s="8" t="str">
+      <x:c r="H24" s="116" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I22" s="14" t="str">
+      <x:c r="I24" s="116" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\main\main_scene4_representative_top.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="42" customHeight="1">
+      <x:c r="A25" s="119" t="str">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B25" s="119" t="str">
+        <x:v>method</x:v>
+      </x:c>
+      <x:c r="C25" s="119" t="str"/>
+      <x:c r="D25" s="119" t="str">
+        <x:v>flowchart</x:v>
+      </x:c>
+      <x:c r="E25" s="120" t="str">
+        <x:v>cvf_ae_method_flowchart.png</x:v>
+      </x:c>
+      <x:c r="F25" s="120" t="str">
+        <x:v>main-text</x:v>
+      </x:c>
+      <x:c r="G25" s="120" t="str">
+        <x:v>Present the complete CVF-AE procedure</x:v>
+      </x:c>
+      <x:c r="H25" s="120" t="str">
+        <x:v>ready</x:v>
+      </x:c>
+      <x:c r="I25" s="120" t="str">
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_paper_completion_figures_20260624_from_formal_results\cvf_ae_method_flowchart.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="42" customHeight="1">
+      <x:c r="A26" s="119" t="str">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B26" s="119" t="str">
+        <x:v>parameter-sensitivity</x:v>
+      </x:c>
+      <x:c r="C26" s="119" t="str"/>
+      <x:c r="D26" s="119" t="str">
+        <x:v>mean-std</x:v>
+      </x:c>
+      <x:c r="E26" s="120" t="str">
+        <x:v>cvf_ae_parameter_sensitivity.png</x:v>
+      </x:c>
+      <x:c r="F26" s="120" t="str">
+        <x:v>main-text</x:v>
+      </x:c>
+      <x:c r="G26" s="120" t="str">
+        <x:v>Evaluate robustness to key CVF parameters</x:v>
+      </x:c>
+      <x:c r="H26" s="120" t="str">
+        <x:v>ready</x:v>
+      </x:c>
+      <x:c r="I26" s="120" t="str">
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_paper_completion_figures_20260624_from_formal_results\cvf_ae_parameter_sensitivity.png</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd27ef4b8957b4d07"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52e1e429ea0a46d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2152,7 +2356,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R324a32778e5549c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa19dae785f34bd1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3822,7 +4026,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd42d90721b004a3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a7083109098478d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5026,7 +5230,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff0b057ed5934b0c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf715fa9ccb824558"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5878,7 +6082,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a9e584f45f549fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R134d3259c7094814"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6512,7 +6716,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R437b8fc378e5467f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf89cfcf65e0a4904"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7376,7 +7580,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdf05d14336e4226"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5512fea505c47fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8810,7 +9014,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26279432754046c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d96c7e129434459"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10128,7 +10332,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfbf8bce00e14295"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c1ce9f32408407b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/routes/route_b_cvf_ae/results/cvf_ae_paper_results_package_20260624_from_formal_results/CVF_AE_PAPER_RESULTS_PACKAGE.xlsx
+++ b/routes/route_b_cvf_ae/results/cvf_ae_paper_results_package_20260624_from_formal_results/CVF_AE_PAPER_RESULTS_PACKAGE.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="R4881aa6a29dc4afb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main Compact" sheetId="2" r:id="R85d6548b381049f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main Long" sheetId="3" r:id="R2927547773f6492a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Significance" sheetId="4" r:id="R7c51ae55261c4639"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ablation" sheetId="5" r:id="Ra96db164ebe94785"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ablation Sig" sheetId="6" r:id="R63f3d778d839466d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="7" r:id="R310f592c1ee04274"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overhead" sheetId="8" r:id="R0eb31390b12549bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trajectory" sheetId="9" r:id="R3db9fdf456e44068"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure Index" sheetId="10" r:id="R5df5d6ac55f44b49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" r:id="Re10325d0c8124791"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main Compact" sheetId="2" r:id="R044246404d0d4938"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Main Long" sheetId="3" r:id="Rb04d624385c141db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Significance" sheetId="4" r:id="Rf868eb74158241b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ablation" sheetId="5" r:id="R33e8a211cffe44eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ablation Sig" sheetId="6" r:id="Rf82e02f9b06644e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="7" r:id="Re84a338510804399"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overhead" sheetId="8" r:id="Rbfd65ccc6f5e455f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trajectory" sheetId="9" r:id="R1d178633f6c5427f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Figure Index" sheetId="10" r:id="Rb85c5310c6774b8f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -65,7 +65,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="14">
+  <x:fills count="24">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -130,6 +130,56 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFCE4D6"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE2F0D9"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFCE4D6"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -204,7 +254,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="121">
+  <x:cellXfs count="159">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -524,6 +574,120 @@
     <x:xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="14" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="14" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="15" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="17" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="19" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="2" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="2" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="2" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="4" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="4" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="4" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="22" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="23" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -532,7 +696,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MainCompactTable" displayName="MainCompactTable" ref="A1:L12" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="MainCompactTable" displayName="MainCompactTable" ref="A1:L12" headerRowCount="1">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="Algorithm"/>
     <x:tableColumn id="2" name="S1 Mean +/- Std"/>
@@ -541,9 +705,9 @@
     <x:tableColumn id="5" name="S2 Mean +/- Std"/>
     <x:tableColumn id="6" name="S2 Feasible"/>
     <x:tableColumn id="7" name="S2 Rank"/>
-    <x:tableColumn id="8" name="S4 Mean +/- Std"/>
-    <x:tableColumn id="9" name="S4 Feasible"/>
-    <x:tableColumn id="10" name="S4 Rank"/>
+    <x:tableColumn id="8" name="S3 Mean +/- Std"/>
+    <x:tableColumn id="9" name="S3 Feasible"/>
+    <x:tableColumn id="10" name="S3 Rank"/>
     <x:tableColumn id="11" name="AverageRank"/>
     <x:tableColumn id="12" name="Avg Visual Flag"/>
   </x:tableColumns>
@@ -552,7 +716,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="MainLongTable" displayName="MainLongTable" ref="A1:P34" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="MainLongTable" displayName="MainLongTable" ref="A1:P34" headerRowCount="1">
   <x:tableColumns count="16">
     <x:tableColumn id="1" name="Scene"/>
     <x:tableColumn id="2" name="Algorithm"/>
@@ -576,7 +740,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SignificanceTable" displayName="SignificanceTable" ref="A1:L31" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="SignificanceTable" displayName="SignificanceTable" ref="A1:L31" headerRowCount="1">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="Scene"/>
     <x:tableColumn id="2" name="ComparedMethod"/>
@@ -586,7 +750,7 @@
     <x:tableColumn id="6" name="RawP"/>
     <x:tableColumn id="7" name="SceneHolmP"/>
     <x:tableColumn id="8" name="Result"/>
-    <x:tableColumn id="9" name="Cliff's Delta"/>
+    <x:tableColumn id="9" name="CliffsDelta"/>
     <x:tableColumn id="10" name="EffectMagnitude"/>
     <x:tableColumn id="11" name="GlobalHolmP"/>
     <x:tableColumn id="12" name="GlobalResult"/>
@@ -596,7 +760,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="AblationTable" displayName="AblationTable" ref="A1:N19" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="AblationTable" displayName="AblationTable" ref="A1:N19" headerRowCount="1">
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="Scene"/>
     <x:tableColumn id="2" name="Variant"/>
@@ -618,7 +782,7 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="AblationSigTable" displayName="AblationSigTable" ref="A1:L16" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="AblationSigTable" displayName="AblationSigTable" ref="A1:L16" headerRowCount="1">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="Scene"/>
     <x:tableColumn id="2" name="ComparedMethod"/>
@@ -628,7 +792,7 @@
     <x:tableColumn id="6" name="RawP"/>
     <x:tableColumn id="7" name="SceneHolmP"/>
     <x:tableColumn id="8" name="Result"/>
-    <x:tableColumn id="9" name="Cliff's Delta"/>
+    <x:tableColumn id="9" name="CliffsDelta"/>
     <x:tableColumn id="10" name="EffectMagnitude"/>
     <x:tableColumn id="11" name="GlobalHolmP"/>
     <x:tableColumn id="12" name="GlobalResult"/>
@@ -638,12 +802,12 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="ParametersTable" displayName="ParametersTable" ref="A1:N19" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="ParametersTable" displayName="ParametersTable" ref="A1:N19" headerRowCount="1">
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="Parameter"/>
     <x:tableColumn id="2" name="ParameterLabel"/>
     <x:tableColumn id="3" name="Level"/>
-    <x:tableColumn id="4" name="Level Description"/>
+    <x:tableColumn id="4" name="LevelDescription"/>
     <x:tableColumn id="5" name="IsDefault"/>
     <x:tableColumn id="6" name="Scene"/>
     <x:tableColumn id="7" name="MeanFitness"/>
@@ -660,7 +824,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="OverheadTable" displayName="OverheadTable" ref="A1:K43" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="OverheadTable" displayName="OverheadTable" ref="A1:K43" headerRowCount="1">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="Analysis"/>
     <x:tableColumn id="2" name="Scene"/>
@@ -669,8 +833,8 @@
     <x:tableColumn id="5" name="NEvals"/>
     <x:tableColumn id="6" name="CVFTriggerCount"/>
     <x:tableColumn id="7" name="CVFSuccessCount"/>
-    <x:tableColumn id="8" name="Runtime Ratio vs w/o CVF"/>
-    <x:tableColumn id="9" name="NEvals Ratio vs w/o CVF"/>
+    <x:tableColumn id="8" name="RuntimeRatioVsWithoutCVF"/>
+    <x:tableColumn id="9" name="NEvalsRatioVsWithoutCVF"/>
     <x:tableColumn id="10" name="FeasibleRate"/>
     <x:tableColumn id="11" name="Rank"/>
   </x:tableColumns>
@@ -679,7 +843,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="TrajectoryTable" displayName="TrajectoryTable" ref="A1:L34" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="TrajectoryTable" displayName="TrajectoryTable" ref="A1:L34" headerRowCount="1">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="Scene"/>
     <x:tableColumn id="2" name="Algorithm"/>
@@ -688,9 +852,9 @@
     <x:tableColumn id="5" name="High-Altitude Frac"/>
     <x:tableColumn id="6" name="DetourRatio"/>
     <x:tableColumn id="7" name="Boundary-Hug Frac"/>
-    <x:tableColumn id="8" name="High-Altitude Flag"/>
-    <x:tableColumn id="9" name="Boundary-Hug Flag"/>
-    <x:tableColumn id="10" name="Detour Flag"/>
+    <x:tableColumn id="8" name="HighAltitudeFlagRate"/>
+    <x:tableColumn id="9" name="BoundaryHugFlagRate"/>
+    <x:tableColumn id="10" name="ExcessiveDetourFlagRate"/>
     <x:tableColumn id="11" name="Visual Flag Rate"/>
     <x:tableColumn id="12" name="Source"/>
   </x:tableColumns>
@@ -699,7 +863,7 @@
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="FigureIndexTable" displayName="FigureIndexTable" ref="A1:I26" headerRowCount="1">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="27" name="FigureIndexTable" displayName="FigureIndexTable" ref="A1:I26" headerRowCount="1">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="FigureId"/>
     <x:tableColumn id="2" name="Group"/>
@@ -967,7 +1131,7 @@
         <x:v>Formal scenes</x:v>
       </x:c>
       <x:c r="B5" s="96" t="str">
-        <x:v>1, 2, 4</x:v>
+        <x:v>1, 2, 3</x:v>
       </x:c>
       <x:c r="D5" s="87"/>
       <x:c r="E5" s="88"/>
@@ -1114,767 +1278,767 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="11" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="36" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="11" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="45" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="30" hidden="0" customHeight="1">
-      <x:c r="A1" s="114" t="str">
+    <x:row r="1" ht="15" hidden="0" customHeight="1">
+      <x:c r="A1" s="142" t="str">
         <x:v>FigureId</x:v>
       </x:c>
-      <x:c r="B1" s="114" t="str">
+      <x:c r="B1" s="142" t="str">
         <x:v>Group</x:v>
       </x:c>
-      <x:c r="C1" s="114" t="str">
+      <x:c r="C1" s="142" t="str">
         <x:v>Scene</x:v>
       </x:c>
-      <x:c r="D1" s="114" t="str">
+      <x:c r="D1" s="142" t="str">
         <x:v>View</x:v>
       </x:c>
-      <x:c r="E1" s="114" t="str">
+      <x:c r="E1" s="142" t="str">
         <x:v>FileName</x:v>
       </x:c>
-      <x:c r="F1" s="114" t="str">
+      <x:c r="F1" s="142" t="str">
         <x:v>SuggestedPlacement</x:v>
       </x:c>
-      <x:c r="G1" s="114" t="str">
+      <x:c r="G1" s="142" t="str">
         <x:v>Purpose</x:v>
       </x:c>
-      <x:c r="H1" s="114" t="str">
+      <x:c r="H1" s="142" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="I1" s="114" t="str">
+      <x:c r="I1" s="142" t="str">
         <x:v>RelativePath</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="42" hidden="0" customHeight="1">
-      <x:c r="A2" s="115" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="115" t="str">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="str">
         <x:v>ablation-path</x:v>
       </x:c>
-      <x:c r="C2" s="115" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="115" t="str">
+      <x:c r="C2" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D2" s="8" t="str">
         <x:v>3d</x:v>
       </x:c>
-      <x:c r="E2" s="116" t="str">
+      <x:c r="E2" s="8" t="str">
         <x:v>ablation_scene1_representative_3d.png</x:v>
       </x:c>
-      <x:c r="F2" s="116" t="str">
+      <x:c r="F2" s="8" t="str">
         <x:v>supplement</x:v>
       </x:c>
-      <x:c r="G2" s="116" t="str">
+      <x:c r="G2" s="14" t="str">
         <x:v>Visualize module contribution and failure cases</x:v>
       </x:c>
-      <x:c r="H2" s="116" t="str">
+      <x:c r="H2" s="8" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I2" s="116" t="str">
+      <x:c r="I2" s="14" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\ablation\ablation_scene1_representative_3d.png</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="42" hidden="0" customHeight="1">
-      <x:c r="A3" s="8" t="str">
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="8" t="str">
         <x:v>ablation-path</x:v>
       </x:c>
-      <x:c r="C3" s="8" t="str">
+      <x:c r="C3" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D3" s="8" t="str">
         <x:v>top</x:v>
       </x:c>
-      <x:c r="E3" s="14" t="str">
+      <x:c r="E3" s="8" t="str">
         <x:v>ablation_scene1_representative_top.png</x:v>
       </x:c>
-      <x:c r="F3" s="14" t="str">
+      <x:c r="F3" s="8" t="str">
         <x:v>supplement</x:v>
       </x:c>
       <x:c r="G3" s="14" t="str">
         <x:v>Visualize module contribution and failure cases</x:v>
       </x:c>
-      <x:c r="H3" s="14" t="str">
+      <x:c r="H3" s="8" t="str">
         <x:v>ready</x:v>
       </x:c>
       <x:c r="I3" s="14" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\ablation\ablation_scene1_representative_top.png</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="42" hidden="0" customHeight="1">
-      <x:c r="A4" s="115" t="str">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B4" s="115" t="str">
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="8" t="str">
         <x:v>ablation-path</x:v>
       </x:c>
-      <x:c r="C4" s="115" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="115" t="str">
+      <x:c r="C4" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D4" s="8" t="str">
         <x:v>3d</x:v>
       </x:c>
-      <x:c r="E4" s="116" t="str">
+      <x:c r="E4" s="8" t="str">
         <x:v>ablation_scene2_representative_3d.png</x:v>
       </x:c>
-      <x:c r="F4" s="116" t="str">
+      <x:c r="F4" s="8" t="str">
         <x:v>supplement</x:v>
       </x:c>
-      <x:c r="G4" s="116" t="str">
+      <x:c r="G4" s="14" t="str">
         <x:v>Visualize module contribution and failure cases</x:v>
       </x:c>
-      <x:c r="H4" s="116" t="str">
+      <x:c r="H4" s="8" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I4" s="116" t="str">
+      <x:c r="I4" s="14" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\ablation\ablation_scene2_representative_3d.png</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="42" hidden="0" customHeight="1">
-      <x:c r="A5" s="119" t="str">
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="152" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B5" s="119" t="str">
+      <x:c r="B5" s="152" t="str">
         <x:v>ablation-path</x:v>
       </x:c>
-      <x:c r="C5" s="119" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="119" t="str">
+      <x:c r="C5" s="152" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D5" s="152" t="str">
         <x:v>top</x:v>
       </x:c>
-      <x:c r="E5" s="120" t="str">
+      <x:c r="E5" s="152" t="str">
         <x:v>ablation_scene2_representative_top.png</x:v>
       </x:c>
-      <x:c r="F5" s="120" t="str">
+      <x:c r="F5" s="152" t="str">
         <x:v>main-text</x:v>
       </x:c>
-      <x:c r="G5" s="120" t="str">
+      <x:c r="G5" s="158" t="str">
         <x:v>Visualize module contribution and failure cases</x:v>
       </x:c>
-      <x:c r="H5" s="120" t="str">
+      <x:c r="H5" s="152" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I5" s="120" t="str">
+      <x:c r="I5" s="158" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\ablation\ablation_scene2_representative_top.png</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="42" hidden="0" customHeight="1">
-      <x:c r="A6" s="115" t="str">
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B6" s="115" t="str">
+      <x:c r="B6" s="8" t="str">
         <x:v>ablation-path</x:v>
       </x:c>
-      <x:c r="C6" s="115" t="str">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="115" t="str">
+      <x:c r="C6" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D6" s="8" t="str">
         <x:v>3d</x:v>
       </x:c>
-      <x:c r="E6" s="116" t="str">
-        <x:v>ablation_scene4_representative_3d.png</x:v>
-      </x:c>
-      <x:c r="F6" s="116" t="str">
+      <x:c r="E6" s="8" t="str">
+        <x:v>ablation_scene3_representative_3d.png</x:v>
+      </x:c>
+      <x:c r="F6" s="8" t="str">
         <x:v>supplement</x:v>
       </x:c>
-      <x:c r="G6" s="116" t="str">
+      <x:c r="G6" s="14" t="str">
         <x:v>Visualize module contribution and failure cases</x:v>
       </x:c>
-      <x:c r="H6" s="116" t="str">
+      <x:c r="H6" s="8" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I6" s="116" t="str">
-        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\ablation\ablation_scene4_representative_3d.png</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="42" hidden="0" customHeight="1">
-      <x:c r="A7" s="119" t="str">
+      <x:c r="I6" s="14" t="str">
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\ablation\ablation_scene3_representative_3d.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B7" s="119" t="str">
+      <x:c r="B7" s="8" t="str">
         <x:v>ablation-path</x:v>
       </x:c>
-      <x:c r="C7" s="119" t="str">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D7" s="119" t="str">
+      <x:c r="C7" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D7" s="8" t="str">
         <x:v>top</x:v>
       </x:c>
-      <x:c r="E7" s="120" t="str">
-        <x:v>ablation_scene4_representative_top.png</x:v>
-      </x:c>
-      <x:c r="F7" s="120" t="str">
+      <x:c r="E7" s="8" t="str">
+        <x:v>ablation_scene3_representative_top.png</x:v>
+      </x:c>
+      <x:c r="F7" s="8" t="str">
+        <x:v>supplement</x:v>
+      </x:c>
+      <x:c r="G7" s="14" t="str">
+        <x:v>Visualize module contribution and failure cases</x:v>
+      </x:c>
+      <x:c r="H7" s="8" t="str">
+        <x:v>ready</x:v>
+      </x:c>
+      <x:c r="I7" s="14" t="str">
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\ablation\ablation_scene3_representative_top.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="8" t="str">
+        <x:v>boxplot</x:v>
+      </x:c>
+      <x:c r="C8" s="8" t="str"/>
+      <x:c r="D8" s="8" t="str">
+        <x:v>all-log</x:v>
+      </x:c>
+      <x:c r="E8" s="8" t="str">
+        <x:v>cvf_ae_boxplots_all_algorithms_log.png</x:v>
+      </x:c>
+      <x:c r="F8" s="8" t="str">
+        <x:v>supplement</x:v>
+      </x:c>
+      <x:c r="G8" s="14" t="str">
+        <x:v>Compare run distributions of all eleven algorithms</x:v>
+      </x:c>
+      <x:c r="H8" s="8" t="str">
+        <x:v>ready</x:v>
+      </x:c>
+      <x:c r="I8" s="14" t="str">
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_paper_completion_figures_20260624_from_formal_results\cvf_ae_boxplots_all_algorithms_log.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="152" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="152" t="str">
+        <x:v>boxplot</x:v>
+      </x:c>
+      <x:c r="C9" s="152" t="str"/>
+      <x:c r="D9" s="152" t="str">
+        <x:v>strong-linear</x:v>
+      </x:c>
+      <x:c r="E9" s="152" t="str">
+        <x:v>cvf_ae_boxplots_strong_algorithms.png</x:v>
+      </x:c>
+      <x:c r="F9" s="152" t="str">
         <x:v>main-text</x:v>
       </x:c>
-      <x:c r="G7" s="120" t="str">
-        <x:v>Visualize module contribution and failure cases</x:v>
-      </x:c>
-      <x:c r="H7" s="120" t="str">
+      <x:c r="G9" s="158" t="str">
+        <x:v>Compare run distributions of six strong algorithms</x:v>
+      </x:c>
+      <x:c r="H9" s="152" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I7" s="120" t="str">
-        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\ablation\ablation_scene4_representative_top.png</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="42" hidden="0" customHeight="1">
-      <x:c r="A8" s="115" t="str">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B8" s="115" t="str">
-        <x:v>boxplot</x:v>
-      </x:c>
-      <x:c r="C8" s="115" t="str"/>
-      <x:c r="D8" s="115" t="str">
-        <x:v>all-log</x:v>
-      </x:c>
-      <x:c r="E8" s="116" t="str">
-        <x:v>cvf_ae_boxplots_all_algorithms_log.png</x:v>
-      </x:c>
-      <x:c r="F8" s="116" t="str">
-        <x:v>supplement</x:v>
-      </x:c>
-      <x:c r="G8" s="116" t="str">
-        <x:v>Compare run distributions of all eleven algorithms</x:v>
-      </x:c>
-      <x:c r="H8" s="116" t="str">
+      <x:c r="I9" s="158" t="str">
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_paper_completion_figures_20260624_from_formal_results\cvf_ae_boxplots_strong_algorithms.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="152" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B10" s="152" t="str">
+        <x:v>convergence</x:v>
+      </x:c>
+      <x:c r="C10" s="152" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D10" s="152" t="str">
+        <x:v>mean-std</x:v>
+      </x:c>
+      <x:c r="E10" s="152" t="str">
+        <x:v>scene1_convergence_mean_std.png</x:v>
+      </x:c>
+      <x:c r="F10" s="152" t="str">
+        <x:v>main-text</x:v>
+      </x:c>
+      <x:c r="G10" s="158" t="str">
+        <x:v>Compare feasible-aware convergence behavior</x:v>
+      </x:c>
+      <x:c r="H10" s="152" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I8" s="116" t="str">
-        <x:v>routes\route_b_cvf_ae\results\cvf_ae_paper_completion_figures_20260624_from_formal_results\cvf_ae_boxplots_all_algorithms_log.png</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="42" hidden="0" customHeight="1">
-      <x:c r="A9" s="119" t="str">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B9" s="119" t="str">
-        <x:v>boxplot</x:v>
-      </x:c>
-      <x:c r="C9" s="119" t="str"/>
-      <x:c r="D9" s="119" t="str">
-        <x:v>strong-linear</x:v>
-      </x:c>
-      <x:c r="E9" s="120" t="str">
-        <x:v>cvf_ae_boxplots_strong_algorithms.png</x:v>
-      </x:c>
-      <x:c r="F9" s="120" t="str">
+      <x:c r="I10" s="158" t="str">
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_convergence_curves_20260623_from_main_comparison\scene1_convergence_mean_std.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="152" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B11" s="152" t="str">
+        <x:v>convergence</x:v>
+      </x:c>
+      <x:c r="C11" s="152" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D11" s="152" t="str">
+        <x:v>mean-std</x:v>
+      </x:c>
+      <x:c r="E11" s="152" t="str">
+        <x:v>scene2_convergence_mean_std.png</x:v>
+      </x:c>
+      <x:c r="F11" s="152" t="str">
         <x:v>main-text</x:v>
       </x:c>
-      <x:c r="G9" s="120" t="str">
-        <x:v>Compare run distributions of six strong algorithms</x:v>
-      </x:c>
-      <x:c r="H9" s="120" t="str">
+      <x:c r="G11" s="158" t="str">
+        <x:v>Compare feasible-aware convergence behavior</x:v>
+      </x:c>
+      <x:c r="H11" s="152" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I9" s="120" t="str">
-        <x:v>routes\route_b_cvf_ae\results\cvf_ae_paper_completion_figures_20260624_from_formal_results\cvf_ae_boxplots_strong_algorithms.png</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="42" hidden="0" customHeight="1">
-      <x:c r="A10" s="119" t="str">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B10" s="119" t="str">
+      <x:c r="I11" s="158" t="str">
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_convergence_curves_20260623_from_main_comparison\scene2_convergence_mean_std.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="152" t="n">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B12" s="152" t="str">
         <x:v>convergence</x:v>
       </x:c>
-      <x:c r="C10" s="119" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="119" t="str">
+      <x:c r="C12" s="152" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D12" s="152" t="str">
         <x:v>mean-std</x:v>
       </x:c>
-      <x:c r="E10" s="120" t="str">
-        <x:v>scene1_convergence_mean_std.png</x:v>
-      </x:c>
-      <x:c r="F10" s="120" t="str">
+      <x:c r="E12" s="152" t="str">
+        <x:v>scene3_convergence_mean_std.png</x:v>
+      </x:c>
+      <x:c r="F12" s="152" t="str">
         <x:v>main-text</x:v>
       </x:c>
-      <x:c r="G10" s="120" t="str">
+      <x:c r="G12" s="158" t="str">
         <x:v>Compare feasible-aware convergence behavior</x:v>
       </x:c>
-      <x:c r="H10" s="120" t="str">
+      <x:c r="H12" s="152" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I10" s="120" t="str">
-        <x:v>routes\route_b_cvf_ae\results\cvf_ae_convergence_curves_20260623_from_main_comparison\scene1_convergence_mean_std.png</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="42" hidden="0" customHeight="1">
-      <x:c r="A11" s="119" t="str">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B11" s="119" t="str">
-        <x:v>convergence</x:v>
-      </x:c>
-      <x:c r="C11" s="119" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="119" t="str">
-        <x:v>mean-std</x:v>
-      </x:c>
-      <x:c r="E11" s="120" t="str">
-        <x:v>scene2_convergence_mean_std.png</x:v>
-      </x:c>
-      <x:c r="F11" s="120" t="str">
-        <x:v>main-text</x:v>
-      </x:c>
-      <x:c r="G11" s="120" t="str">
-        <x:v>Compare feasible-aware convergence behavior</x:v>
-      </x:c>
-      <x:c r="H11" s="120" t="str">
-        <x:v>ready</x:v>
-      </x:c>
-      <x:c r="I11" s="120" t="str">
-        <x:v>routes\route_b_cvf_ae\results\cvf_ae_convergence_curves_20260623_from_main_comparison\scene2_convergence_mean_std.png</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="42" hidden="0" customHeight="1">
-      <x:c r="A12" s="119" t="str">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B12" s="119" t="str">
-        <x:v>convergence</x:v>
-      </x:c>
-      <x:c r="C12" s="119" t="str">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D12" s="119" t="str">
-        <x:v>mean-std</x:v>
-      </x:c>
-      <x:c r="E12" s="120" t="str">
-        <x:v>scene4_convergence_mean_std.png</x:v>
-      </x:c>
-      <x:c r="F12" s="120" t="str">
-        <x:v>main-text</x:v>
-      </x:c>
-      <x:c r="G12" s="120" t="str">
-        <x:v>Compare feasible-aware convergence behavior</x:v>
-      </x:c>
-      <x:c r="H12" s="120" t="str">
-        <x:v>ready</x:v>
-      </x:c>
-      <x:c r="I12" s="120" t="str">
-        <x:v>routes\route_b_cvf_ae\results\cvf_ae_convergence_curves_20260623_from_main_comparison\scene4_convergence_mean_std.png</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="42" hidden="0" customHeight="1">
-      <x:c r="A13" s="8" t="str">
+      <x:c r="I12" s="158" t="str">
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_convergence_curves_20260623_from_main_comparison\scene3_convergence_mean_std.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="8" t="n">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="8" t="str">
         <x:v>extended-path</x:v>
       </x:c>
-      <x:c r="C13" s="8" t="str">
+      <x:c r="C13" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D13" s="8" t="str">
         <x:v>3d</x:v>
       </x:c>
-      <x:c r="E13" s="14" t="str">
+      <x:c r="E13" s="8" t="str">
         <x:v>extended_scene1_representative_3d.png</x:v>
       </x:c>
-      <x:c r="F13" s="14" t="str">
+      <x:c r="F13" s="8" t="str">
         <x:v>supplement</x:v>
       </x:c>
       <x:c r="G13" s="14" t="str">
         <x:v>Compare CVF-AE with strong and recent improved methods</x:v>
       </x:c>
-      <x:c r="H13" s="14" t="str">
+      <x:c r="H13" s="8" t="str">
         <x:v>ready</x:v>
       </x:c>
       <x:c r="I13" s="14" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\extended\extended_scene1_representative_3d.png</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="42" hidden="0" customHeight="1">
-      <x:c r="A14" s="119" t="str">
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="152" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B14" s="119" t="str">
+      <x:c r="B14" s="152" t="str">
         <x:v>extended-path</x:v>
       </x:c>
-      <x:c r="C14" s="119" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D14" s="119" t="str">
+      <x:c r="C14" s="152" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D14" s="152" t="str">
         <x:v>top</x:v>
       </x:c>
-      <x:c r="E14" s="120" t="str">
+      <x:c r="E14" s="152" t="str">
         <x:v>extended_scene1_representative_top.png</x:v>
       </x:c>
-      <x:c r="F14" s="120" t="str">
+      <x:c r="F14" s="152" t="str">
         <x:v>main-text</x:v>
       </x:c>
-      <x:c r="G14" s="120" t="str">
+      <x:c r="G14" s="158" t="str">
         <x:v>Compare CVF-AE with strong and recent improved methods</x:v>
       </x:c>
-      <x:c r="H14" s="120" t="str">
+      <x:c r="H14" s="152" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I14" s="120" t="str">
+      <x:c r="I14" s="158" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\extended\extended_scene1_representative_top.png</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="42" hidden="0" customHeight="1">
-      <x:c r="A15" s="8" t="str">
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="8" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="8" t="str">
         <x:v>extended-path</x:v>
       </x:c>
-      <x:c r="C15" s="8" t="str">
+      <x:c r="C15" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D15" s="8" t="str">
         <x:v>3d</x:v>
       </x:c>
-      <x:c r="E15" s="14" t="str">
+      <x:c r="E15" s="8" t="str">
         <x:v>extended_scene2_representative_3d.png</x:v>
       </x:c>
-      <x:c r="F15" s="14" t="str">
+      <x:c r="F15" s="8" t="str">
         <x:v>supplement</x:v>
       </x:c>
       <x:c r="G15" s="14" t="str">
         <x:v>Compare CVF-AE with strong and recent improved methods</x:v>
       </x:c>
-      <x:c r="H15" s="14" t="str">
+      <x:c r="H15" s="8" t="str">
         <x:v>ready</x:v>
       </x:c>
       <x:c r="I15" s="14" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\extended\extended_scene2_representative_3d.png</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="42" hidden="0" customHeight="1">
-      <x:c r="A16" s="119" t="str">
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="152" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="B16" s="119" t="str">
+      <x:c r="B16" s="152" t="str">
         <x:v>extended-path</x:v>
       </x:c>
-      <x:c r="C16" s="119" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="119" t="str">
+      <x:c r="C16" s="152" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D16" s="152" t="str">
         <x:v>top</x:v>
       </x:c>
-      <x:c r="E16" s="120" t="str">
+      <x:c r="E16" s="152" t="str">
         <x:v>extended_scene2_representative_top.png</x:v>
       </x:c>
-      <x:c r="F16" s="120" t="str">
+      <x:c r="F16" s="152" t="str">
         <x:v>main-text</x:v>
       </x:c>
-      <x:c r="G16" s="120" t="str">
+      <x:c r="G16" s="158" t="str">
         <x:v>Compare CVF-AE with strong and recent improved methods</x:v>
       </x:c>
-      <x:c r="H16" s="120" t="str">
+      <x:c r="H16" s="152" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I16" s="120" t="str">
+      <x:c r="I16" s="158" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\extended\extended_scene2_representative_top.png</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="42" hidden="0" customHeight="1">
-      <x:c r="A17" s="8" t="str">
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="8" t="n">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B17" s="8" t="str">
         <x:v>extended-path</x:v>
       </x:c>
-      <x:c r="C17" s="8" t="str">
-        <x:v>4</x:v>
+      <x:c r="C17" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D17" s="8" t="str">
         <x:v>3d</x:v>
       </x:c>
-      <x:c r="E17" s="14" t="str">
-        <x:v>extended_scene4_representative_3d.png</x:v>
-      </x:c>
-      <x:c r="F17" s="14" t="str">
+      <x:c r="E17" s="8" t="str">
+        <x:v>extended_scene3_representative_3d.png</x:v>
+      </x:c>
+      <x:c r="F17" s="8" t="str">
         <x:v>supplement</x:v>
       </x:c>
       <x:c r="G17" s="14" t="str">
         <x:v>Compare CVF-AE with strong and recent improved methods</x:v>
       </x:c>
-      <x:c r="H17" s="14" t="str">
+      <x:c r="H17" s="8" t="str">
         <x:v>ready</x:v>
       </x:c>
       <x:c r="I17" s="14" t="str">
-        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\extended\extended_scene4_representative_3d.png</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="42" hidden="0" customHeight="1">
-      <x:c r="A18" s="119" t="str">
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\extended\extended_scene3_representative_3d.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="152" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B18" s="119" t="str">
+      <x:c r="B18" s="152" t="str">
         <x:v>extended-path</x:v>
       </x:c>
-      <x:c r="C18" s="119" t="str">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D18" s="119" t="str">
+      <x:c r="C18" s="152" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D18" s="152" t="str">
         <x:v>top</x:v>
       </x:c>
-      <x:c r="E18" s="120" t="str">
-        <x:v>extended_scene4_representative_top.png</x:v>
-      </x:c>
-      <x:c r="F18" s="120" t="str">
+      <x:c r="E18" s="152" t="str">
+        <x:v>extended_scene3_representative_top.png</x:v>
+      </x:c>
+      <x:c r="F18" s="152" t="str">
         <x:v>main-text</x:v>
       </x:c>
-      <x:c r="G18" s="120" t="str">
+      <x:c r="G18" s="158" t="str">
         <x:v>Compare CVF-AE with strong and recent improved methods</x:v>
       </x:c>
-      <x:c r="H18" s="120" t="str">
+      <x:c r="H18" s="152" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I18" s="120" t="str">
-        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\extended\extended_scene4_representative_top.png</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="42" hidden="0" customHeight="1">
-      <x:c r="A19" s="8" t="str">
+      <x:c r="I18" s="158" t="str">
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\extended\extended_scene3_representative_top.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="8" t="n">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="8" t="str">
         <x:v>main-path</x:v>
       </x:c>
-      <x:c r="C19" s="8" t="str">
+      <x:c r="C19" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D19" s="8" t="str">
         <x:v>3d</x:v>
       </x:c>
-      <x:c r="E19" s="14" t="str">
+      <x:c r="E19" s="8" t="str">
         <x:v>main_scene1_representative_3d.png</x:v>
       </x:c>
-      <x:c r="F19" s="14" t="str">
+      <x:c r="F19" s="8" t="str">
         <x:v>supplement</x:v>
       </x:c>
       <x:c r="G19" s="14" t="str">
         <x:v>Classic-baseline representative path comparison</x:v>
       </x:c>
-      <x:c r="H19" s="14" t="str">
+      <x:c r="H19" s="8" t="str">
         <x:v>ready</x:v>
       </x:c>
       <x:c r="I19" s="14" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\main\main_scene1_representative_3d.png</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="42" hidden="0" customHeight="1">
-      <x:c r="A20" s="115" t="str">
+    <x:row r="20" ht="15" hidden="0" customHeight="1">
+      <x:c r="A20" s="8" t="n">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B20" s="115" t="str">
+      <x:c r="B20" s="8" t="str">
         <x:v>main-path</x:v>
       </x:c>
-      <x:c r="C20" s="115" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="115" t="str">
+      <x:c r="C20" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D20" s="8" t="str">
         <x:v>top</x:v>
       </x:c>
-      <x:c r="E20" s="116" t="str">
+      <x:c r="E20" s="8" t="str">
         <x:v>main_scene1_representative_top.png</x:v>
       </x:c>
-      <x:c r="F20" s="116" t="str">
+      <x:c r="F20" s="8" t="str">
         <x:v>supplement</x:v>
       </x:c>
-      <x:c r="G20" s="116" t="str">
+      <x:c r="G20" s="14" t="str">
         <x:v>Classic-baseline representative path comparison</x:v>
       </x:c>
-      <x:c r="H20" s="116" t="str">
+      <x:c r="H20" s="8" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I20" s="116" t="str">
+      <x:c r="I20" s="14" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\main\main_scene1_representative_top.png</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="42" hidden="0" customHeight="1">
-      <x:c r="A21" s="8" t="str">
+    <x:row r="21" ht="15" hidden="0" customHeight="1">
+      <x:c r="A21" s="8" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B21" s="8" t="str">
         <x:v>main-path</x:v>
       </x:c>
-      <x:c r="C21" s="8" t="str">
+      <x:c r="C21" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D21" s="8" t="str">
         <x:v>3d</x:v>
       </x:c>
-      <x:c r="E21" s="14" t="str">
+      <x:c r="E21" s="8" t="str">
         <x:v>main_scene2_representative_3d.png</x:v>
       </x:c>
-      <x:c r="F21" s="14" t="str">
+      <x:c r="F21" s="8" t="str">
         <x:v>supplement</x:v>
       </x:c>
       <x:c r="G21" s="14" t="str">
         <x:v>Classic-baseline representative path comparison</x:v>
       </x:c>
-      <x:c r="H21" s="14" t="str">
+      <x:c r="H21" s="8" t="str">
         <x:v>ready</x:v>
       </x:c>
       <x:c r="I21" s="14" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\main\main_scene2_representative_3d.png</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="42" hidden="0" customHeight="1">
-      <x:c r="A22" s="115" t="str">
+    <x:row r="22" ht="15" hidden="0" customHeight="1">
+      <x:c r="A22" s="8" t="n">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B22" s="115" t="str">
+      <x:c r="B22" s="8" t="str">
         <x:v>main-path</x:v>
       </x:c>
-      <x:c r="C22" s="115" t="str">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D22" s="115" t="str">
+      <x:c r="C22" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D22" s="8" t="str">
         <x:v>top</x:v>
       </x:c>
-      <x:c r="E22" s="116" t="str">
+      <x:c r="E22" s="8" t="str">
         <x:v>main_scene2_representative_top.png</x:v>
       </x:c>
-      <x:c r="F22" s="116" t="str">
+      <x:c r="F22" s="8" t="str">
         <x:v>supplement</x:v>
       </x:c>
-      <x:c r="G22" s="116" t="str">
+      <x:c r="G22" s="14" t="str">
         <x:v>Classic-baseline representative path comparison</x:v>
       </x:c>
-      <x:c r="H22" s="116" t="str">
+      <x:c r="H22" s="8" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I22" s="116" t="str">
+      <x:c r="I22" s="14" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\main\main_scene2_representative_top.png</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="42" customHeight="1">
-      <x:c r="A23" s="8" t="str">
+    <x:row r="23" ht="15" hidden="0" customHeight="1">
+      <x:c r="A23" s="8" t="n">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B23" s="8" t="str">
         <x:v>main-path</x:v>
       </x:c>
-      <x:c r="C23" s="8" t="str">
-        <x:v>4</x:v>
+      <x:c r="C23" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D23" s="8" t="str">
         <x:v>3d</x:v>
       </x:c>
-      <x:c r="E23" s="14" t="str">
-        <x:v>main_scene4_representative_3d.png</x:v>
-      </x:c>
-      <x:c r="F23" s="14" t="str">
+      <x:c r="E23" s="8" t="str">
+        <x:v>main_scene3_representative_3d.png</x:v>
+      </x:c>
+      <x:c r="F23" s="8" t="str">
         <x:v>supplement</x:v>
       </x:c>
       <x:c r="G23" s="14" t="str">
         <x:v>Classic-baseline representative path comparison</x:v>
       </x:c>
-      <x:c r="H23" s="14" t="str">
+      <x:c r="H23" s="8" t="str">
         <x:v>ready</x:v>
       </x:c>
       <x:c r="I23" s="14" t="str">
-        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\main\main_scene4_representative_3d.png</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" ht="42" customHeight="1">
-      <x:c r="A24" s="115" t="str">
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\main\main_scene3_representative_3d.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="15" hidden="0" customHeight="1">
+      <x:c r="A24" s="8" t="n">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="B24" s="115" t="str">
+      <x:c r="B24" s="8" t="str">
         <x:v>main-path</x:v>
       </x:c>
-      <x:c r="C24" s="115" t="str">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D24" s="115" t="str">
+      <x:c r="C24" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D24" s="8" t="str">
         <x:v>top</x:v>
       </x:c>
-      <x:c r="E24" s="116" t="str">
-        <x:v>main_scene4_representative_top.png</x:v>
-      </x:c>
-      <x:c r="F24" s="116" t="str">
+      <x:c r="E24" s="8" t="str">
+        <x:v>main_scene3_representative_top.png</x:v>
+      </x:c>
+      <x:c r="F24" s="8" t="str">
         <x:v>supplement</x:v>
       </x:c>
-      <x:c r="G24" s="116" t="str">
+      <x:c r="G24" s="14" t="str">
         <x:v>Classic-baseline representative path comparison</x:v>
       </x:c>
-      <x:c r="H24" s="116" t="str">
+      <x:c r="H24" s="8" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I24" s="116" t="str">
-        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\main\main_scene4_representative_top.png</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="42" customHeight="1">
-      <x:c r="A25" s="119" t="str">
+      <x:c r="I24" s="14" t="str">
+        <x:v>routes\route_b_cvf_ae\results\cvf_ae_representative_paths_20260623_from_formal_results\main\main_scene3_representative_top.png</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="15" hidden="0" customHeight="1">
+      <x:c r="A25" s="152" t="n">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B25" s="119" t="str">
+      <x:c r="B25" s="152" t="str">
         <x:v>method</x:v>
       </x:c>
-      <x:c r="C25" s="119" t="str"/>
-      <x:c r="D25" s="119" t="str">
+      <x:c r="C25" s="152" t="str"/>
+      <x:c r="D25" s="152" t="str">
         <x:v>flowchart</x:v>
       </x:c>
-      <x:c r="E25" s="120" t="str">
+      <x:c r="E25" s="152" t="str">
         <x:v>cvf_ae_method_flowchart.png</x:v>
       </x:c>
-      <x:c r="F25" s="120" t="str">
+      <x:c r="F25" s="152" t="str">
         <x:v>main-text</x:v>
       </x:c>
-      <x:c r="G25" s="120" t="str">
+      <x:c r="G25" s="158" t="str">
         <x:v>Present the complete CVF-AE procedure</x:v>
       </x:c>
-      <x:c r="H25" s="120" t="str">
+      <x:c r="H25" s="152" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I25" s="120" t="str">
+      <x:c r="I25" s="158" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_paper_completion_figures_20260624_from_formal_results\cvf_ae_method_flowchart.png</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="42" customHeight="1">
-      <x:c r="A26" s="119" t="str">
+    <x:row r="26" ht="15" hidden="0" customHeight="1">
+      <x:c r="A26" s="152" t="n">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="B26" s="119" t="str">
+      <x:c r="B26" s="152" t="str">
         <x:v>parameter-sensitivity</x:v>
       </x:c>
-      <x:c r="C26" s="119" t="str"/>
-      <x:c r="D26" s="119" t="str">
+      <x:c r="C26" s="152" t="str"/>
+      <x:c r="D26" s="152" t="str">
         <x:v>mean-std</x:v>
       </x:c>
-      <x:c r="E26" s="120" t="str">
+      <x:c r="E26" s="152" t="str">
         <x:v>cvf_ae_parameter_sensitivity.png</x:v>
       </x:c>
-      <x:c r="F26" s="120" t="str">
+      <x:c r="F26" s="152" t="str">
         <x:v>main-text</x:v>
       </x:c>
-      <x:c r="G26" s="120" t="str">
+      <x:c r="G26" s="158" t="str">
         <x:v>Evaluate robustness to key CVF parameters</x:v>
       </x:c>
-      <x:c r="H26" s="120" t="str">
+      <x:c r="H26" s="152" t="str">
         <x:v>ready</x:v>
       </x:c>
-      <x:c r="I26" s="120" t="str">
+      <x:c r="I26" s="158" t="str">
         <x:v>routes\route_b_cvf_ae\results\cvf_ae_paper_completion_figures_20260624_from_formal_results\cvf_ae_parameter_sensitivity.png</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52e1e429ea0a46d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83d60a0abadb4933"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1884,92 +2048,92 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="11" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="28" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="11" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="11" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="11" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="11" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="13" t="str">
+      <x:c r="A1" s="142" t="str">
         <x:v>Algorithm</x:v>
       </x:c>
-      <x:c r="B1" s="13" t="str">
+      <x:c r="B1" s="142" t="str">
         <x:v>S1 Mean +/- Std</x:v>
       </x:c>
-      <x:c r="C1" s="13" t="str">
+      <x:c r="C1" s="142" t="str">
         <x:v>S1 Feasible</x:v>
       </x:c>
-      <x:c r="D1" s="13" t="str">
+      <x:c r="D1" s="142" t="str">
         <x:v>S1 Rank</x:v>
       </x:c>
-      <x:c r="E1" s="13" t="str">
+      <x:c r="E1" s="142" t="str">
         <x:v>S2 Mean +/- Std</x:v>
       </x:c>
-      <x:c r="F1" s="13" t="str">
+      <x:c r="F1" s="142" t="str">
         <x:v>S2 Feasible</x:v>
       </x:c>
-      <x:c r="G1" s="13" t="str">
+      <x:c r="G1" s="142" t="str">
         <x:v>S2 Rank</x:v>
       </x:c>
-      <x:c r="H1" s="13" t="str">
-        <x:v>S4 Mean +/- Std</x:v>
-      </x:c>
-      <x:c r="I1" s="13" t="str">
-        <x:v>S4 Feasible</x:v>
-      </x:c>
-      <x:c r="J1" s="13" t="str">
-        <x:v>S4 Rank</x:v>
-      </x:c>
-      <x:c r="K1" s="13" t="str">
+      <x:c r="H1" s="142" t="str">
+        <x:v>S3 Mean +/- Std</x:v>
+      </x:c>
+      <x:c r="I1" s="142" t="str">
+        <x:v>S3 Feasible</x:v>
+      </x:c>
+      <x:c r="J1" s="142" t="str">
+        <x:v>S3 Rank</x:v>
+      </x:c>
+      <x:c r="K1" s="142" t="str">
         <x:v>AverageRank</x:v>
       </x:c>
-      <x:c r="L1" s="13" t="str">
+      <x:c r="L1" s="142" t="str">
         <x:v>Avg Visual Flag</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="29" t="str">
+      <x:c r="A2" s="147" t="str">
         <x:v>CVF-AE</x:v>
       </x:c>
-      <x:c r="B2" s="30" t="str">
+      <x:c r="B2" s="148" t="str">
         <x:v>298.1379 +/- 2.7821</x:v>
       </x:c>
-      <x:c r="C2" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="32" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E2" s="30" t="str">
+      <x:c r="C2" s="149" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D2" s="150" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E2" s="148" t="str">
         <x:v>301.2018 +/- 2.9019</x:v>
       </x:c>
-      <x:c r="F2" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G2" s="32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H2" s="30" t="str">
+      <x:c r="F2" s="149" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G2" s="150" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H2" s="148" t="str">
         <x:v>349.2270 +/- 19.8954</x:v>
       </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
+      <x:c r="I2" s="149" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J2" s="150" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K2" s="150" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L2" s="149" t="n">
         <x:v>0.0666666666666667</x:v>
       </x:c>
     </x:row>
@@ -1977,31 +2141,31 @@
       <x:c r="A3" s="8" t="str">
         <x:v>CPO</x:v>
       </x:c>
-      <x:c r="B3" s="15" t="str">
+      <x:c r="B3" s="19" t="str">
         <x:v>298.3594 +/- 5.5794</x:v>
       </x:c>
       <x:c r="C3" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D3" s="17" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E3" s="15" t="str">
+      <x:c r="D3" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E3" s="19" t="str">
         <x:v>278.1196 +/- 1.8768</x:v>
       </x:c>
       <x:c r="F3" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G3" s="17" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="15" t="str">
+      <x:c r="G3" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H3" s="19" t="str">
         <x:v>519.8797 +/- 313.2061</x:v>
       </x:c>
       <x:c r="I3" s="16" t="n">
         <x:v>0.733333333333333</x:v>
       </x:c>
-      <x:c r="J3" s="17" t="n">
+      <x:c r="J3" s="18" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="K3" s="18" t="n">
@@ -2015,31 +2179,31 @@
       <x:c r="A4" s="8" t="str">
         <x:v>GDSAO</x:v>
       </x:c>
-      <x:c r="B4" s="15" t="str">
+      <x:c r="B4" s="19" t="str">
         <x:v>315.7542 +/- 8.2913</x:v>
       </x:c>
       <x:c r="C4" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D4" s="17" t="n">
+      <x:c r="D4" s="18" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="E4" s="15" t="str">
+      <x:c r="E4" s="19" t="str">
         <x:v>307.0675 +/- 18.8776</x:v>
       </x:c>
       <x:c r="F4" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G4" s="17" t="n">
+      <x:c r="G4" s="18" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="H4" s="15" t="str">
+      <x:c r="H4" s="19" t="str">
         <x:v>346.8474 +/- 3.8175</x:v>
       </x:c>
       <x:c r="I4" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J4" s="17" t="n">
+      <x:c r="J4" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K4" s="18" t="n">
@@ -2053,31 +2217,31 @@
       <x:c r="A5" s="8" t="str">
         <x:v>MSCSO</x:v>
       </x:c>
-      <x:c r="B5" s="15" t="str">
+      <x:c r="B5" s="19" t="str">
         <x:v>314.3453 +/- 19.2807</x:v>
       </x:c>
       <x:c r="C5" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D5" s="17" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E5" s="15" t="str">
+      <x:c r="D5" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E5" s="19" t="str">
         <x:v>291.1680 +/- 15.7347</x:v>
       </x:c>
       <x:c r="F5" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G5" s="17" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H5" s="15" t="str">
+      <x:c r="G5" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H5" s="19" t="str">
         <x:v>402.2712 +/- 189.0229</x:v>
       </x:c>
       <x:c r="I5" s="16" t="n">
         <x:v>0.933333333333333</x:v>
       </x:c>
-      <x:c r="J5" s="17" t="n">
+      <x:c r="J5" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="K5" s="18" t="n">
@@ -2091,31 +2255,31 @@
       <x:c r="A6" s="8" t="str">
         <x:v>ERIME</x:v>
       </x:c>
-      <x:c r="B6" s="15" t="str">
+      <x:c r="B6" s="19" t="str">
         <x:v>322.9893 +/- 12.0174</x:v>
       </x:c>
       <x:c r="C6" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D6" s="17" t="n">
+      <x:c r="D6" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="E6" s="15" t="str">
+      <x:c r="E6" s="19" t="str">
         <x:v>316.1932 +/- 28.5245</x:v>
       </x:c>
       <x:c r="F6" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G6" s="17" t="n">
+      <x:c r="G6" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="H6" s="15" t="str">
+      <x:c r="H6" s="19" t="str">
         <x:v>360.2347 +/- 21.6704</x:v>
       </x:c>
       <x:c r="I6" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J6" s="17" t="n">
+      <x:c r="J6" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="K6" s="18" t="n">
@@ -2129,31 +2293,31 @@
       <x:c r="A7" s="8" t="str">
         <x:v>DBO</x:v>
       </x:c>
-      <x:c r="B7" s="15" t="str">
+      <x:c r="B7" s="19" t="str">
         <x:v>344.8827 +/- 19.9703</x:v>
       </x:c>
       <x:c r="C7" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D7" s="17" t="n">
+      <x:c r="D7" s="18" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E7" s="15" t="str">
+      <x:c r="E7" s="19" t="str">
         <x:v>337.7867 +/- 29.1340</x:v>
       </x:c>
       <x:c r="F7" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G7" s="17" t="n">
+      <x:c r="G7" s="18" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H7" s="15" t="str">
+      <x:c r="H7" s="19" t="str">
         <x:v>376.3041 +/- 15.9951</x:v>
       </x:c>
       <x:c r="I7" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J7" s="17" t="n">
+      <x:c r="J7" s="18" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="K7" s="18" t="n">
@@ -2167,31 +2331,31 @@
       <x:c r="A8" s="8" t="str">
         <x:v>GWO</x:v>
       </x:c>
-      <x:c r="B8" s="15" t="str">
+      <x:c r="B8" s="19" t="str">
         <x:v>345.3695 +/- 81.8962</x:v>
       </x:c>
       <x:c r="C8" s="16" t="n">
         <x:v>0.933333333333333</x:v>
       </x:c>
-      <x:c r="D8" s="17" t="n">
+      <x:c r="D8" s="18" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="str">
+      <x:c r="E8" s="19" t="str">
         <x:v>341.1611 +/- 38.8516</x:v>
       </x:c>
       <x:c r="F8" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G8" s="17" t="n">
+      <x:c r="G8" s="18" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="H8" s="15" t="str">
+      <x:c r="H8" s="19" t="str">
         <x:v>608.4571 +/- 333.1796</x:v>
       </x:c>
       <x:c r="I8" s="16" t="n">
         <x:v>0.633333333333333</x:v>
       </x:c>
-      <x:c r="J8" s="17" t="n">
+      <x:c r="J8" s="18" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="K8" s="18" t="n">
@@ -2205,31 +2369,31 @@
       <x:c r="A9" s="8" t="str">
         <x:v>HHO</x:v>
       </x:c>
-      <x:c r="B9" s="15" t="str">
+      <x:c r="B9" s="19" t="str">
         <x:v>450.5575 +/- 198.3628</x:v>
       </x:c>
       <x:c r="C9" s="16" t="n">
         <x:v>0.8</x:v>
       </x:c>
-      <x:c r="D9" s="17" t="n">
+      <x:c r="D9" s="18" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="str">
+      <x:c r="E9" s="19" t="str">
         <x:v>395.8343 +/- 180.5172</x:v>
       </x:c>
       <x:c r="F9" s="16" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="G9" s="17" t="n">
+      <x:c r="G9" s="18" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="H9" s="15" t="str">
+      <x:c r="H9" s="19" t="str">
         <x:v>898.3440 +/- 469.4671</x:v>
       </x:c>
       <x:c r="I9" s="16" t="n">
         <x:v>0.366666666666667</x:v>
       </x:c>
-      <x:c r="J9" s="17" t="n">
+      <x:c r="J9" s="18" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="K9" s="18" t="n">
@@ -2243,31 +2407,31 @@
       <x:c r="A10" s="8" t="str">
         <x:v>PSO</x:v>
       </x:c>
-      <x:c r="B10" s="15" t="str">
+      <x:c r="B10" s="19" t="str">
         <x:v>397.5087 +/- 183.8273</x:v>
       </x:c>
       <x:c r="C10" s="16" t="n">
         <x:v>0.866666666666667</x:v>
       </x:c>
-      <x:c r="D10" s="17" t="n">
+      <x:c r="D10" s="18" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="str">
+      <x:c r="E10" s="19" t="str">
         <x:v>729.9490 +/- 434.6311</x:v>
       </x:c>
       <x:c r="F10" s="16" t="n">
         <x:v>0.433333333333333</x:v>
       </x:c>
-      <x:c r="G10" s="17" t="n">
+      <x:c r="G10" s="18" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="H10" s="15" t="str">
+      <x:c r="H10" s="19" t="str">
         <x:v>1295.4587 +/- 382.0206</x:v>
       </x:c>
       <x:c r="I10" s="16" t="n">
         <x:v>0.0333333333333333</x:v>
       </x:c>
-      <x:c r="J10" s="17" t="n">
+      <x:c r="J10" s="18" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="K10" s="18" t="n">
@@ -2281,31 +2445,31 @@
       <x:c r="A11" s="8" t="str">
         <x:v>WOA</x:v>
       </x:c>
-      <x:c r="B11" s="15" t="str">
+      <x:c r="B11" s="19" t="str">
         <x:v>611.0975 +/- 216.5299</x:v>
       </x:c>
       <x:c r="C11" s="16" t="n">
         <x:v>0.8</x:v>
       </x:c>
-      <x:c r="D11" s="17" t="n">
+      <x:c r="D11" s="18" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="str">
+      <x:c r="E11" s="19" t="str">
         <x:v>915.9034 +/- 396.6288</x:v>
       </x:c>
       <x:c r="F11" s="16" t="n">
         <x:v>0.433333333333333</x:v>
       </x:c>
-      <x:c r="G11" s="17" t="n">
+      <x:c r="G11" s="18" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H11" s="15" t="str">
+      <x:c r="H11" s="19" t="str">
         <x:v>1485.6743 +/- 426.3900</x:v>
       </x:c>
       <x:c r="I11" s="16" t="n">
         <x:v>0.0666666666666667</x:v>
       </x:c>
-      <x:c r="J11" s="17" t="n">
+      <x:c r="J11" s="18" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="K11" s="18" t="n">
@@ -2319,31 +2483,31 @@
       <x:c r="A12" s="8" t="str">
         <x:v>AE</x:v>
       </x:c>
-      <x:c r="B12" s="15" t="str">
+      <x:c r="B12" s="19" t="str">
         <x:v>810.3258 +/- 328.2829</x:v>
       </x:c>
       <x:c r="C12" s="16" t="n">
         <x:v>0.333333333333333</x:v>
       </x:c>
-      <x:c r="D12" s="17" t="n">
+      <x:c r="D12" s="18" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="str">
+      <x:c r="E12" s="19" t="str">
         <x:v>1668.4042 +/- 421.8461</x:v>
       </x:c>
       <x:c r="F12" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G12" s="17" t="n">
+      <x:c r="G12" s="18" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="H12" s="15" t="str">
+      <x:c r="H12" s="19" t="str">
         <x:v>1653.2705 +/- 200.9002</x:v>
       </x:c>
       <x:c r="I12" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J12" s="17" t="n">
+      <x:c r="J12" s="18" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="K12" s="18" t="n">
@@ -2356,7 +2520,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa19dae785f34bd1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06906de2608f45da"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2365,126 +2529,126 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="11" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="11" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="12.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="11" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="11.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="13" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="13.75" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="11" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="11.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="14" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="13" t="str">
+      <x:c r="A1" s="142" t="str">
         <x:v>Scene</x:v>
       </x:c>
-      <x:c r="B1" s="13" t="str">
+      <x:c r="B1" s="142" t="str">
         <x:v>Algorithm</x:v>
       </x:c>
-      <x:c r="C1" s="13" t="str">
+      <x:c r="C1" s="142" t="str">
         <x:v>MeanFitness</x:v>
       </x:c>
-      <x:c r="D1" s="13" t="str">
+      <x:c r="D1" s="142" t="str">
         <x:v>StdFitness</x:v>
       </x:c>
-      <x:c r="E1" s="13" t="str">
+      <x:c r="E1" s="142" t="str">
         <x:v>Mean +/- Std</x:v>
       </x:c>
-      <x:c r="F1" s="13" t="str">
+      <x:c r="F1" s="142" t="str">
         <x:v>FeasibleRate</x:v>
       </x:c>
-      <x:c r="G1" s="13" t="str">
+      <x:c r="G1" s="142" t="str">
         <x:v>SceneRank</x:v>
       </x:c>
-      <x:c r="H1" s="13" t="str">
+      <x:c r="H1" s="142" t="str">
         <x:v>AverageRank</x:v>
       </x:c>
-      <x:c r="I1" s="13" t="str">
+      <x:c r="I1" s="142" t="str">
         <x:v>RuntimeSeconds</x:v>
       </x:c>
-      <x:c r="J1" s="13" t="str">
+      <x:c r="J1" s="142" t="str">
         <x:v>NEvals</x:v>
       </x:c>
-      <x:c r="K1" s="13" t="str">
+      <x:c r="K1" s="142" t="str">
         <x:v>First Feasible Iter</x:v>
       </x:c>
-      <x:c r="L1" s="13" t="str">
+      <x:c r="L1" s="142" t="str">
         <x:v>Visual Flag Rate</x:v>
       </x:c>
-      <x:c r="M1" s="13" t="str">
+      <x:c r="M1" s="142" t="str">
         <x:v>High-Altitude Frac</x:v>
       </x:c>
-      <x:c r="N1" s="13" t="str">
+      <x:c r="N1" s="142" t="str">
         <x:v>Boundary-Hug Frac</x:v>
       </x:c>
-      <x:c r="O1" s="13" t="str">
+      <x:c r="O1" s="142" t="str">
         <x:v>DetourRatio</x:v>
       </x:c>
-      <x:c r="P1" s="13" t="str">
+      <x:c r="P1" s="142" t="str">
         <x:v>Source</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="32" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="29" t="str">
+      <x:c r="A2" s="147" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="147" t="str">
         <x:v>CVF-AE</x:v>
       </x:c>
-      <x:c r="C2" s="37" t="n">
+      <x:c r="C2" s="148" t="n">
         <x:v>298.137864539111</x:v>
       </x:c>
-      <x:c r="D2" s="37" t="n">
+      <x:c r="D2" s="148" t="n">
         <x:v>2.78208655359367</x:v>
       </x:c>
-      <x:c r="E2" s="30" t="str">
+      <x:c r="E2" s="148" t="str">
         <x:v>298.1379 +/- 2.7821</x:v>
       </x:c>
-      <x:c r="F2" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G2" s="32" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
+      <x:c r="F2" s="149" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G2" s="150" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H2" s="150" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I2" s="147" t="n">
         <x:v>5.93901229333333</x:v>
       </x:c>
-      <x:c r="J2" s="38" t="n">
+      <x:c r="J2" s="147" t="n">
         <x:v>9568.9</x:v>
       </x:c>
-      <x:c r="K2" s="39" t="n">
+      <x:c r="K2" s="149" t="n">
         <x:v>2.53333333333333</x:v>
       </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="31" t="n">
+      <x:c r="L2" s="149" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M2" s="149" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N2" s="149" t="n">
         <x:v>0.0187604690117253</x:v>
       </x:c>
-      <x:c r="O2" s="37" t="n">
+      <x:c r="O2" s="148" t="n">
         <x:v>1.06671698183956</x:v>
       </x:c>
-      <x:c r="P2" s="29" t="str">
+      <x:c r="P2" s="147" t="str">
         <x:v>formal-main</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="17" t="n">
+      <x:c r="A3" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="8" t="str">
@@ -2496,25 +2660,25 @@
       <x:c r="D3" s="19" t="n">
         <x:v>5.57943310837686</x:v>
       </x:c>
-      <x:c r="E3" s="15" t="str">
+      <x:c r="E3" s="19" t="str">
         <x:v>298.3594 +/- 5.5794</x:v>
       </x:c>
       <x:c r="F3" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G3" s="17" t="n">
+      <x:c r="G3" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="H3" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I3" s="16" t="n">
+      <x:c r="I3" s="8" t="n">
         <x:v>4.98090939</x:v>
       </x:c>
-      <x:c r="J3" s="20" t="n">
+      <x:c r="J3" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="K3" s="21" t="str"/>
+      <x:c r="K3" s="16" t="str"/>
       <x:c r="L3" s="16" t="n">
         <x:v>0.8</x:v>
       </x:c>
@@ -2532,7 +2696,7 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
-      <x:c r="A4" s="17" t="n">
+      <x:c r="A4" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="8" t="str">
@@ -2544,25 +2708,25 @@
       <x:c r="D4" s="19" t="n">
         <x:v>8.29126014009976</x:v>
       </x:c>
-      <x:c r="E4" s="15" t="str">
+      <x:c r="E4" s="19" t="str">
         <x:v>315.7542 +/- 8.2913</x:v>
       </x:c>
       <x:c r="F4" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G4" s="17" t="n">
+      <x:c r="G4" s="18" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="H4" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I4" s="16" t="n">
+      <x:c r="I4" s="8" t="n">
         <x:v>10.6612001</x:v>
       </x:c>
-      <x:c r="J4" s="20" t="n">
+      <x:c r="J4" s="8" t="n">
         <x:v>17955</x:v>
       </x:c>
-      <x:c r="K4" s="21" t="str"/>
+      <x:c r="K4" s="16" t="str"/>
       <x:c r="L4" s="16" t="n">
         <x:v>0.333333333333333</x:v>
       </x:c>
@@ -2580,7 +2744,7 @@
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="17" t="n">
+      <x:c r="A5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="8" t="str">
@@ -2592,25 +2756,25 @@
       <x:c r="D5" s="19" t="n">
         <x:v>19.2806929297655</x:v>
       </x:c>
-      <x:c r="E5" s="15" t="str">
+      <x:c r="E5" s="19" t="str">
         <x:v>314.3453 +/- 19.2807</x:v>
       </x:c>
       <x:c r="F5" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G5" s="17" t="n">
+      <x:c r="G5" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="H5" s="18" t="n">
         <x:v>3.33333333333333</x:v>
       </x:c>
-      <x:c r="I5" s="16" t="n">
+      <x:c r="I5" s="8" t="n">
         <x:v>13.31786533</x:v>
       </x:c>
-      <x:c r="J5" s="20" t="n">
+      <x:c r="J5" s="8" t="n">
         <x:v>21449.0666666667</x:v>
       </x:c>
-      <x:c r="K5" s="21" t="str"/>
+      <x:c r="K5" s="16" t="str"/>
       <x:c r="L5" s="16" t="n">
         <x:v>0.533333333333333</x:v>
       </x:c>
@@ -2628,7 +2792,7 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="17" t="n">
+      <x:c r="A6" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="8" t="str">
@@ -2640,25 +2804,25 @@
       <x:c r="D6" s="19" t="n">
         <x:v>12.0173974372193</x:v>
       </x:c>
-      <x:c r="E6" s="15" t="str">
+      <x:c r="E6" s="19" t="str">
         <x:v>322.9893 +/- 12.0174</x:v>
       </x:c>
       <x:c r="F6" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G6" s="17" t="n">
+      <x:c r="G6" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H6" s="18" t="n">
         <x:v>4.33333333333333</x:v>
       </x:c>
-      <x:c r="I6" s="16" t="n">
+      <x:c r="I6" s="8" t="n">
         <x:v>6.82150923666667</x:v>
       </x:c>
-      <x:c r="J6" s="20" t="n">
+      <x:c r="J6" s="8" t="n">
         <x:v>9483</x:v>
       </x:c>
-      <x:c r="K6" s="21" t="str"/>
+      <x:c r="K6" s="16" t="str"/>
       <x:c r="L6" s="16" t="n">
         <x:v>0.7</x:v>
       </x:c>
@@ -2676,7 +2840,7 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="17" t="n">
+      <x:c r="A7" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B7" s="8" t="str">
@@ -2688,25 +2852,25 @@
       <x:c r="D7" s="19" t="n">
         <x:v>19.9702827242648</x:v>
       </x:c>
-      <x:c r="E7" s="15" t="str">
+      <x:c r="E7" s="19" t="str">
         <x:v>344.8827 +/- 19.9703</x:v>
       </x:c>
       <x:c r="F7" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G7" s="17" t="n">
+      <x:c r="G7" s="18" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="H7" s="18" t="n">
         <x:v>5.33333333333333</x:v>
       </x:c>
-      <x:c r="I7" s="16" t="n">
+      <x:c r="I7" s="8" t="n">
         <x:v>6.99538198</x:v>
       </x:c>
-      <x:c r="J7" s="20" t="n">
+      <x:c r="J7" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="K7" s="21" t="str"/>
+      <x:c r="K7" s="16" t="str"/>
       <x:c r="L7" s="16" t="n">
         <x:v>0.9</x:v>
       </x:c>
@@ -2724,7 +2888,7 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="17" t="n">
+      <x:c r="A8" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B8" s="8" t="str">
@@ -2736,25 +2900,25 @@
       <x:c r="D8" s="19" t="n">
         <x:v>81.8961556697385</x:v>
       </x:c>
-      <x:c r="E8" s="15" t="str">
+      <x:c r="E8" s="19" t="str">
         <x:v>345.3695 +/- 81.8962</x:v>
       </x:c>
       <x:c r="F8" s="16" t="n">
         <x:v>0.933333333333333</x:v>
       </x:c>
-      <x:c r="G8" s="17" t="n">
+      <x:c r="G8" s="18" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="H8" s="18" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I8" s="16" t="n">
+      <x:c r="I8" s="8" t="n">
         <x:v>4.40407022333333</x:v>
       </x:c>
-      <x:c r="J8" s="20" t="n">
+      <x:c r="J8" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="K8" s="21" t="str"/>
+      <x:c r="K8" s="16" t="str"/>
       <x:c r="L8" s="16" t="n">
         <x:v>0.9</x:v>
       </x:c>
@@ -2772,7 +2936,7 @@
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="17" t="n">
+      <x:c r="A9" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="8" t="str">
@@ -2784,25 +2948,25 @@
       <x:c r="D9" s="19" t="n">
         <x:v>198.362819241478</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="str">
+      <x:c r="E9" s="19" t="str">
         <x:v>450.5575 +/- 198.3628</x:v>
       </x:c>
       <x:c r="F9" s="16" t="n">
         <x:v>0.8</x:v>
       </x:c>
-      <x:c r="G9" s="17" t="n">
+      <x:c r="G9" s="18" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="H9" s="18" t="n">
         <x:v>8.33333333333333</x:v>
       </x:c>
-      <x:c r="I9" s="16" t="n">
+      <x:c r="I9" s="8" t="n">
         <x:v>6.75716871666667</x:v>
       </x:c>
-      <x:c r="J9" s="20" t="n">
+      <x:c r="J9" s="8" t="n">
         <x:v>11484.2666666667</x:v>
       </x:c>
-      <x:c r="K9" s="21" t="str"/>
+      <x:c r="K9" s="16" t="str"/>
       <x:c r="L9" s="16" t="n">
         <x:v>0.6</x:v>
       </x:c>
@@ -2820,7 +2984,7 @@
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="17" t="n">
+      <x:c r="A10" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B10" s="8" t="str">
@@ -2832,25 +2996,25 @@
       <x:c r="D10" s="19" t="n">
         <x:v>183.82733574219</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="str">
+      <x:c r="E10" s="19" t="str">
         <x:v>397.5087 +/- 183.8273</x:v>
       </x:c>
       <x:c r="F10" s="16" t="n">
         <x:v>0.866666666666667</x:v>
       </x:c>
-      <x:c r="G10" s="17" t="n">
+      <x:c r="G10" s="18" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H10" s="18" t="n">
         <x:v>8.66666666666667</x:v>
       </x:c>
-      <x:c r="I10" s="16" t="n">
+      <x:c r="I10" s="8" t="n">
         <x:v>4.25249685</x:v>
       </x:c>
-      <x:c r="J10" s="20" t="n">
+      <x:c r="J10" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="K10" s="21" t="str"/>
+      <x:c r="K10" s="16" t="str"/>
       <x:c r="L10" s="16" t="n">
         <x:v>0.733333333333333</x:v>
       </x:c>
@@ -2868,7 +3032,7 @@
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
-      <x:c r="A11" s="17" t="n">
+      <x:c r="A11" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B11" s="8" t="str">
@@ -2880,25 +3044,25 @@
       <x:c r="D11" s="19" t="n">
         <x:v>216.529920450129</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="str">
+      <x:c r="E11" s="19" t="str">
         <x:v>611.0975 +/- 216.5299</x:v>
       </x:c>
       <x:c r="F11" s="16" t="n">
         <x:v>0.8</x:v>
       </x:c>
-      <x:c r="G11" s="17" t="n">
+      <x:c r="G11" s="18" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H11" s="18" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I11" s="16" t="n">
+      <x:c r="I11" s="8" t="n">
         <x:v>4.31642514333333</x:v>
       </x:c>
-      <x:c r="J11" s="20" t="n">
+      <x:c r="J11" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="K11" s="21" t="str"/>
+      <x:c r="K11" s="16" t="str"/>
       <x:c r="L11" s="16" t="n">
         <x:v>0.933333333333333</x:v>
       </x:c>
@@ -2916,7 +3080,7 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
-      <x:c r="A12" s="17" t="n">
+      <x:c r="A12" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B12" s="8" t="str">
@@ -2928,25 +3092,25 @@
       <x:c r="D12" s="19" t="n">
         <x:v>328.282889753162</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="str">
+      <x:c r="E12" s="19" t="str">
         <x:v>810.3258 +/- 328.2829</x:v>
       </x:c>
       <x:c r="F12" s="16" t="n">
         <x:v>0.333333333333333</x:v>
       </x:c>
-      <x:c r="G12" s="17" t="n">
+      <x:c r="G12" s="18" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="H12" s="18" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="I12" s="16" t="n">
+      <x:c r="I12" s="8" t="n">
         <x:v>4.41410844333333</x:v>
       </x:c>
-      <x:c r="J12" s="20" t="n">
+      <x:c r="J12" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="K12" s="21" t="str"/>
+      <x:c r="K12" s="16" t="str"/>
       <x:c r="L12" s="16" t="n">
         <x:v>0.666666666666667</x:v>
       </x:c>
@@ -2964,57 +3128,57 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
-      <x:c r="A13" s="32" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B13" s="29" t="str">
+      <x:c r="A13" s="147" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B13" s="147" t="str">
         <x:v>CVF-AE</x:v>
       </x:c>
-      <x:c r="C13" s="37" t="n">
+      <x:c r="C13" s="148" t="n">
         <x:v>301.201825136219</x:v>
       </x:c>
-      <x:c r="D13" s="37" t="n">
+      <x:c r="D13" s="148" t="n">
         <x:v>2.90186972412191</x:v>
       </x:c>
-      <x:c r="E13" s="30" t="str">
+      <x:c r="E13" s="148" t="str">
         <x:v>301.2018 +/- 2.9019</x:v>
       </x:c>
-      <x:c r="F13" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G13" s="32" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="H13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
+      <x:c r="F13" s="149" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G13" s="150" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H13" s="150" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I13" s="147" t="n">
         <x:v>6.79069524666667</x:v>
       </x:c>
-      <x:c r="J13" s="38" t="n">
+      <x:c r="J13" s="147" t="n">
         <x:v>9554.2</x:v>
       </x:c>
-      <x:c r="K13" s="39" t="n">
+      <x:c r="K13" s="149" t="n">
         <x:v>5.9</x:v>
       </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="31" t="n">
+      <x:c r="L13" s="149" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M13" s="149" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" s="149" t="n">
         <x:v>0.0872696817420436</x:v>
       </x:c>
-      <x:c r="O13" s="37" t="n">
+      <x:c r="O13" s="148" t="n">
         <x:v>1.15735054897051</x:v>
       </x:c>
-      <x:c r="P13" s="29" t="str">
+      <x:c r="P13" s="147" t="str">
         <x:v>formal-main</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
-      <x:c r="A14" s="17" t="n">
+      <x:c r="A14" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B14" s="8" t="str">
@@ -3026,25 +3190,25 @@
       <x:c r="D14" s="19" t="n">
         <x:v>1.87675641582886</x:v>
       </x:c>
-      <x:c r="E14" s="15" t="str">
+      <x:c r="E14" s="19" t="str">
         <x:v>278.1196 +/- 1.8768</x:v>
       </x:c>
       <x:c r="F14" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G14" s="17" t="n">
+      <x:c r="G14" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H14" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I14" s="16" t="n">
+      <x:c r="I14" s="8" t="n">
         <x:v>5.19165132333333</x:v>
       </x:c>
-      <x:c r="J14" s="20" t="n">
+      <x:c r="J14" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="K14" s="21" t="str"/>
+      <x:c r="K14" s="16" t="str"/>
       <x:c r="L14" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -3062,7 +3226,7 @@
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
-      <x:c r="A15" s="17" t="n">
+      <x:c r="A15" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B15" s="8" t="str">
@@ -3074,25 +3238,25 @@
       <x:c r="D15" s="19" t="n">
         <x:v>18.8775766793904</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="str">
+      <x:c r="E15" s="19" t="str">
         <x:v>307.0675 +/- 18.8776</x:v>
       </x:c>
       <x:c r="F15" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G15" s="17" t="n">
+      <x:c r="G15" s="18" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="H15" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I15" s="16" t="n">
+      <x:c r="I15" s="8" t="n">
         <x:v>11.4291836933333</x:v>
       </x:c>
-      <x:c r="J15" s="20" t="n">
+      <x:c r="J15" s="8" t="n">
         <x:v>17955</x:v>
       </x:c>
-      <x:c r="K15" s="21" t="str"/>
+      <x:c r="K15" s="16" t="str"/>
       <x:c r="L15" s="16" t="n">
         <x:v>0.933333333333333</x:v>
       </x:c>
@@ -3110,7 +3274,7 @@
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
-      <x:c r="A16" s="17" t="n">
+      <x:c r="A16" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B16" s="8" t="str">
@@ -3122,25 +3286,25 @@
       <x:c r="D16" s="19" t="n">
         <x:v>15.7347313951818</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="str">
+      <x:c r="E16" s="19" t="str">
         <x:v>291.1680 +/- 15.7347</x:v>
       </x:c>
       <x:c r="F16" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G16" s="17" t="n">
+      <x:c r="G16" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="H16" s="18" t="n">
         <x:v>3.33333333333333</x:v>
       </x:c>
-      <x:c r="I16" s="16" t="n">
+      <x:c r="I16" s="8" t="n">
         <x:v>13.4843612533333</x:v>
       </x:c>
-      <x:c r="J16" s="20" t="n">
+      <x:c r="J16" s="8" t="n">
         <x:v>21461.7333333333</x:v>
       </x:c>
-      <x:c r="K16" s="21" t="str"/>
+      <x:c r="K16" s="16" t="str"/>
       <x:c r="L16" s="16" t="n">
         <x:v>0.633333333333333</x:v>
       </x:c>
@@ -3158,7 +3322,7 @@
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
-      <x:c r="A17" s="17" t="n">
+      <x:c r="A17" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B17" s="8" t="str">
@@ -3170,25 +3334,25 @@
       <x:c r="D17" s="19" t="n">
         <x:v>28.5245034056776</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="str">
+      <x:c r="E17" s="19" t="str">
         <x:v>316.1932 +/- 28.5245</x:v>
       </x:c>
       <x:c r="F17" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G17" s="17" t="n">
+      <x:c r="G17" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H17" s="18" t="n">
         <x:v>4.33333333333333</x:v>
       </x:c>
-      <x:c r="I17" s="16" t="n">
+      <x:c r="I17" s="8" t="n">
         <x:v>6.28235261666667</x:v>
       </x:c>
-      <x:c r="J17" s="20" t="n">
+      <x:c r="J17" s="8" t="n">
         <x:v>9484.7</x:v>
       </x:c>
-      <x:c r="K17" s="21" t="str"/>
+      <x:c r="K17" s="16" t="str"/>
       <x:c r="L17" s="16" t="n">
         <x:v>0.666666666666667</x:v>
       </x:c>
@@ -3206,7 +3370,7 @@
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
-      <x:c r="A18" s="17" t="n">
+      <x:c r="A18" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B18" s="8" t="str">
@@ -3218,25 +3382,25 @@
       <x:c r="D18" s="19" t="n">
         <x:v>29.1339905205832</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="str">
+      <x:c r="E18" s="19" t="str">
         <x:v>337.7867 +/- 29.1340</x:v>
       </x:c>
       <x:c r="F18" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G18" s="17" t="n">
+      <x:c r="G18" s="18" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="H18" s="18" t="n">
         <x:v>5.33333333333333</x:v>
       </x:c>
-      <x:c r="I18" s="16" t="n">
+      <x:c r="I18" s="8" t="n">
         <x:v>4.83305744333333</x:v>
       </x:c>
-      <x:c r="J18" s="20" t="n">
+      <x:c r="J18" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="K18" s="21" t="str"/>
+      <x:c r="K18" s="16" t="str"/>
       <x:c r="L18" s="16" t="n">
         <x:v>0.933333333333333</x:v>
       </x:c>
@@ -3254,7 +3418,7 @@
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
-      <x:c r="A19" s="17" t="n">
+      <x:c r="A19" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B19" s="8" t="str">
@@ -3266,25 +3430,25 @@
       <x:c r="D19" s="19" t="n">
         <x:v>38.8515934412663</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="str">
+      <x:c r="E19" s="19" t="str">
         <x:v>341.1611 +/- 38.8516</x:v>
       </x:c>
       <x:c r="F19" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G19" s="17" t="n">
+      <x:c r="G19" s="18" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="H19" s="18" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I19" s="16" t="n">
+      <x:c r="I19" s="8" t="n">
         <x:v>5.70009725</x:v>
       </x:c>
-      <x:c r="J19" s="20" t="n">
+      <x:c r="J19" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="K19" s="21" t="str"/>
+      <x:c r="K19" s="16" t="str"/>
       <x:c r="L19" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -3302,7 +3466,7 @@
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
-      <x:c r="A20" s="17" t="n">
+      <x:c r="A20" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B20" s="8" t="str">
@@ -3314,25 +3478,25 @@
       <x:c r="D20" s="19" t="n">
         <x:v>180.517182230101</x:v>
       </x:c>
-      <x:c r="E20" s="15" t="str">
+      <x:c r="E20" s="19" t="str">
         <x:v>395.8343 +/- 180.5172</x:v>
       </x:c>
       <x:c r="F20" s="16" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="G20" s="17" t="n">
+      <x:c r="G20" s="18" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H20" s="18" t="n">
         <x:v>8.33333333333333</x:v>
       </x:c>
-      <x:c r="I20" s="16" t="n">
+      <x:c r="I20" s="8" t="n">
         <x:v>6.43362172</x:v>
       </x:c>
-      <x:c r="J20" s="20" t="n">
+      <x:c r="J20" s="8" t="n">
         <x:v>11451.7</x:v>
       </x:c>
-      <x:c r="K20" s="21" t="str"/>
+      <x:c r="K20" s="16" t="str"/>
       <x:c r="L20" s="16" t="n">
         <x:v>0.766666666666667</x:v>
       </x:c>
@@ -3350,7 +3514,7 @@
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
-      <x:c r="A21" s="17" t="n">
+      <x:c r="A21" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B21" s="8" t="str">
@@ -3362,25 +3526,25 @@
       <x:c r="D21" s="19" t="n">
         <x:v>434.631052838891</x:v>
       </x:c>
-      <x:c r="E21" s="15" t="str">
+      <x:c r="E21" s="19" t="str">
         <x:v>729.9490 +/- 434.6311</x:v>
       </x:c>
       <x:c r="F21" s="16" t="n">
         <x:v>0.433333333333333</x:v>
       </x:c>
-      <x:c r="G21" s="17" t="n">
+      <x:c r="G21" s="18" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="H21" s="18" t="n">
         <x:v>8.66666666666667</x:v>
       </x:c>
-      <x:c r="I21" s="16" t="n">
+      <x:c r="I21" s="8" t="n">
         <x:v>5.04003198333333</x:v>
       </x:c>
-      <x:c r="J21" s="20" t="n">
+      <x:c r="J21" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="K21" s="21" t="str"/>
+      <x:c r="K21" s="16" t="str"/>
       <x:c r="L21" s="16" t="n">
         <x:v>0.533333333333333</x:v>
       </x:c>
@@ -3398,7 +3562,7 @@
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
-      <x:c r="A22" s="17" t="n">
+      <x:c r="A22" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B22" s="8" t="str">
@@ -3410,25 +3574,25 @@
       <x:c r="D22" s="19" t="n">
         <x:v>396.628764364027</x:v>
       </x:c>
-      <x:c r="E22" s="15" t="str">
+      <x:c r="E22" s="19" t="str">
         <x:v>915.9034 +/- 396.6288</x:v>
       </x:c>
       <x:c r="F22" s="16" t="n">
         <x:v>0.433333333333333</x:v>
       </x:c>
-      <x:c r="G22" s="17" t="n">
+      <x:c r="G22" s="18" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H22" s="18" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I22" s="16" t="n">
+      <x:c r="I22" s="8" t="n">
         <x:v>5.96214051333333</x:v>
       </x:c>
-      <x:c r="J22" s="20" t="n">
+      <x:c r="J22" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="K22" s="21" t="str"/>
+      <x:c r="K22" s="16" t="str"/>
       <x:c r="L22" s="16" t="n">
         <x:v>0.966666666666667</x:v>
       </x:c>
@@ -3446,7 +3610,7 @@
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
-      <x:c r="A23" s="17" t="n">
+      <x:c r="A23" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B23" s="8" t="str">
@@ -3458,25 +3622,25 @@
       <x:c r="D23" s="19" t="n">
         <x:v>421.846106869853</x:v>
       </x:c>
-      <x:c r="E23" s="15" t="str">
+      <x:c r="E23" s="19" t="str">
         <x:v>1668.4042 +/- 421.8461</x:v>
       </x:c>
       <x:c r="F23" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="17" t="n">
+      <x:c r="G23" s="18" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="H23" s="18" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="I23" s="16" t="n">
+      <x:c r="I23" s="8" t="n">
         <x:v>5.25174961</x:v>
       </x:c>
-      <x:c r="J23" s="20" t="n">
+      <x:c r="J23" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="K23" s="21" t="str"/>
+      <x:c r="K23" s="16" t="str"/>
       <x:c r="L23" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -3494,58 +3658,58 @@
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
-      <x:c r="A24" s="32" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B24" s="29" t="str">
+      <x:c r="A24" s="147" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B24" s="147" t="str">
         <x:v>CVF-AE</x:v>
       </x:c>
-      <x:c r="C24" s="37" t="n">
+      <x:c r="C24" s="148" t="n">
         <x:v>349.227029913288</x:v>
       </x:c>
-      <x:c r="D24" s="37" t="n">
+      <x:c r="D24" s="148" t="n">
         <x:v>19.8953883191019</x:v>
       </x:c>
-      <x:c r="E24" s="30" t="str">
+      <x:c r="E24" s="148" t="str">
         <x:v>349.2270 +/- 19.8954</x:v>
       </x:c>
-      <x:c r="F24" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G24" s="32" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="H24" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
+      <x:c r="F24" s="149" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G24" s="150" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="H24" s="150" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="I24" s="147" t="n">
         <x:v>7.81631366</x:v>
       </x:c>
-      <x:c r="J24" s="38" t="n">
+      <x:c r="J24" s="147" t="n">
         <x:v>9355.2</x:v>
       </x:c>
-      <x:c r="K24" s="39" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
+      <x:c r="K24" s="149" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L24" s="149" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="M24" s="31" t="n">
+      <x:c r="M24" s="149" t="n">
         <x:v>0.000909090909090909</x:v>
       </x:c>
-      <x:c r="N24" s="31" t="n">
+      <x:c r="N24" s="149" t="n">
         <x:v>0.24891122278057</x:v>
       </x:c>
-      <x:c r="O24" s="37" t="n">
+      <x:c r="O24" s="148" t="n">
         <x:v>1.22963383476046</x:v>
       </x:c>
-      <x:c r="P24" s="29" t="str">
+      <x:c r="P24" s="147" t="str">
         <x:v>formal-main</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
-      <x:c r="A25" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A25" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B25" s="8" t="str">
         <x:v>CPO</x:v>
@@ -3556,25 +3720,25 @@
       <x:c r="D25" s="19" t="n">
         <x:v>313.206082734113</x:v>
       </x:c>
-      <x:c r="E25" s="15" t="str">
+      <x:c r="E25" s="19" t="str">
         <x:v>519.8797 +/- 313.2061</x:v>
       </x:c>
       <x:c r="F25" s="16" t="n">
         <x:v>0.733333333333333</x:v>
       </x:c>
-      <x:c r="G25" s="17" t="n">
+      <x:c r="G25" s="18" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="H25" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I25" s="16" t="n">
+      <x:c r="I25" s="8" t="n">
         <x:v>5.56996168</x:v>
       </x:c>
-      <x:c r="J25" s="20" t="n">
+      <x:c r="J25" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="K25" s="21" t="str"/>
+      <x:c r="K25" s="16" t="str"/>
       <x:c r="L25" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -3592,8 +3756,8 @@
       </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
-      <x:c r="A26" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A26" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B26" s="8" t="str">
         <x:v>GDSAO</x:v>
@@ -3604,25 +3768,25 @@
       <x:c r="D26" s="19" t="n">
         <x:v>3.81752402471026</x:v>
       </x:c>
-      <x:c r="E26" s="15" t="str">
+      <x:c r="E26" s="19" t="str">
         <x:v>346.8474 +/- 3.8175</x:v>
       </x:c>
       <x:c r="F26" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G26" s="17" t="n">
+      <x:c r="G26" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H26" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I26" s="16" t="n">
+      <x:c r="I26" s="8" t="n">
         <x:v>11.3887188766667</x:v>
       </x:c>
-      <x:c r="J26" s="20" t="n">
+      <x:c r="J26" s="8" t="n">
         <x:v>17955</x:v>
       </x:c>
-      <x:c r="K26" s="21" t="str"/>
+      <x:c r="K26" s="16" t="str"/>
       <x:c r="L26" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -3640,8 +3804,8 @@
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
-      <x:c r="A27" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A27" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B27" s="8" t="str">
         <x:v>MSCSO</x:v>
@@ -3652,25 +3816,25 @@
       <x:c r="D27" s="19" t="n">
         <x:v>189.022943849173</x:v>
       </x:c>
-      <x:c r="E27" s="15" t="str">
+      <x:c r="E27" s="19" t="str">
         <x:v>402.2712 +/- 189.0229</x:v>
       </x:c>
       <x:c r="F27" s="16" t="n">
         <x:v>0.933333333333333</x:v>
       </x:c>
-      <x:c r="G27" s="17" t="n">
+      <x:c r="G27" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H27" s="18" t="n">
         <x:v>3.33333333333333</x:v>
       </x:c>
-      <x:c r="I27" s="16" t="n">
+      <x:c r="I27" s="8" t="n">
         <x:v>15.3013203933333</x:v>
       </x:c>
-      <x:c r="J27" s="20" t="n">
+      <x:c r="J27" s="8" t="n">
         <x:v>21444.7666666667</x:v>
       </x:c>
-      <x:c r="K27" s="21" t="str"/>
+      <x:c r="K27" s="16" t="str"/>
       <x:c r="L27" s="16" t="n">
         <x:v>0.666666666666667</x:v>
       </x:c>
@@ -3688,8 +3852,8 @@
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
-      <x:c r="A28" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A28" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B28" s="8" t="str">
         <x:v>ERIME</x:v>
@@ -3700,25 +3864,25 @@
       <x:c r="D28" s="19" t="n">
         <x:v>21.6703632105875</x:v>
       </x:c>
-      <x:c r="E28" s="15" t="str">
+      <x:c r="E28" s="19" t="str">
         <x:v>360.2347 +/- 21.6704</x:v>
       </x:c>
       <x:c r="F28" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G28" s="17" t="n">
+      <x:c r="G28" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="H28" s="18" t="n">
         <x:v>4.33333333333333</x:v>
       </x:c>
-      <x:c r="I28" s="16" t="n">
+      <x:c r="I28" s="8" t="n">
         <x:v>7.05888226666667</x:v>
       </x:c>
-      <x:c r="J28" s="20" t="n">
+      <x:c r="J28" s="8" t="n">
         <x:v>9481.8</x:v>
       </x:c>
-      <x:c r="K28" s="21" t="str"/>
+      <x:c r="K28" s="16" t="str"/>
       <x:c r="L28" s="16" t="n">
         <x:v>0.966666666666667</x:v>
       </x:c>
@@ -3736,8 +3900,8 @@
       </x:c>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
-      <x:c r="A29" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A29" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B29" s="8" t="str">
         <x:v>DBO</x:v>
@@ -3748,25 +3912,25 @@
       <x:c r="D29" s="19" t="n">
         <x:v>15.9951175210005</x:v>
       </x:c>
-      <x:c r="E29" s="15" t="str">
+      <x:c r="E29" s="19" t="str">
         <x:v>376.3041 +/- 15.9951</x:v>
       </x:c>
       <x:c r="F29" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G29" s="17" t="n">
+      <x:c r="G29" s="18" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="H29" s="18" t="n">
         <x:v>5.33333333333333</x:v>
       </x:c>
-      <x:c r="I29" s="16" t="n">
+      <x:c r="I29" s="8" t="n">
         <x:v>5.80182613</x:v>
       </x:c>
-      <x:c r="J29" s="20" t="n">
+      <x:c r="J29" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="K29" s="21" t="str"/>
+      <x:c r="K29" s="16" t="str"/>
       <x:c r="L29" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -3784,8 +3948,8 @@
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
-      <x:c r="A30" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A30" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B30" s="8" t="str">
         <x:v>GWO</x:v>
@@ -3796,25 +3960,25 @@
       <x:c r="D30" s="19" t="n">
         <x:v>333.179590508335</x:v>
       </x:c>
-      <x:c r="E30" s="15" t="str">
+      <x:c r="E30" s="19" t="str">
         <x:v>608.4571 +/- 333.1796</x:v>
       </x:c>
       <x:c r="F30" s="16" t="n">
         <x:v>0.633333333333333</x:v>
       </x:c>
-      <x:c r="G30" s="17" t="n">
+      <x:c r="G30" s="18" t="n">
         <x:v>7</x:v>
       </x:c>
       <x:c r="H30" s="18" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="I30" s="16" t="n">
+      <x:c r="I30" s="8" t="n">
         <x:v>5.95338771333333</x:v>
       </x:c>
-      <x:c r="J30" s="20" t="n">
+      <x:c r="J30" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="K30" s="21" t="str"/>
+      <x:c r="K30" s="16" t="str"/>
       <x:c r="L30" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -3832,8 +3996,8 @@
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
-      <x:c r="A31" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A31" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B31" s="8" t="str">
         <x:v>HHO</x:v>
@@ -3844,25 +4008,25 @@
       <x:c r="D31" s="19" t="n">
         <x:v>469.467061570051</x:v>
       </x:c>
-      <x:c r="E31" s="15" t="str">
+      <x:c r="E31" s="19" t="str">
         <x:v>898.3440 +/- 469.4671</x:v>
       </x:c>
       <x:c r="F31" s="16" t="n">
         <x:v>0.366666666666667</x:v>
       </x:c>
-      <x:c r="G31" s="17" t="n">
+      <x:c r="G31" s="18" t="n">
         <x:v>8</x:v>
       </x:c>
       <x:c r="H31" s="18" t="n">
         <x:v>8.33333333333333</x:v>
       </x:c>
-      <x:c r="I31" s="16" t="n">
+      <x:c r="I31" s="8" t="n">
         <x:v>7.51364364333333</x:v>
       </x:c>
-      <x:c r="J31" s="20" t="n">
+      <x:c r="J31" s="8" t="n">
         <x:v>11474.9666666667</x:v>
       </x:c>
-      <x:c r="K31" s="21" t="str"/>
+      <x:c r="K31" s="16" t="str"/>
       <x:c r="L31" s="16" t="n">
         <x:v>0.966666666666667</x:v>
       </x:c>
@@ -3880,8 +4044,8 @@
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
-      <x:c r="A32" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A32" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B32" s="8" t="str">
         <x:v>PSO</x:v>
@@ -3892,25 +4056,25 @@
       <x:c r="D32" s="19" t="n">
         <x:v>382.020606804982</x:v>
       </x:c>
-      <x:c r="E32" s="15" t="str">
+      <x:c r="E32" s="19" t="str">
         <x:v>1295.4587 +/- 382.0206</x:v>
       </x:c>
       <x:c r="F32" s="16" t="n">
         <x:v>0.0333333333333333</x:v>
       </x:c>
-      <x:c r="G32" s="17" t="n">
+      <x:c r="G32" s="18" t="n">
         <x:v>9</x:v>
       </x:c>
       <x:c r="H32" s="18" t="n">
         <x:v>8.66666666666667</x:v>
       </x:c>
-      <x:c r="I32" s="16" t="n">
+      <x:c r="I32" s="8" t="n">
         <x:v>5.54881991333333</x:v>
       </x:c>
-      <x:c r="J32" s="20" t="n">
+      <x:c r="J32" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="K32" s="21" t="str"/>
+      <x:c r="K32" s="16" t="str"/>
       <x:c r="L32" s="16" t="n">
         <x:v>0.1</x:v>
       </x:c>
@@ -3928,8 +4092,8 @@
       </x:c>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
-      <x:c r="A33" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A33" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B33" s="8" t="str">
         <x:v>WOA</x:v>
@@ -3940,25 +4104,25 @@
       <x:c r="D33" s="19" t="n">
         <x:v>426.39000079659</x:v>
       </x:c>
-      <x:c r="E33" s="15" t="str">
+      <x:c r="E33" s="19" t="str">
         <x:v>1485.6743 +/- 426.3900</x:v>
       </x:c>
       <x:c r="F33" s="16" t="n">
         <x:v>0.0666666666666667</x:v>
       </x:c>
-      <x:c r="G33" s="17" t="n">
+      <x:c r="G33" s="18" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="H33" s="18" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I33" s="16" t="n">
+      <x:c r="I33" s="8" t="n">
         <x:v>5.52293523666667</x:v>
       </x:c>
-      <x:c r="J33" s="20" t="n">
+      <x:c r="J33" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="K33" s="21" t="str"/>
+      <x:c r="K33" s="16" t="str"/>
       <x:c r="L33" s="16" t="n">
         <x:v>0.866666666666667</x:v>
       </x:c>
@@ -3976,8 +4140,8 @@
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
-      <x:c r="A34" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A34" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B34" s="8" t="str">
         <x:v>AE</x:v>
@@ -3988,25 +4152,25 @@
       <x:c r="D34" s="19" t="n">
         <x:v>200.900207932275</x:v>
       </x:c>
-      <x:c r="E34" s="15" t="str">
+      <x:c r="E34" s="19" t="str">
         <x:v>1653.2705 +/- 200.9002</x:v>
       </x:c>
       <x:c r="F34" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G34" s="17" t="n">
+      <x:c r="G34" s="18" t="n">
         <x:v>11</x:v>
       </x:c>
       <x:c r="H34" s="18" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="I34" s="16" t="n">
+      <x:c r="I34" s="8" t="n">
         <x:v>6.51338697666667</x:v>
       </x:c>
-      <x:c r="J34" s="20" t="n">
+      <x:c r="J34" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="K34" s="21" t="str"/>
+      <x:c r="K34" s="16" t="str"/>
       <x:c r="L34" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4026,7 +4190,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a7083109098478d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R773ea0da058546f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4035,60 +4199,60 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11.880000114440918" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="11.75" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="11" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="11" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="11" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="11" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="11" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="13" t="str">
+      <x:c r="A1" s="142" t="str">
         <x:v>Scene</x:v>
       </x:c>
-      <x:c r="B1" s="13" t="str">
+      <x:c r="B1" s="142" t="str">
         <x:v>ComparedMethod</x:v>
       </x:c>
-      <x:c r="C1" s="13" t="str">
+      <x:c r="C1" s="142" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="D1" s="13" t="str">
+      <x:c r="D1" s="142" t="str">
         <x:v>CVFAEMean</x:v>
       </x:c>
-      <x:c r="E1" s="13" t="str">
+      <x:c r="E1" s="142" t="str">
         <x:v>ComparedMean</x:v>
       </x:c>
-      <x:c r="F1" s="13" t="str">
+      <x:c r="F1" s="142" t="str">
         <x:v>RawP</x:v>
       </x:c>
-      <x:c r="G1" s="13" t="str">
+      <x:c r="G1" s="142" t="str">
         <x:v>SceneHolmP</x:v>
       </x:c>
-      <x:c r="H1" s="13" t="str">
+      <x:c r="H1" s="142" t="str">
         <x:v>Result</x:v>
       </x:c>
-      <x:c r="I1" s="13" t="str">
-        <x:v>Cliff's Delta</x:v>
-      </x:c>
-      <x:c r="J1" s="13" t="str">
+      <x:c r="I1" s="142" t="str">
+        <x:v>CliffsDelta</x:v>
+      </x:c>
+      <x:c r="J1" s="142" t="str">
         <x:v>EffectMagnitude</x:v>
       </x:c>
-      <x:c r="K1" s="13" t="str">
+      <x:c r="K1" s="142" t="str">
         <x:v>GlobalHolmP</x:v>
       </x:c>
-      <x:c r="L1" s="13" t="str">
+      <x:c r="L1" s="142" t="str">
         <x:v>GlobalResult</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="17" t="n">
+      <x:c r="A2" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="8" t="str">
@@ -4109,7 +4273,7 @@
       <x:c r="G2" s="22" t="n">
         <x:v>3.01985935916215e-10</x:v>
       </x:c>
-      <x:c r="H2" s="56" t="str">
+      <x:c r="H2" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I2" s="19" t="n">
@@ -4126,7 +4290,7 @@
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="17" t="n">
+      <x:c r="A3" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="8" t="str">
@@ -4147,7 +4311,7 @@
       <x:c r="G3" s="22" t="n">
         <x:v>1.95832093724871e-7</x:v>
       </x:c>
-      <x:c r="H3" s="56" t="str">
+      <x:c r="H3" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I3" s="19" t="n">
@@ -4164,7 +4328,7 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
-      <x:c r="A4" s="17" t="n">
+      <x:c r="A4" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="8" t="str">
@@ -4185,7 +4349,7 @@
       <x:c r="G4" s="22" t="n">
         <x:v>3.01985935916215e-10</x:v>
       </x:c>
-      <x:c r="H4" s="56" t="str">
+      <x:c r="H4" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I4" s="19" t="n">
@@ -4202,7 +4366,7 @@
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="17" t="n">
+      <x:c r="A5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="8" t="str">
@@ -4223,7 +4387,7 @@
       <x:c r="G5" s="22" t="n">
         <x:v>3.01985935916215e-10</x:v>
       </x:c>
-      <x:c r="H5" s="56" t="str">
+      <x:c r="H5" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I5" s="19" t="n">
@@ -4240,7 +4404,7 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="17" t="n">
+      <x:c r="A6" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="8" t="str">
@@ -4261,7 +4425,7 @@
       <x:c r="G6" s="22" t="n">
         <x:v>1.04394111518234e-9</x:v>
       </x:c>
-      <x:c r="H6" s="56" t="str">
+      <x:c r="H6" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I6" s="19" t="n">
@@ -4278,7 +4442,7 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="17" t="n">
+      <x:c r="A7" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B7" s="8" t="str">
@@ -4299,7 +4463,7 @@
       <x:c r="G7" s="22" t="n">
         <x:v>3.01985935916215e-10</x:v>
       </x:c>
-      <x:c r="H7" s="56" t="str">
+      <x:c r="H7" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I7" s="19" t="n">
@@ -4316,7 +4480,7 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="17" t="n">
+      <x:c r="A8" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B8" s="8" t="str">
@@ -4337,7 +4501,7 @@
       <x:c r="G8" s="22" t="n">
         <x:v>0.773119942467523</x:v>
       </x:c>
-      <x:c r="H8" s="57" t="str">
+      <x:c r="H8" s="154" t="str">
         <x:v>=</x:v>
       </x:c>
       <x:c r="I8" s="19" t="n">
@@ -4354,7 +4518,7 @@
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="17" t="n">
+      <x:c r="A9" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="8" t="str">
@@ -4375,7 +4539,7 @@
       <x:c r="G9" s="22" t="n">
         <x:v>5.46834781554953e-10</x:v>
       </x:c>
-      <x:c r="H9" s="56" t="str">
+      <x:c r="H9" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I9" s="19" t="n">
@@ -4392,7 +4556,7 @@
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="17" t="n">
+      <x:c r="A10" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B10" s="8" t="str">
@@ -4413,7 +4577,7 @@
       <x:c r="G10" s="22" t="n">
         <x:v>4.01731137930011e-10</x:v>
       </x:c>
-      <x:c r="H10" s="56" t="str">
+      <x:c r="H10" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I10" s="19" t="n">
@@ -4430,7 +4594,7 @@
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
-      <x:c r="A11" s="17" t="n">
+      <x:c r="A11" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B11" s="8" t="str">
@@ -4451,7 +4615,7 @@
       <x:c r="G11" s="22" t="n">
         <x:v>4.75364010090902e-7</x:v>
       </x:c>
-      <x:c r="H11" s="56" t="str">
+      <x:c r="H11" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I11" s="19" t="n">
@@ -4468,7 +4632,7 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
-      <x:c r="A12" s="17" t="n">
+      <x:c r="A12" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B12" s="8" t="str">
@@ -4489,7 +4653,7 @@
       <x:c r="G12" s="22" t="n">
         <x:v>3.01985935916215e-10</x:v>
       </x:c>
-      <x:c r="H12" s="56" t="str">
+      <x:c r="H12" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I12" s="19" t="n">
@@ -4506,7 +4670,7 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
-      <x:c r="A13" s="17" t="n">
+      <x:c r="A13" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B13" s="8" t="str">
@@ -4527,7 +4691,7 @@
       <x:c r="G13" s="22" t="n">
         <x:v>0.000552676127622991</x:v>
       </x:c>
-      <x:c r="H13" s="56" t="str">
+      <x:c r="H13" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I13" s="19" t="n">
@@ -4544,7 +4708,7 @@
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
-      <x:c r="A14" s="17" t="n">
+      <x:c r="A14" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B14" s="8" t="str">
@@ -4565,7 +4729,7 @@
       <x:c r="G14" s="22" t="n">
         <x:v>0.00119424228534853</x:v>
       </x:c>
-      <x:c r="H14" s="56" t="str">
+      <x:c r="H14" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I14" s="19" t="n">
@@ -4582,7 +4746,7 @@
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
-      <x:c r="A15" s="17" t="n">
+      <x:c r="A15" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B15" s="8" t="str">
@@ -4603,7 +4767,7 @@
       <x:c r="G15" s="22" t="n">
         <x:v>3.01985935916215e-10</x:v>
       </x:c>
-      <x:c r="H15" s="56" t="str">
+      <x:c r="H15" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I15" s="19" t="n">
@@ -4620,7 +4784,7 @@
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
-      <x:c r="A16" s="17" t="n">
+      <x:c r="A16" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B16" s="8" t="str">
@@ -4641,7 +4805,7 @@
       <x:c r="G16" s="22" t="n">
         <x:v>0.00119424228534853</x:v>
       </x:c>
-      <x:c r="H16" s="56" t="str">
+      <x:c r="H16" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I16" s="19" t="n">
@@ -4658,7 +4822,7 @@
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
-      <x:c r="A17" s="17" t="n">
+      <x:c r="A17" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B17" s="8" t="str">
@@ -4679,7 +4843,7 @@
       <x:c r="G17" s="22" t="n">
         <x:v>0.00000153711987276549</x:v>
       </x:c>
-      <x:c r="H17" s="56" t="str">
+      <x:c r="H17" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I17" s="19" t="n">
@@ -4696,7 +4860,7 @@
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
-      <x:c r="A18" s="17" t="n">
+      <x:c r="A18" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B18" s="8" t="str">
@@ -4717,7 +4881,7 @@
       <x:c r="G18" s="22" t="n">
         <x:v>3.01985935916215e-10</x:v>
       </x:c>
-      <x:c r="H18" s="60" t="str">
+      <x:c r="H18" s="156" t="str">
         <x:v>-</x:v>
       </x:c>
       <x:c r="I18" s="19" t="n">
@@ -4734,7 +4898,7 @@
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
-      <x:c r="A19" s="17" t="n">
+      <x:c r="A19" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B19" s="8" t="str">
@@ -4755,7 +4919,7 @@
       <x:c r="G19" s="22" t="n">
         <x:v>0.620403720627753</x:v>
       </x:c>
-      <x:c r="H19" s="57" t="str">
+      <x:c r="H19" s="154" t="str">
         <x:v>=</x:v>
       </x:c>
       <x:c r="I19" s="19" t="n">
@@ -4772,7 +4936,7 @@
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
-      <x:c r="A20" s="17" t="n">
+      <x:c r="A20" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B20" s="8" t="str">
@@ -4793,7 +4957,7 @@
       <x:c r="G20" s="22" t="n">
         <x:v>0.594543378178614</x:v>
       </x:c>
-      <x:c r="H20" s="57" t="str">
+      <x:c r="H20" s="154" t="str">
         <x:v>=</x:v>
       </x:c>
       <x:c r="I20" s="19" t="n">
@@ -4810,7 +4974,7 @@
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
-      <x:c r="A21" s="17" t="n">
+      <x:c r="A21" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B21" s="8" t="str">
@@ -4831,7 +4995,7 @@
       <x:c r="G21" s="22" t="n">
         <x:v>0.00196459385056385</x:v>
       </x:c>
-      <x:c r="H21" s="60" t="str">
+      <x:c r="H21" s="156" t="str">
         <x:v>-</x:v>
       </x:c>
       <x:c r="I21" s="19" t="n">
@@ -4848,8 +5012,8 @@
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
-      <x:c r="A22" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A22" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B22" s="8" t="str">
         <x:v>AE</x:v>
@@ -4869,7 +5033,7 @@
       <x:c r="G22" s="22" t="n">
         <x:v>3.01985935916215e-10</x:v>
       </x:c>
-      <x:c r="H22" s="56" t="str">
+      <x:c r="H22" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I22" s="19" t="n">
@@ -4886,8 +5050,8 @@
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
-      <x:c r="A23" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A23" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B23" s="8" t="str">
         <x:v>PSO</x:v>
@@ -4907,7 +5071,7 @@
       <x:c r="G23" s="22" t="n">
         <x:v>3.01985935916215e-10</x:v>
       </x:c>
-      <x:c r="H23" s="56" t="str">
+      <x:c r="H23" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I23" s="19" t="n">
@@ -4924,8 +5088,8 @@
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
-      <x:c r="A24" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A24" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B24" s="8" t="str">
         <x:v>GWO</x:v>
@@ -4945,7 +5109,7 @@
       <x:c r="G24" s="22" t="n">
         <x:v>0.0000214248052727498</x:v>
       </x:c>
-      <x:c r="H24" s="56" t="str">
+      <x:c r="H24" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I24" s="19" t="n">
@@ -4962,8 +5126,8 @@
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
-      <x:c r="A25" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A25" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B25" s="8" t="str">
         <x:v>WOA</x:v>
@@ -4983,7 +5147,7 @@
       <x:c r="G25" s="22" t="n">
         <x:v>3.01985935916215e-10</x:v>
       </x:c>
-      <x:c r="H25" s="56" t="str">
+      <x:c r="H25" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I25" s="19" t="n">
@@ -5000,8 +5164,8 @@
       </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
-      <x:c r="A26" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A26" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B26" s="8" t="str">
         <x:v>HHO</x:v>
@@ -5021,7 +5185,7 @@
       <x:c r="G26" s="22" t="n">
         <x:v>5.93934103010363e-8</x:v>
       </x:c>
-      <x:c r="H26" s="56" t="str">
+      <x:c r="H26" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I26" s="19" t="n">
@@ -5038,8 +5202,8 @@
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
-      <x:c r="A27" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A27" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B27" s="8" t="str">
         <x:v>DBO</x:v>
@@ -5059,7 +5223,7 @@
       <x:c r="G27" s="22" t="n">
         <x:v>0.0000509384467621355</x:v>
       </x:c>
-      <x:c r="H27" s="56" t="str">
+      <x:c r="H27" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I27" s="19" t="n">
@@ -5076,8 +5240,8 @@
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
-      <x:c r="A28" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A28" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B28" s="8" t="str">
         <x:v>CPO</x:v>
@@ -5097,7 +5261,7 @@
       <x:c r="G28" s="22" t="n">
         <x:v>0.933562930230825</x:v>
       </x:c>
-      <x:c r="H28" s="57" t="str">
+      <x:c r="H28" s="154" t="str">
         <x:v>=</x:v>
       </x:c>
       <x:c r="I28" s="19" t="n">
@@ -5114,8 +5278,8 @@
       </x:c>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
-      <x:c r="A29" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A29" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B29" s="8" t="str">
         <x:v>GDSAO</x:v>
@@ -5135,7 +5299,7 @@
       <x:c r="G29" s="22" t="n">
         <x:v>0.933562930230825</x:v>
       </x:c>
-      <x:c r="H29" s="57" t="str">
+      <x:c r="H29" s="154" t="str">
         <x:v>=</x:v>
       </x:c>
       <x:c r="I29" s="19" t="n">
@@ -5152,8 +5316,8 @@
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
-      <x:c r="A30" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A30" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B30" s="8" t="str">
         <x:v>ERIME</x:v>
@@ -5173,7 +5337,7 @@
       <x:c r="G30" s="22" t="n">
         <x:v>0.0966275385712506</x:v>
       </x:c>
-      <x:c r="H30" s="57" t="str">
+      <x:c r="H30" s="154" t="str">
         <x:v>=</x:v>
       </x:c>
       <x:c r="I30" s="19" t="n">
@@ -5190,8 +5354,8 @@
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
-      <x:c r="A31" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A31" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B31" s="8" t="str">
         <x:v>MSCSO</x:v>
@@ -5211,7 +5375,7 @@
       <x:c r="G31" s="22" t="n">
         <x:v>0.933562930230825</x:v>
       </x:c>
-      <x:c r="H31" s="57" t="str">
+      <x:c r="H31" s="154" t="str">
         <x:v>=</x:v>
       </x:c>
       <x:c r="I31" s="19" t="n">
@@ -5230,7 +5394,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf715fa9ccb824558"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc64565cea2da4d36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5239,112 +5403,112 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="28" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="11" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="11" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="12.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="11" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="22" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="11" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="12.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="12.5" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="13" t="str">
+      <x:c r="A1" s="142" t="str">
         <x:v>Scene</x:v>
       </x:c>
-      <x:c r="B1" s="13" t="str">
+      <x:c r="B1" s="142" t="str">
         <x:v>Variant</x:v>
       </x:c>
-      <x:c r="C1" s="13" t="str">
+      <x:c r="C1" s="142" t="str">
         <x:v>MeanFitness</x:v>
       </x:c>
-      <x:c r="D1" s="13" t="str">
+      <x:c r="D1" s="142" t="str">
         <x:v>StdFitness</x:v>
       </x:c>
-      <x:c r="E1" s="13" t="str">
+      <x:c r="E1" s="142" t="str">
         <x:v>Mean +/- Std</x:v>
       </x:c>
-      <x:c r="F1" s="13" t="str">
+      <x:c r="F1" s="142" t="str">
         <x:v>FeasibleRate</x:v>
       </x:c>
-      <x:c r="G1" s="13" t="str">
+      <x:c r="G1" s="142" t="str">
         <x:v>SceneRank</x:v>
       </x:c>
-      <x:c r="H1" s="13" t="str">
+      <x:c r="H1" s="142" t="str">
         <x:v>AverageRank</x:v>
       </x:c>
-      <x:c r="I1" s="13" t="str">
+      <x:c r="I1" s="142" t="str">
         <x:v>RuntimeSeconds</x:v>
       </x:c>
-      <x:c r="J1" s="13" t="str">
+      <x:c r="J1" s="142" t="str">
         <x:v>NEvals</x:v>
       </x:c>
-      <x:c r="K1" s="13" t="str">
+      <x:c r="K1" s="142" t="str">
         <x:v>First Feasible Iter</x:v>
       </x:c>
-      <x:c r="L1" s="13" t="str">
+      <x:c r="L1" s="142" t="str">
         <x:v>RepairCount</x:v>
       </x:c>
-      <x:c r="M1" s="13" t="str">
+      <x:c r="M1" s="142" t="str">
         <x:v>CVFTriggerCount</x:v>
       </x:c>
-      <x:c r="N1" s="13" t="str">
+      <x:c r="N1" s="142" t="str">
         <x:v>CVFSuccessCount</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="32" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="29" t="str">
+      <x:c r="A2" s="147" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="147" t="str">
         <x:v>CVF-AE</x:v>
       </x:c>
-      <x:c r="C2" s="37" t="n">
+      <x:c r="C2" s="148" t="n">
         <x:v>297.831801364604</x:v>
       </x:c>
-      <x:c r="D2" s="37" t="n">
+      <x:c r="D2" s="148" t="n">
         <x:v>3.11190201143395</x:v>
       </x:c>
-      <x:c r="E2" s="30" t="str">
+      <x:c r="E2" s="148" t="str">
         <x:v>297.8318 +/- 3.1119</x:v>
       </x:c>
-      <x:c r="F2" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G2" s="32" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
+      <x:c r="F2" s="149" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G2" s="150" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H2" s="150" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I2" s="147" t="n">
         <x:v>27.4089501233333</x:v>
       </x:c>
-      <x:c r="J2" s="38" t="n">
+      <x:c r="J2" s="147" t="n">
         <x:v>9566.36666666667</x:v>
       </x:c>
-      <x:c r="K2" s="39" t="n">
+      <x:c r="K2" s="149" t="n">
         <x:v>1.93333333333333</x:v>
       </x:c>
-      <x:c r="L2" s="31" t="n">
+      <x:c r="L2" s="147" t="n">
         <x:v>515.233333333333</x:v>
       </x:c>
-      <x:c r="M2" s="31" t="n">
+      <x:c r="M2" s="147" t="n">
         <x:v>21.1333333333333</x:v>
       </x:c>
-      <x:c r="N2" s="31" t="n">
+      <x:c r="N2" s="147" t="n">
         <x:v>19.1666666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="17" t="n">
+      <x:c r="A3" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="8" t="str">
@@ -5356,39 +5520,39 @@
       <x:c r="D3" s="19" t="n">
         <x:v>3.49173789624349</x:v>
       </x:c>
-      <x:c r="E3" s="15" t="str">
+      <x:c r="E3" s="19" t="str">
         <x:v>306.1985 +/- 3.4917</x:v>
       </x:c>
       <x:c r="F3" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G3" s="17" t="n">
+      <x:c r="G3" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="H3" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I3" s="16" t="n">
+      <x:c r="I3" s="8" t="n">
         <x:v>25.6912313233333</x:v>
       </x:c>
-      <x:c r="J3" s="20" t="n">
+      <x:c r="J3" s="8" t="n">
         <x:v>9471.83333333333</x:v>
       </x:c>
-      <x:c r="K3" s="21" t="n">
+      <x:c r="K3" s="16" t="n">
         <x:v>1.46666666666667</x:v>
       </x:c>
-      <x:c r="L3" s="16" t="n">
+      <x:c r="L3" s="8" t="n">
         <x:v>441.833333333333</x:v>
       </x:c>
-      <x:c r="M3" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="16" t="n">
+      <x:c r="M3" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N3" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
-      <x:c r="A4" s="17" t="n">
+      <x:c r="A4" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="8" t="str">
@@ -5400,39 +5564,39 @@
       <x:c r="D4" s="19" t="n">
         <x:v>3.21609369562628</x:v>
       </x:c>
-      <x:c r="E4" s="15" t="str">
+      <x:c r="E4" s="19" t="str">
         <x:v>298.3037 +/- 3.2161</x:v>
       </x:c>
       <x:c r="F4" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G4" s="17" t="n">
+      <x:c r="G4" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="H4" s="18" t="n">
         <x:v>2.33333333333333</x:v>
       </x:c>
-      <x:c r="I4" s="16" t="n">
+      <x:c r="I4" s="8" t="n">
         <x:v>24.53378375</x:v>
       </x:c>
-      <x:c r="J4" s="20" t="n">
+      <x:c r="J4" s="8" t="n">
         <x:v>9565.96666666667</x:v>
       </x:c>
-      <x:c r="K4" s="21" t="n">
+      <x:c r="K4" s="16" t="n">
         <x:v>1.73333333333333</x:v>
       </x:c>
-      <x:c r="L4" s="16" t="n">
+      <x:c r="L4" s="8" t="n">
         <x:v>515.333333333333</x:v>
       </x:c>
-      <x:c r="M4" s="16" t="n">
+      <x:c r="M4" s="8" t="n">
         <x:v>20.6333333333333</x:v>
       </x:c>
-      <x:c r="N4" s="16" t="n">
+      <x:c r="N4" s="8" t="n">
         <x:v>19.6666666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="17" t="n">
+      <x:c r="A5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="8" t="str">
@@ -5444,39 +5608,39 @@
       <x:c r="D5" s="19" t="n">
         <x:v>4.99731706294944</x:v>
       </x:c>
-      <x:c r="E5" s="15" t="str">
+      <x:c r="E5" s="19" t="str">
         <x:v>306.3793 +/- 4.9973</x:v>
       </x:c>
       <x:c r="F5" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G5" s="17" t="n">
+      <x:c r="G5" s="18" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="H5" s="18" t="n">
         <x:v>3.66666666666667</x:v>
       </x:c>
-      <x:c r="I5" s="16" t="n">
+      <x:c r="I5" s="8" t="n">
         <x:v>20.64546617</x:v>
       </x:c>
-      <x:c r="J5" s="20" t="n">
+      <x:c r="J5" s="8" t="n">
         <x:v>9140.13333333333</x:v>
       </x:c>
-      <x:c r="K5" s="21" t="n">
+      <x:c r="K5" s="16" t="n">
         <x:v>6.2</x:v>
       </x:c>
-      <x:c r="L5" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M5" s="16" t="n">
+      <x:c r="L5" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M5" s="8" t="n">
         <x:v>110.133333333333</x:v>
       </x:c>
-      <x:c r="N5" s="16" t="n">
+      <x:c r="N5" s="8" t="n">
         <x:v>90.6666666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="17" t="n">
+      <x:c r="A6" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="8" t="str">
@@ -5488,39 +5652,39 @@
       <x:c r="D6" s="19" t="n">
         <x:v>11.8480573502927</x:v>
       </x:c>
-      <x:c r="E6" s="15" t="str">
+      <x:c r="E6" s="19" t="str">
         <x:v>316.9964 +/- 11.8481</x:v>
       </x:c>
       <x:c r="F6" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G6" s="17" t="n">
+      <x:c r="G6" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H6" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I6" s="16" t="n">
+      <x:c r="I6" s="8" t="n">
         <x:v>5.78709746</x:v>
       </x:c>
-      <x:c r="J6" s="20" t="n">
+      <x:c r="J6" s="8" t="n">
         <x:v>9587.56666666667</x:v>
       </x:c>
-      <x:c r="K6" s="21" t="n">
+      <x:c r="K6" s="16" t="n">
         <x:v>21.1333333333333</x:v>
       </x:c>
-      <x:c r="L6" s="16" t="n">
+      <x:c r="L6" s="8" t="n">
         <x:v>417.333333333333</x:v>
       </x:c>
-      <x:c r="M6" s="16" t="n">
+      <x:c r="M6" s="8" t="n">
         <x:v>140.233333333333</x:v>
       </x:c>
-      <x:c r="N6" s="16" t="n">
+      <x:c r="N6" s="8" t="n">
         <x:v>93.0666666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="17" t="n">
+      <x:c r="A7" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B7" s="8" t="str">
@@ -5532,79 +5696,79 @@
       <x:c r="D7" s="19" t="n">
         <x:v>328.714214134176</x:v>
       </x:c>
-      <x:c r="E7" s="15" t="str">
+      <x:c r="E7" s="19" t="str">
         <x:v>654.0475 +/- 328.7142</x:v>
       </x:c>
       <x:c r="F7" s="16" t="n">
         <x:v>0.633333333333333</x:v>
       </x:c>
-      <x:c r="G7" s="17" t="n">
+      <x:c r="G7" s="18" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="H7" s="18" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I7" s="16" t="n">
+      <x:c r="I7" s="8" t="n">
         <x:v>4.37732100666667</x:v>
       </x:c>
-      <x:c r="J7" s="20" t="n">
+      <x:c r="J7" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="K7" s="21" t="str"/>
-      <x:c r="L7" s="16" t="str"/>
-      <x:c r="M7" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="16" t="n">
+      <x:c r="K7" s="16" t="str"/>
+      <x:c r="L7" s="8" t="str"/>
+      <x:c r="M7" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N7" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="32" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B8" s="29" t="str">
+      <x:c r="A8" s="147" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B8" s="147" t="str">
         <x:v>CVF-AE</x:v>
       </x:c>
-      <x:c r="C8" s="37" t="n">
+      <x:c r="C8" s="148" t="n">
         <x:v>300.661217364572</x:v>
       </x:c>
-      <x:c r="D8" s="37" t="n">
+      <x:c r="D8" s="148" t="n">
         <x:v>3.2775077673419</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="str">
+      <x:c r="E8" s="148" t="str">
         <x:v>300.6612 +/- 3.2775</x:v>
       </x:c>
-      <x:c r="F8" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G8" s="32" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
+      <x:c r="F8" s="149" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G8" s="150" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H8" s="150" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I8" s="147" t="n">
         <x:v>28.3060269366667</x:v>
       </x:c>
-      <x:c r="J8" s="38" t="n">
+      <x:c r="J8" s="147" t="n">
         <x:v>9551.6</x:v>
       </x:c>
-      <x:c r="K8" s="39" t="n">
+      <x:c r="K8" s="149" t="n">
         <x:v>4.6</x:v>
       </x:c>
-      <x:c r="L8" s="31" t="n">
+      <x:c r="L8" s="147" t="n">
         <x:v>511</x:v>
       </x:c>
-      <x:c r="M8" s="31" t="n">
+      <x:c r="M8" s="147" t="n">
         <x:v>10.6</x:v>
       </x:c>
-      <x:c r="N8" s="31" t="n">
+      <x:c r="N8" s="147" t="n">
         <x:v>7.9</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="17" t="n">
+      <x:c r="A9" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B9" s="8" t="str">
@@ -5616,39 +5780,39 @@
       <x:c r="D9" s="19" t="n">
         <x:v>4.95649053217946</x:v>
       </x:c>
-      <x:c r="E9" s="15" t="str">
+      <x:c r="E9" s="19" t="str">
         <x:v>303.7697 +/- 4.9565</x:v>
       </x:c>
       <x:c r="F9" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G9" s="17" t="n">
+      <x:c r="G9" s="18" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="H9" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I9" s="16" t="n">
+      <x:c r="I9" s="8" t="n">
         <x:v>25.8824157833333</x:v>
       </x:c>
-      <x:c r="J9" s="20" t="n">
+      <x:c r="J9" s="8" t="n">
         <x:v>9432.46666666667</x:v>
       </x:c>
-      <x:c r="K9" s="21" t="n">
+      <x:c r="K9" s="16" t="n">
         <x:v>5.36666666666667</x:v>
       </x:c>
-      <x:c r="L9" s="16" t="n">
+      <x:c r="L9" s="8" t="n">
         <x:v>402.466666666667</x:v>
       </x:c>
-      <x:c r="M9" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N9" s="16" t="n">
+      <x:c r="M9" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N9" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="17" t="n">
+      <x:c r="A10" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="8" t="str">
@@ -5660,39 +5824,39 @@
       <x:c r="D10" s="19" t="n">
         <x:v>2.93321887813262</x:v>
       </x:c>
-      <x:c r="E10" s="15" t="str">
+      <x:c r="E10" s="19" t="str">
         <x:v>301.8164 +/- 2.9332</x:v>
       </x:c>
       <x:c r="F10" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G10" s="17" t="n">
+      <x:c r="G10" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="H10" s="18" t="n">
         <x:v>2.33333333333333</x:v>
       </x:c>
-      <x:c r="I10" s="16" t="n">
+      <x:c r="I10" s="8" t="n">
         <x:v>28.8627510466667</x:v>
       </x:c>
-      <x:c r="J10" s="20" t="n">
+      <x:c r="J10" s="8" t="n">
         <x:v>9560.86666666667</x:v>
       </x:c>
-      <x:c r="K10" s="21" t="n">
+      <x:c r="K10" s="16" t="n">
         <x:v>10.1666666666667</x:v>
       </x:c>
-      <x:c r="L10" s="16" t="n">
+      <x:c r="L10" s="8" t="n">
         <x:v>510.433333333333</x:v>
       </x:c>
-      <x:c r="M10" s="16" t="n">
+      <x:c r="M10" s="8" t="n">
         <x:v>20.4333333333333</x:v>
       </x:c>
-      <x:c r="N10" s="16" t="n">
+      <x:c r="N10" s="8" t="n">
         <x:v>14.5666666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
-      <x:c r="A11" s="17" t="n">
+      <x:c r="A11" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B11" s="8" t="str">
@@ -5704,39 +5868,39 @@
       <x:c r="D11" s="19" t="n">
         <x:v>6.07177449589908</x:v>
       </x:c>
-      <x:c r="E11" s="15" t="str">
+      <x:c r="E11" s="19" t="str">
         <x:v>303.3114 +/- 6.0718</x:v>
       </x:c>
       <x:c r="F11" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G11" s="17" t="n">
+      <x:c r="G11" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="H11" s="18" t="n">
         <x:v>3.66666666666667</x:v>
       </x:c>
-      <x:c r="I11" s="16" t="n">
+      <x:c r="I11" s="8" t="n">
         <x:v>20.91003299</x:v>
       </x:c>
-      <x:c r="J11" s="20" t="n">
+      <x:c r="J11" s="8" t="n">
         <x:v>9107.83333333333</x:v>
       </x:c>
-      <x:c r="K11" s="21" t="n">
+      <x:c r="K11" s="16" t="n">
         <x:v>5.63333333333333</x:v>
       </x:c>
-      <x:c r="L11" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M11" s="16" t="n">
+      <x:c r="L11" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M11" s="8" t="n">
         <x:v>77.8333333333333</x:v>
       </x:c>
-      <x:c r="N11" s="16" t="n">
+      <x:c r="N11" s="8" t="n">
         <x:v>51.5</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
-      <x:c r="A12" s="17" t="n">
+      <x:c r="A12" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B12" s="8" t="str">
@@ -5748,39 +5912,39 @@
       <x:c r="D12" s="19" t="n">
         <x:v>18.341193455388</x:v>
       </x:c>
-      <x:c r="E12" s="15" t="str">
+      <x:c r="E12" s="19" t="str">
         <x:v>313.2191 +/- 18.3412</x:v>
       </x:c>
       <x:c r="F12" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G12" s="17" t="n">
+      <x:c r="G12" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H12" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I12" s="16" t="n">
+      <x:c r="I12" s="8" t="n">
         <x:v>28.7959834</x:v>
       </x:c>
-      <x:c r="J12" s="20" t="n">
+      <x:c r="J12" s="8" t="n">
         <x:v>9592.43333333333</x:v>
       </x:c>
-      <x:c r="K12" s="21" t="n">
+      <x:c r="K12" s="16" t="n">
         <x:v>33.0333333333333</x:v>
       </x:c>
-      <x:c r="L12" s="16" t="n">
+      <x:c r="L12" s="8" t="n">
         <x:v>408.7</x:v>
       </x:c>
-      <x:c r="M12" s="16" t="n">
+      <x:c r="M12" s="8" t="n">
         <x:v>153.733333333333</x:v>
       </x:c>
-      <x:c r="N12" s="16" t="n">
+      <x:c r="N12" s="8" t="n">
         <x:v>107.433333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
-      <x:c r="A13" s="17" t="n">
+      <x:c r="A13" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B13" s="8" t="str">
@@ -5792,80 +5956,80 @@
       <x:c r="D13" s="19" t="n">
         <x:v>342.479097072238</x:v>
       </x:c>
-      <x:c r="E13" s="15" t="str">
+      <x:c r="E13" s="19" t="str">
         <x:v>1597.4829 +/- 342.4791</x:v>
       </x:c>
       <x:c r="F13" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G13" s="17" t="n">
+      <x:c r="G13" s="18" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="H13" s="18" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I13" s="16" t="n">
+      <x:c r="I13" s="8" t="n">
         <x:v>18.1763893466667</x:v>
       </x:c>
-      <x:c r="J13" s="20" t="n">
+      <x:c r="J13" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="K13" s="21" t="str"/>
-      <x:c r="L13" s="16" t="str"/>
-      <x:c r="M13" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N13" s="16" t="n">
+      <x:c r="K13" s="16" t="str"/>
+      <x:c r="L13" s="8" t="str"/>
+      <x:c r="M13" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N13" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
-      <x:c r="A14" s="32" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B14" s="29" t="str">
+      <x:c r="A14" s="147" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B14" s="147" t="str">
         <x:v>CVF-AE</x:v>
       </x:c>
-      <x:c r="C14" s="37" t="n">
+      <x:c r="C14" s="148" t="n">
         <x:v>348.585570334195</x:v>
       </x:c>
-      <x:c r="D14" s="37" t="n">
+      <x:c r="D14" s="148" t="n">
         <x:v>21.815306818365</x:v>
       </x:c>
-      <x:c r="E14" s="30" t="str">
+      <x:c r="E14" s="148" t="str">
         <x:v>348.5856 +/- 21.8153</x:v>
       </x:c>
-      <x:c r="F14" s="31" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G14" s="32" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
+      <x:c r="F14" s="149" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G14" s="150" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H14" s="150" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I14" s="147" t="n">
         <x:v>18.5574635633333</x:v>
       </x:c>
-      <x:c r="J14" s="38" t="n">
+      <x:c r="J14" s="147" t="n">
         <x:v>9367.06666666667</x:v>
       </x:c>
-      <x:c r="K14" s="39" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
+      <x:c r="K14" s="149" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L14" s="147" t="n">
         <x:v>250.266666666667</x:v>
       </x:c>
-      <x:c r="M14" s="31" t="n">
+      <x:c r="M14" s="147" t="n">
         <x:v>86.8</x:v>
       </x:c>
-      <x:c r="N14" s="31" t="n">
+      <x:c r="N14" s="147" t="n">
         <x:v>59.5333333333333</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
-      <x:c r="A15" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A15" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B15" s="8" t="str">
         <x:v>CVF-AE-w/o-CVF</x:v>
@@ -5876,40 +6040,40 @@
       <x:c r="D15" s="19" t="n">
         <x:v>21.3085674527326</x:v>
       </x:c>
-      <x:c r="E15" s="15" t="str">
+      <x:c r="E15" s="19" t="str">
         <x:v>355.8347 +/- 21.3086</x:v>
       </x:c>
       <x:c r="F15" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G15" s="17" t="n">
+      <x:c r="G15" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="H15" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I15" s="16" t="n">
+      <x:c r="I15" s="8" t="n">
         <x:v>24.1732099333333</x:v>
       </x:c>
-      <x:c r="J15" s="20" t="n">
+      <x:c r="J15" s="8" t="n">
         <x:v>9258.5</x:v>
       </x:c>
-      <x:c r="K15" s="21" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L15" s="16" t="n">
+      <x:c r="K15" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L15" s="8" t="n">
         <x:v>228.5</x:v>
       </x:c>
-      <x:c r="M15" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="16" t="n">
+      <x:c r="M15" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N15" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
-      <x:c r="A16" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A16" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B16" s="8" t="str">
         <x:v>CVF-AE-w/o-StateAdaptiveCVF</x:v>
@@ -5920,40 +6084,40 @@
       <x:c r="D16" s="19" t="n">
         <x:v>35.0403448813833</x:v>
       </x:c>
-      <x:c r="E16" s="15" t="str">
+      <x:c r="E16" s="19" t="str">
         <x:v>361.3123 +/- 35.0403</x:v>
       </x:c>
       <x:c r="F16" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G16" s="17" t="n">
+      <x:c r="G16" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="H16" s="18" t="n">
         <x:v>2.33333333333333</x:v>
       </x:c>
-      <x:c r="I16" s="16" t="n">
+      <x:c r="I16" s="8" t="n">
         <x:v>26.13774229</x:v>
       </x:c>
-      <x:c r="J16" s="20" t="n">
+      <x:c r="J16" s="8" t="n">
         <x:v>9321.83333333333</x:v>
       </x:c>
-      <x:c r="K16" s="21" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L16" s="16" t="n">
+      <x:c r="K16" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L16" s="8" t="n">
         <x:v>219.366666666667</x:v>
       </x:c>
-      <x:c r="M16" s="16" t="n">
+      <x:c r="M16" s="8" t="n">
         <x:v>72.4666666666667</x:v>
       </x:c>
-      <x:c r="N16" s="16" t="n">
+      <x:c r="N16" s="8" t="n">
         <x:v>46.2666666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
-      <x:c r="A17" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A17" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B17" s="8" t="str">
         <x:v>CVF-AE-w/o-SparsePreservation</x:v>
@@ -5964,40 +6128,40 @@
       <x:c r="D17" s="19" t="n">
         <x:v>19.821585619792</x:v>
       </x:c>
-      <x:c r="E17" s="15" t="str">
+      <x:c r="E17" s="19" t="str">
         <x:v>372.2255 +/- 19.8216</x:v>
       </x:c>
       <x:c r="F17" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G17" s="17" t="n">
+      <x:c r="G17" s="18" t="n">
         <x:v>4</x:v>
       </x:c>
       <x:c r="H17" s="18" t="n">
         <x:v>3.66666666666667</x:v>
       </x:c>
-      <x:c r="I17" s="16" t="n">
+      <x:c r="I17" s="8" t="n">
         <x:v>20.7890775266667</x:v>
       </x:c>
-      <x:c r="J17" s="20" t="n">
+      <x:c r="J17" s="8" t="n">
         <x:v>9118.7</x:v>
       </x:c>
-      <x:c r="K17" s="21" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L17" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M17" s="16" t="n">
+      <x:c r="K17" s="16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L17" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M17" s="8" t="n">
         <x:v>88.7</x:v>
       </x:c>
-      <x:c r="N17" s="16" t="n">
+      <x:c r="N17" s="8" t="n">
         <x:v>56.6</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
-      <x:c r="A18" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A18" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B18" s="8" t="str">
         <x:v>CVF-AE-w/o-Init</x:v>
@@ -6008,40 +6172,40 @@
       <x:c r="D18" s="19" t="n">
         <x:v>348.826404709658</x:v>
       </x:c>
-      <x:c r="E18" s="15" t="str">
+      <x:c r="E18" s="19" t="str">
         <x:v>556.7515 +/- 348.8264</x:v>
       </x:c>
       <x:c r="F18" s="16" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="G18" s="17" t="n">
+      <x:c r="G18" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
       <x:c r="H18" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I18" s="16" t="n">
+      <x:c r="I18" s="8" t="n">
         <x:v>32.5411983966667</x:v>
       </x:c>
-      <x:c r="J18" s="20" t="n">
+      <x:c r="J18" s="8" t="n">
         <x:v>9802.7</x:v>
       </x:c>
-      <x:c r="K18" s="21" t="n">
+      <x:c r="K18" s="16" t="n">
         <x:v>129.190476190476</x:v>
       </x:c>
-      <x:c r="L18" s="16" t="n">
+      <x:c r="L18" s="8" t="n">
         <x:v>354.8</x:v>
       </x:c>
-      <x:c r="M18" s="16" t="n">
+      <x:c r="M18" s="8" t="n">
         <x:v>417.9</x:v>
       </x:c>
-      <x:c r="N18" s="16" t="n">
+      <x:c r="N18" s="8" t="n">
         <x:v>336.466666666667</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
-      <x:c r="A19" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A19" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B19" s="8" t="str">
         <x:v>Base-AE</x:v>
@@ -6052,37 +6216,37 @@
       <x:c r="D19" s="19" t="n">
         <x:v>199.402741409474</x:v>
       </x:c>
-      <x:c r="E19" s="15" t="str">
+      <x:c r="E19" s="19" t="str">
         <x:v>1643.7320 +/- 199.4027</x:v>
       </x:c>
       <x:c r="F19" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G19" s="17" t="n">
+      <x:c r="G19" s="18" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="H19" s="18" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="I19" s="16" t="n">
+      <x:c r="I19" s="8" t="n">
         <x:v>11.5175831466667</x:v>
       </x:c>
-      <x:c r="J19" s="20" t="n">
+      <x:c r="J19" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="K19" s="21" t="str"/>
-      <x:c r="L19" s="16" t="str"/>
-      <x:c r="M19" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="16" t="n">
+      <x:c r="K19" s="16" t="str"/>
+      <x:c r="L19" s="8" t="str"/>
+      <x:c r="M19" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N19" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R134d3259c7094814"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0fa13108a9d4234"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6091,60 +6255,60 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="11.75" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="11" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="11" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="11" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="11" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="11" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="13" t="str">
+      <x:c r="A1" s="142" t="str">
         <x:v>Scene</x:v>
       </x:c>
-      <x:c r="B1" s="13" t="str">
+      <x:c r="B1" s="142" t="str">
         <x:v>ComparedMethod</x:v>
       </x:c>
-      <x:c r="C1" s="13" t="str">
+      <x:c r="C1" s="142" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="D1" s="13" t="str">
+      <x:c r="D1" s="142" t="str">
         <x:v>CVFAEMean</x:v>
       </x:c>
-      <x:c r="E1" s="13" t="str">
+      <x:c r="E1" s="142" t="str">
         <x:v>ComparedMean</x:v>
       </x:c>
-      <x:c r="F1" s="13" t="str">
+      <x:c r="F1" s="142" t="str">
         <x:v>RawP</x:v>
       </x:c>
-      <x:c r="G1" s="13" t="str">
+      <x:c r="G1" s="142" t="str">
         <x:v>SceneHolmP</x:v>
       </x:c>
-      <x:c r="H1" s="13" t="str">
+      <x:c r="H1" s="142" t="str">
         <x:v>Result</x:v>
       </x:c>
-      <x:c r="I1" s="13" t="str">
-        <x:v>Cliff's Delta</x:v>
-      </x:c>
-      <x:c r="J1" s="13" t="str">
+      <x:c r="I1" s="142" t="str">
+        <x:v>CliffsDelta</x:v>
+      </x:c>
+      <x:c r="J1" s="142" t="str">
         <x:v>EffectMagnitude</x:v>
       </x:c>
-      <x:c r="K1" s="13" t="str">
+      <x:c r="K1" s="142" t="str">
         <x:v>GlobalHolmP</x:v>
       </x:c>
-      <x:c r="L1" s="13" t="str">
+      <x:c r="L1" s="142" t="str">
         <x:v>GlobalResult</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="17" t="n">
+      <x:c r="A2" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="8" t="str">
@@ -6165,7 +6329,7 @@
       <x:c r="G2" s="22" t="n">
         <x:v>1.50992967958108e-10</x:v>
       </x:c>
-      <x:c r="H2" s="56" t="str">
+      <x:c r="H2" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I2" s="19" t="n">
@@ -6182,7 +6346,7 @@
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="17" t="n">
+      <x:c r="A3" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="8" t="str">
@@ -6203,7 +6367,7 @@
       <x:c r="G3" s="22" t="n">
         <x:v>2.68878174336545e-9</x:v>
       </x:c>
-      <x:c r="H3" s="56" t="str">
+      <x:c r="H3" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I3" s="19" t="n">
@@ -6220,7 +6384,7 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
-      <x:c r="A4" s="17" t="n">
+      <x:c r="A4" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="8" t="str">
@@ -6241,7 +6405,7 @@
       <x:c r="G4" s="22" t="n">
         <x:v>0.59968948451237</x:v>
       </x:c>
-      <x:c r="H4" s="57" t="str">
+      <x:c r="H4" s="154" t="str">
         <x:v>=</x:v>
       </x:c>
       <x:c r="I4" s="19" t="n">
@@ -6258,7 +6422,7 @@
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="17" t="n">
+      <x:c r="A5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="8" t="str">
@@ -6279,7 +6443,7 @@
       <x:c r="G5" s="22" t="n">
         <x:v>1.53899271219002e-7</x:v>
       </x:c>
-      <x:c r="H5" s="56" t="str">
+      <x:c r="H5" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I5" s="19" t="n">
@@ -6296,7 +6460,7 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="17" t="n">
+      <x:c r="A6" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="8" t="str">
@@ -6317,7 +6481,7 @@
       <x:c r="G6" s="22" t="n">
         <x:v>3.30701983832931e-8</x:v>
       </x:c>
-      <x:c r="H6" s="56" t="str">
+      <x:c r="H6" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I6" s="19" t="n">
@@ -6334,7 +6498,7 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="17" t="n">
+      <x:c r="A7" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="8" t="str">
@@ -6355,7 +6519,7 @@
       <x:c r="G7" s="22" t="n">
         <x:v>1.50992967958108e-10</x:v>
       </x:c>
-      <x:c r="H7" s="56" t="str">
+      <x:c r="H7" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I7" s="19" t="n">
@@ -6372,7 +6536,7 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="17" t="n">
+      <x:c r="A8" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B8" s="8" t="str">
@@ -6393,7 +6557,7 @@
       <x:c r="G8" s="22" t="n">
         <x:v>0.0000069161250499397</x:v>
       </x:c>
-      <x:c r="H8" s="56" t="str">
+      <x:c r="H8" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I8" s="19" t="n">
@@ -6410,7 +6574,7 @@
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="17" t="n">
+      <x:c r="A9" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B9" s="8" t="str">
@@ -6431,7 +6595,7 @@
       <x:c r="G9" s="22" t="n">
         <x:v>0.258051495086236</x:v>
       </x:c>
-      <x:c r="H9" s="57" t="str">
+      <x:c r="H9" s="154" t="str">
         <x:v>=</x:v>
       </x:c>
       <x:c r="I9" s="19" t="n">
@@ -6448,7 +6612,7 @@
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="17" t="n">
+      <x:c r="A10" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B10" s="8" t="str">
@@ -6469,7 +6633,7 @@
       <x:c r="G10" s="22" t="n">
         <x:v>0.198515216479652</x:v>
       </x:c>
-      <x:c r="H10" s="57" t="str">
+      <x:c r="H10" s="154" t="str">
         <x:v>=</x:v>
       </x:c>
       <x:c r="I10" s="19" t="n">
@@ -6486,7 +6650,7 @@
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
-      <x:c r="A11" s="17" t="n">
+      <x:c r="A11" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B11" s="8" t="str">
@@ -6507,7 +6671,7 @@
       <x:c r="G11" s="22" t="n">
         <x:v>0.0272062829798207</x:v>
       </x:c>
-      <x:c r="H11" s="56" t="str">
+      <x:c r="H11" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I11" s="19" t="n">
@@ -6524,8 +6688,8 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
-      <x:c r="A12" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A12" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B12" s="8" t="str">
         <x:v>Base-AE</x:v>
@@ -6545,7 +6709,7 @@
       <x:c r="G12" s="22" t="n">
         <x:v>1.50992967958108e-10</x:v>
       </x:c>
-      <x:c r="H12" s="56" t="str">
+      <x:c r="H12" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I12" s="19" t="n">
@@ -6562,8 +6726,8 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
-      <x:c r="A13" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A13" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B13" s="8" t="str">
         <x:v>CVF-AE-w/o-Init</x:v>
@@ -6583,7 +6747,7 @@
       <x:c r="G13" s="22" t="n">
         <x:v>0.853381736754793</x:v>
       </x:c>
-      <x:c r="H13" s="57" t="str">
+      <x:c r="H13" s="154" t="str">
         <x:v>=</x:v>
       </x:c>
       <x:c r="I13" s="19" t="n">
@@ -6600,8 +6764,8 @@
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
-      <x:c r="A14" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A14" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B14" s="8" t="str">
         <x:v>CVF-AE-w/o-StateAdaptiveCVF</x:v>
@@ -6621,7 +6785,7 @@
       <x:c r="G14" s="22" t="n">
         <x:v>0.710944945188621</x:v>
       </x:c>
-      <x:c r="H14" s="57" t="str">
+      <x:c r="H14" s="154" t="str">
         <x:v>=</x:v>
       </x:c>
       <x:c r="I14" s="19" t="n">
@@ -6638,8 +6802,8 @@
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
-      <x:c r="A15" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A15" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B15" s="8" t="str">
         <x:v>CVF-AE-w/o-SparsePreservation</x:v>
@@ -6659,7 +6823,7 @@
       <x:c r="G15" s="22" t="n">
         <x:v>0.000442309038723352</x:v>
       </x:c>
-      <x:c r="H15" s="56" t="str">
+      <x:c r="H15" s="152" t="str">
         <x:v>+</x:v>
       </x:c>
       <x:c r="I15" s="19" t="n">
@@ -6676,8 +6840,8 @@
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
-      <x:c r="A16" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A16" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B16" s="8" t="str">
         <x:v>CVF-AE-w/o-CVF</x:v>
@@ -6697,7 +6861,7 @@
       <x:c r="G16" s="22" t="n">
         <x:v>0.411968504540979</x:v>
       </x:c>
-      <x:c r="H16" s="57" t="str">
+      <x:c r="H16" s="154" t="str">
         <x:v>=</x:v>
       </x:c>
       <x:c r="I16" s="19" t="n">
@@ -6716,7 +6880,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf89cfcf65e0a4904"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1558cea287d748d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6725,71 +6889,71 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="32" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="28" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="11" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="11" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="11" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="11" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="11" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="11" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="12.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="11" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="12.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="14" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="13" t="str">
+      <x:c r="A1" s="142" t="str">
         <x:v>Parameter</x:v>
       </x:c>
-      <x:c r="B1" s="13" t="str">
+      <x:c r="B1" s="142" t="str">
         <x:v>ParameterLabel</x:v>
       </x:c>
-      <x:c r="C1" s="13" t="str">
+      <x:c r="C1" s="142" t="str">
         <x:v>Level</x:v>
       </x:c>
-      <x:c r="D1" s="13" t="str">
-        <x:v>Level Description</x:v>
-      </x:c>
-      <x:c r="E1" s="13" t="str">
+      <x:c r="D1" s="142" t="str">
+        <x:v>LevelDescription</x:v>
+      </x:c>
+      <x:c r="E1" s="142" t="str">
         <x:v>IsDefault</x:v>
       </x:c>
-      <x:c r="F1" s="13" t="str">
+      <x:c r="F1" s="142" t="str">
         <x:v>Scene</x:v>
       </x:c>
-      <x:c r="G1" s="13" t="str">
+      <x:c r="G1" s="142" t="str">
         <x:v>MeanFitness</x:v>
       </x:c>
-      <x:c r="H1" s="13" t="str">
+      <x:c r="H1" s="142" t="str">
         <x:v>StdFitness</x:v>
       </x:c>
-      <x:c r="I1" s="13" t="str">
+      <x:c r="I1" s="142" t="str">
         <x:v>FeasibleRate</x:v>
       </x:c>
-      <x:c r="J1" s="13" t="str">
+      <x:c r="J1" s="142" t="str">
         <x:v>SceneRank</x:v>
       </x:c>
-      <x:c r="K1" s="13" t="str">
+      <x:c r="K1" s="142" t="str">
         <x:v>AverageRank</x:v>
       </x:c>
-      <x:c r="L1" s="13" t="str">
+      <x:c r="L1" s="142" t="str">
         <x:v>RuntimeSeconds</x:v>
       </x:c>
-      <x:c r="M1" s="13" t="str">
+      <x:c r="M1" s="142" t="str">
         <x:v>NEvals</x:v>
       </x:c>
-      <x:c r="N1" s="13" t="str">
+      <x:c r="N1" s="142" t="str">
         <x:v>CVFTriggerCount</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="30" hidden="0" customHeight="1">
-      <x:c r="A2" s="14" t="str">
+    <x:row r="2" ht="15" hidden="0" customHeight="1">
+      <x:c r="A2" s="8" t="str">
         <x:v>quota_scale</x:v>
       </x:c>
-      <x:c r="B2" s="14" t="str">
+      <x:c r="B2" s="8" t="str">
         <x:v>CVF candidate quota scale</x:v>
       </x:c>
       <x:c r="C2" s="8" t="str">
@@ -6801,7 +6965,7 @@
       <x:c r="E2" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F2" s="17" t="n">
+      <x:c r="F2" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G2" s="19" t="n">
@@ -6813,71 +6977,71 @@
       <x:c r="I2" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J2" s="17" t="n">
+      <x:c r="J2" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K2" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L2" s="16" t="n">
+      <x:c r="L2" s="8" t="n">
         <x:v>16.70037636</x:v>
       </x:c>
-      <x:c r="M2" s="20" t="n">
+      <x:c r="M2" s="8" t="n">
         <x:v>9561.6</x:v>
       </x:c>
-      <x:c r="N2" s="16" t="n">
+      <x:c r="N2" s="8" t="n">
         <x:v>20.4</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="30" hidden="0" customHeight="1">
-      <x:c r="A3" s="47" t="str">
+    <x:row r="3" ht="15" hidden="0" customHeight="1">
+      <x:c r="A3" s="8" t="str">
         <x:v>quota_scale</x:v>
       </x:c>
-      <x:c r="B3" s="47" t="str">
+      <x:c r="B3" s="8" t="str">
         <x:v>CVF candidate quota scale</x:v>
       </x:c>
-      <x:c r="C3" s="48" t="str">
+      <x:c r="C3" s="8" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="D3" s="47" t="str">
+      <x:c r="D3" s="14" t="str">
         <x:v>default CVF sparse trigger quota</x:v>
       </x:c>
-      <x:c r="E3" s="48" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F3" s="49" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G3" s="50" t="n">
+      <x:c r="E3" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F3" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G3" s="19" t="n">
         <x:v>302.066342593858</x:v>
       </x:c>
-      <x:c r="H3" s="50" t="n">
+      <x:c r="H3" s="19" t="n">
         <x:v>2.72247711842544</x:v>
       </x:c>
-      <x:c r="I3" s="51" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J3" s="49" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K3" s="52" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L3" s="51" t="n">
+      <x:c r="I3" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J3" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K3" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L3" s="8" t="n">
         <x:v>14.87216704</x:v>
       </x:c>
-      <x:c r="M3" s="53" t="n">
+      <x:c r="M3" s="8" t="n">
         <x:v>9553.4</x:v>
       </x:c>
-      <x:c r="N3" s="51" t="n">
+      <x:c r="N3" s="8" t="n">
         <x:v>12.6</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="30" hidden="0" customHeight="1">
-      <x:c r="A4" s="14" t="str">
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8" t="str">
         <x:v>quota_scale</x:v>
       </x:c>
-      <x:c r="B4" s="14" t="str">
+      <x:c r="B4" s="8" t="str">
         <x:v>CVF candidate quota scale</x:v>
       </x:c>
       <x:c r="C4" s="8" t="str">
@@ -6889,7 +7053,7 @@
       <x:c r="E4" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F4" s="17" t="n">
+      <x:c r="F4" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G4" s="19" t="n">
@@ -6901,27 +7065,27 @@
       <x:c r="I4" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J4" s="17" t="n">
+      <x:c r="J4" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="K4" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L4" s="16" t="n">
+      <x:c r="L4" s="8" t="n">
         <x:v>13.03620065</x:v>
       </x:c>
-      <x:c r="M4" s="20" t="n">
+      <x:c r="M4" s="8" t="n">
         <x:v>9551</x:v>
       </x:c>
-      <x:c r="N4" s="16" t="n">
+      <x:c r="N4" s="8" t="n">
         <x:v>9.2</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="30" hidden="0" customHeight="1">
-      <x:c r="A5" s="14" t="str">
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8" t="str">
         <x:v>quota_scale</x:v>
       </x:c>
-      <x:c r="B5" s="14" t="str">
+      <x:c r="B5" s="8" t="str">
         <x:v>CVF candidate quota scale</x:v>
       </x:c>
       <x:c r="C5" s="8" t="str">
@@ -6933,8 +7097,8 @@
       <x:c r="E5" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F5" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="F5" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G5" s="19" t="n">
         <x:v>340.567579352115</x:v>
@@ -6945,71 +7109,71 @@
       <x:c r="I5" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J5" s="17" t="n">
+      <x:c r="J5" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K5" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="L5" s="16" t="n">
+      <x:c r="L5" s="8" t="n">
         <x:v>19.64399309</x:v>
       </x:c>
-      <x:c r="M5" s="20" t="n">
+      <x:c r="M5" s="8" t="n">
         <x:v>9366.6</x:v>
       </x:c>
-      <x:c r="N5" s="16" t="n">
+      <x:c r="N5" s="8" t="n">
         <x:v>85.7</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="30" hidden="0" customHeight="1">
-      <x:c r="A6" s="47" t="str">
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8" t="str">
         <x:v>quota_scale</x:v>
       </x:c>
-      <x:c r="B6" s="47" t="str">
+      <x:c r="B6" s="8" t="str">
         <x:v>CVF candidate quota scale</x:v>
       </x:c>
-      <x:c r="C6" s="48" t="str">
+      <x:c r="C6" s="8" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="D6" s="47" t="str">
+      <x:c r="D6" s="14" t="str">
         <x:v>default CVF sparse trigger quota</x:v>
       </x:c>
-      <x:c r="E6" s="48" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F6" s="49" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G6" s="50" t="n">
+      <x:c r="E6" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F6" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G6" s="19" t="n">
         <x:v>342.398730539812</x:v>
       </x:c>
-      <x:c r="H6" s="50" t="n">
+      <x:c r="H6" s="19" t="n">
         <x:v>19.0285230463495</x:v>
       </x:c>
-      <x:c r="I6" s="51" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J6" s="49" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K6" s="52" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L6" s="51" t="n">
+      <x:c r="I6" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J6" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K6" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L6" s="8" t="n">
         <x:v>14.83497602</x:v>
       </x:c>
-      <x:c r="M6" s="53" t="n">
+      <x:c r="M6" s="8" t="n">
         <x:v>9336</x:v>
       </x:c>
-      <x:c r="N6" s="51" t="n">
+      <x:c r="N6" s="8" t="n">
         <x:v>82.4</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="30" hidden="0" customHeight="1">
-      <x:c r="A7" s="14" t="str">
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8" t="str">
         <x:v>quota_scale</x:v>
       </x:c>
-      <x:c r="B7" s="14" t="str">
+      <x:c r="B7" s="8" t="str">
         <x:v>CVF candidate quota scale</x:v>
       </x:c>
       <x:c r="C7" s="8" t="str">
@@ -7021,8 +7185,8 @@
       <x:c r="E7" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F7" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="F7" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G7" s="19" t="n">
         <x:v>354.883975923183</x:v>
@@ -7033,27 +7197,27 @@
       <x:c r="I7" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J7" s="17" t="n">
+      <x:c r="J7" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="K7" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="L7" s="16" t="n">
+      <x:c r="L7" s="8" t="n">
         <x:v>5.71331897</x:v>
       </x:c>
-      <x:c r="M7" s="20" t="n">
+      <x:c r="M7" s="8" t="n">
         <x:v>9341.9</x:v>
       </x:c>
-      <x:c r="N7" s="16" t="n">
+      <x:c r="N7" s="8" t="n">
         <x:v>88.8</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="30" hidden="0" customHeight="1">
-      <x:c r="A8" s="14" t="str">
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8" t="str">
         <x:v>state_switch_threshold</x:v>
       </x:c>
-      <x:c r="B8" s="14" t="str">
+      <x:c r="B8" s="8" t="str">
         <x:v>Conservative state switching threshold</x:v>
       </x:c>
       <x:c r="C8" s="8" t="str">
@@ -7065,7 +7229,7 @@
       <x:c r="E8" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F8" s="17" t="n">
+      <x:c r="F8" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G8" s="19" t="n">
@@ -7077,71 +7241,71 @@
       <x:c r="I8" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J8" s="17" t="n">
+      <x:c r="J8" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K8" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L8" s="16" t="n">
+      <x:c r="L8" s="8" t="n">
         <x:v>6.26920627</x:v>
       </x:c>
-      <x:c r="M8" s="20" t="n">
+      <x:c r="M8" s="8" t="n">
         <x:v>9557.4</x:v>
       </x:c>
-      <x:c r="N8" s="16" t="n">
+      <x:c r="N8" s="8" t="n">
         <x:v>15.7</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="30" hidden="0" customHeight="1">
-      <x:c r="A9" s="47" t="str">
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8" t="str">
         <x:v>state_switch_threshold</x:v>
       </x:c>
-      <x:c r="B9" s="47" t="str">
+      <x:c r="B9" s="8" t="str">
         <x:v>Conservative state switching threshold</x:v>
       </x:c>
-      <x:c r="C9" s="48" t="str">
+      <x:c r="C9" s="8" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="D9" s="47" t="str">
+      <x:c r="D9" s="14" t="str">
         <x:v>default conservative switching threshold</x:v>
       </x:c>
-      <x:c r="E9" s="48" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F9" s="49" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G9" s="50" t="n">
+      <x:c r="E9" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F9" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G9" s="19" t="n">
         <x:v>301.239860854481</x:v>
       </x:c>
-      <x:c r="H9" s="50" t="n">
+      <x:c r="H9" s="19" t="n">
         <x:v>2.76019485638891</x:v>
       </x:c>
-      <x:c r="I9" s="51" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J9" s="49" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K9" s="52" t="n">
+      <x:c r="I9" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J9" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K9" s="18" t="n">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="L9" s="51" t="n">
+      <x:c r="L9" s="8" t="n">
         <x:v>6.23726825</x:v>
       </x:c>
-      <x:c r="M9" s="53" t="n">
+      <x:c r="M9" s="8" t="n">
         <x:v>9551.6</x:v>
       </x:c>
-      <x:c r="N9" s="51" t="n">
+      <x:c r="N9" s="8" t="n">
         <x:v>9.4</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="30" hidden="0" customHeight="1">
-      <x:c r="A10" s="14" t="str">
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8" t="str">
         <x:v>state_switch_threshold</x:v>
       </x:c>
-      <x:c r="B10" s="14" t="str">
+      <x:c r="B10" s="8" t="str">
         <x:v>Conservative state switching threshold</x:v>
       </x:c>
       <x:c r="C10" s="8" t="str">
@@ -7153,7 +7317,7 @@
       <x:c r="E10" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F10" s="17" t="n">
+      <x:c r="F10" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G10" s="19" t="n">
@@ -7165,71 +7329,71 @@
       <x:c r="I10" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J10" s="17" t="n">
+      <x:c r="J10" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="K10" s="18" t="n">
         <x:v>2.5</x:v>
       </x:c>
-      <x:c r="L10" s="16" t="n">
+      <x:c r="L10" s="8" t="n">
         <x:v>6.257871</x:v>
       </x:c>
-      <x:c r="M10" s="20" t="n">
+      <x:c r="M10" s="8" t="n">
         <x:v>9550.1</x:v>
       </x:c>
-      <x:c r="N10" s="16" t="n">
+      <x:c r="N10" s="8" t="n">
         <x:v>9.3</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="30" hidden="0" customHeight="1">
-      <x:c r="A11" s="47" t="str">
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8" t="str">
         <x:v>state_switch_threshold</x:v>
       </x:c>
-      <x:c r="B11" s="47" t="str">
+      <x:c r="B11" s="8" t="str">
         <x:v>Conservative state switching threshold</x:v>
       </x:c>
-      <x:c r="C11" s="48" t="str">
+      <x:c r="C11" s="8" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="D11" s="47" t="str">
+      <x:c r="D11" s="14" t="str">
         <x:v>default conservative switching threshold</x:v>
       </x:c>
-      <x:c r="E11" s="48" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F11" s="49" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G11" s="50" t="n">
+      <x:c r="E11" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F11" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G11" s="19" t="n">
         <x:v>351.042228377221</x:v>
       </x:c>
-      <x:c r="H11" s="50" t="n">
+      <x:c r="H11" s="19" t="n">
         <x:v>20.8199079582641</x:v>
       </x:c>
-      <x:c r="I11" s="51" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J11" s="49" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K11" s="52" t="n">
+      <x:c r="I11" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J11" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K11" s="18" t="n">
         <x:v>1.5</x:v>
       </x:c>
-      <x:c r="L11" s="51" t="n">
+      <x:c r="L11" s="8" t="n">
         <x:v>5.93557599</x:v>
       </x:c>
-      <x:c r="M11" s="53" t="n">
+      <x:c r="M11" s="8" t="n">
         <x:v>9343</x:v>
       </x:c>
-      <x:c r="N11" s="51" t="n">
+      <x:c r="N11" s="8" t="n">
         <x:v>89</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="30" hidden="0" customHeight="1">
-      <x:c r="A12" s="14" t="str">
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="8" t="str">
         <x:v>state_switch_threshold</x:v>
       </x:c>
-      <x:c r="B12" s="14" t="str">
+      <x:c r="B12" s="8" t="str">
         <x:v>Conservative state switching threshold</x:v>
       </x:c>
       <x:c r="C12" s="8" t="str">
@@ -7241,8 +7405,8 @@
       <x:c r="E12" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F12" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="F12" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G12" s="19" t="n">
         <x:v>354.087942003274</x:v>
@@ -7253,27 +7417,27 @@
       <x:c r="I12" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J12" s="17" t="n">
+      <x:c r="J12" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="K12" s="18" t="n">
         <x:v>2.5</x:v>
       </x:c>
-      <x:c r="L12" s="16" t="n">
+      <x:c r="L12" s="8" t="n">
         <x:v>6.0499411</x:v>
       </x:c>
-      <x:c r="M12" s="20" t="n">
+      <x:c r="M12" s="8" t="n">
         <x:v>9379.6</x:v>
       </x:c>
-      <x:c r="N12" s="16" t="n">
+      <x:c r="N12" s="8" t="n">
         <x:v>82.9</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="30" hidden="0" customHeight="1">
-      <x:c r="A13" s="14" t="str">
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="8" t="str">
         <x:v>state_switch_threshold</x:v>
       </x:c>
-      <x:c r="B13" s="14" t="str">
+      <x:c r="B13" s="8" t="str">
         <x:v>Conservative state switching threshold</x:v>
       </x:c>
       <x:c r="C13" s="8" t="str">
@@ -7285,8 +7449,8 @@
       <x:c r="E13" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F13" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="F13" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G13" s="19" t="n">
         <x:v>356.912157313134</x:v>
@@ -7297,71 +7461,71 @@
       <x:c r="I13" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J13" s="17" t="n">
+      <x:c r="J13" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="K13" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L13" s="16" t="n">
+      <x:c r="L13" s="8" t="n">
         <x:v>6.07994243</x:v>
       </x:c>
-      <x:c r="M13" s="20" t="n">
+      <x:c r="M13" s="8" t="n">
         <x:v>9383.6</x:v>
       </x:c>
-      <x:c r="N13" s="16" t="n">
+      <x:c r="N13" s="8" t="n">
         <x:v>92.7</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="30" hidden="0" customHeight="1">
-      <x:c r="A14" s="47" t="str">
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14" s="8" t="str">
         <x:v>step_strength</x:v>
       </x:c>
-      <x:c r="B14" s="47" t="str">
+      <x:c r="B14" s="8" t="str">
         <x:v>CVF step strength</x:v>
       </x:c>
-      <x:c r="C14" s="48" t="str">
+      <x:c r="C14" s="8" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="D14" s="47" t="str">
+      <x:c r="D14" s="14" t="str">
         <x:v>default CVF field strength</x:v>
       </x:c>
-      <x:c r="E14" s="48" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F14" s="49" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G14" s="50" t="n">
+      <x:c r="E14" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F14" s="8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G14" s="19" t="n">
         <x:v>300.544296257537</x:v>
       </x:c>
-      <x:c r="H14" s="50" t="n">
+      <x:c r="H14" s="19" t="n">
         <x:v>1.93997775498066</x:v>
       </x:c>
-      <x:c r="I14" s="51" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J14" s="49" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K14" s="52" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L14" s="51" t="n">
+      <x:c r="I14" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K14" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L14" s="8" t="n">
         <x:v>28.62980939</x:v>
       </x:c>
-      <x:c r="M14" s="53" t="n">
+      <x:c r="M14" s="8" t="n">
         <x:v>9557.5</x:v>
       </x:c>
-      <x:c r="N14" s="51" t="n">
+      <x:c r="N14" s="8" t="n">
         <x:v>16.7</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="30" hidden="0" customHeight="1">
-      <x:c r="A15" s="14" t="str">
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15" s="8" t="str">
         <x:v>step_strength</x:v>
       </x:c>
-      <x:c r="B15" s="14" t="str">
+      <x:c r="B15" s="8" t="str">
         <x:v>CVF step strength</x:v>
       </x:c>
       <x:c r="C15" s="8" t="str">
@@ -7373,7 +7537,7 @@
       <x:c r="E15" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F15" s="17" t="n">
+      <x:c r="F15" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G15" s="19" t="n">
@@ -7385,27 +7549,27 @@
       <x:c r="I15" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J15" s="17" t="n">
+      <x:c r="J15" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="K15" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L15" s="16" t="n">
+      <x:c r="L15" s="8" t="n">
         <x:v>29.04853466</x:v>
       </x:c>
-      <x:c r="M15" s="20" t="n">
+      <x:c r="M15" s="8" t="n">
         <x:v>9554.8</x:v>
       </x:c>
-      <x:c r="N15" s="16" t="n">
+      <x:c r="N15" s="8" t="n">
         <x:v>13.7</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="30" hidden="0" customHeight="1">
-      <x:c r="A16" s="14" t="str">
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16" s="8" t="str">
         <x:v>step_strength</x:v>
       </x:c>
-      <x:c r="B16" s="14" t="str">
+      <x:c r="B16" s="8" t="str">
         <x:v>CVF step strength</x:v>
       </x:c>
       <x:c r="C16" s="8" t="str">
@@ -7417,7 +7581,7 @@
       <x:c r="E16" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F16" s="17" t="n">
+      <x:c r="F16" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="G16" s="19" t="n">
@@ -7429,27 +7593,27 @@
       <x:c r="I16" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J16" s="17" t="n">
+      <x:c r="J16" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="K16" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L16" s="16" t="n">
+      <x:c r="L16" s="8" t="n">
         <x:v>18.87387044</x:v>
       </x:c>
-      <x:c r="M16" s="20" t="n">
+      <x:c r="M16" s="8" t="n">
         <x:v>9553.4</x:v>
       </x:c>
-      <x:c r="N16" s="16" t="n">
+      <x:c r="N16" s="8" t="n">
         <x:v>13</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="30" hidden="0" customHeight="1">
-      <x:c r="A17" s="14" t="str">
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17" s="8" t="str">
         <x:v>step_strength</x:v>
       </x:c>
-      <x:c r="B17" s="14" t="str">
+      <x:c r="B17" s="8" t="str">
         <x:v>CVF step strength</x:v>
       </x:c>
       <x:c r="C17" s="8" t="str">
@@ -7461,8 +7625,8 @@
       <x:c r="E17" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F17" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="F17" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G17" s="19" t="n">
         <x:v>347.026790075119</x:v>
@@ -7473,27 +7637,27 @@
       <x:c r="I17" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J17" s="17" t="n">
+      <x:c r="J17" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="K17" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L17" s="16" t="n">
+      <x:c r="L17" s="8" t="n">
         <x:v>20.29039721</x:v>
       </x:c>
-      <x:c r="M17" s="20" t="n">
+      <x:c r="M17" s="8" t="n">
         <x:v>9361.9</x:v>
       </x:c>
-      <x:c r="N17" s="16" t="n">
+      <x:c r="N17" s="8" t="n">
         <x:v>85.9</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="30" hidden="0" customHeight="1">
-      <x:c r="A18" s="14" t="str">
+    <x:row r="18" ht="15" hidden="0" customHeight="1">
+      <x:c r="A18" s="8" t="str">
         <x:v>step_strength</x:v>
       </x:c>
-      <x:c r="B18" s="14" t="str">
+      <x:c r="B18" s="8" t="str">
         <x:v>CVF step strength</x:v>
       </x:c>
       <x:c r="C18" s="8" t="str">
@@ -7505,8 +7669,8 @@
       <x:c r="E18" s="8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="F18" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G18" s="19" t="n">
         <x:v>351.598294072786</x:v>
@@ -7517,70 +7681,70 @@
       <x:c r="I18" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J18" s="17" t="n">
+      <x:c r="J18" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="K18" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="L18" s="16" t="n">
+      <x:c r="L18" s="8" t="n">
         <x:v>6.72012654</x:v>
       </x:c>
-      <x:c r="M18" s="20" t="n">
+      <x:c r="M18" s="8" t="n">
         <x:v>9340.2</x:v>
       </x:c>
-      <x:c r="N18" s="16" t="n">
+      <x:c r="N18" s="8" t="n">
         <x:v>84.6</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="30" hidden="0" customHeight="1">
-      <x:c r="A19" s="47" t="str">
+    <x:row r="19" ht="15" hidden="0" customHeight="1">
+      <x:c r="A19" s="8" t="str">
         <x:v>step_strength</x:v>
       </x:c>
-      <x:c r="B19" s="47" t="str">
+      <x:c r="B19" s="8" t="str">
         <x:v>CVF step strength</x:v>
       </x:c>
-      <x:c r="C19" s="48" t="str">
+      <x:c r="C19" s="8" t="str">
         <x:v>default</x:v>
       </x:c>
-      <x:c r="D19" s="47" t="str">
+      <x:c r="D19" s="14" t="str">
         <x:v>default CVF field strength</x:v>
       </x:c>
-      <x:c r="E19" s="48" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="F19" s="49" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="G19" s="50" t="n">
+      <x:c r="E19" s="8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F19" s="8" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G19" s="19" t="n">
         <x:v>355.392949162461</x:v>
       </x:c>
-      <x:c r="H19" s="50" t="n">
+      <x:c r="H19" s="19" t="n">
         <x:v>16.1756703226076</x:v>
       </x:c>
-      <x:c r="I19" s="51" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J19" s="49" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="K19" s="52" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="L19" s="51" t="n">
+      <x:c r="I19" s="16" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J19" s="18" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K19" s="18" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="L19" s="8" t="n">
         <x:v>28.3670393</x:v>
       </x:c>
-      <x:c r="M19" s="53" t="n">
+      <x:c r="M19" s="8" t="n">
         <x:v>9358</x:v>
       </x:c>
-      <x:c r="N19" s="51" t="n">
+      <x:c r="N19" s="8" t="n">
         <x:v>86.2</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5512fea505c47fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f863bd6885f446d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7589,51 +7753,51 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="14.25" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="11" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="12.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="11" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="12.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="12.5" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="11" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="11" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="13" t="str">
+      <x:c r="A1" s="142" t="str">
         <x:v>Analysis</x:v>
       </x:c>
-      <x:c r="B1" s="13" t="str">
+      <x:c r="B1" s="142" t="str">
         <x:v>Scene</x:v>
       </x:c>
-      <x:c r="C1" s="13" t="str">
+      <x:c r="C1" s="142" t="str">
         <x:v>Algorithm</x:v>
       </x:c>
-      <x:c r="D1" s="13" t="str">
+      <x:c r="D1" s="142" t="str">
         <x:v>RuntimeSeconds</x:v>
       </x:c>
-      <x:c r="E1" s="13" t="str">
+      <x:c r="E1" s="142" t="str">
         <x:v>NEvals</x:v>
       </x:c>
-      <x:c r="F1" s="13" t="str">
+      <x:c r="F1" s="142" t="str">
         <x:v>CVFTriggerCount</x:v>
       </x:c>
-      <x:c r="G1" s="13" t="str">
+      <x:c r="G1" s="142" t="str">
         <x:v>CVFSuccessCount</x:v>
       </x:c>
-      <x:c r="H1" s="13" t="str">
-        <x:v>Runtime Ratio vs w/o CVF</x:v>
-      </x:c>
-      <x:c r="I1" s="13" t="str">
-        <x:v>NEvals Ratio vs w/o CVF</x:v>
-      </x:c>
-      <x:c r="J1" s="13" t="str">
+      <x:c r="H1" s="142" t="str">
+        <x:v>RuntimeRatioVsWithoutCVF</x:v>
+      </x:c>
+      <x:c r="I1" s="142" t="str">
+        <x:v>NEvalsRatioVsWithoutCVF</x:v>
+      </x:c>
+      <x:c r="J1" s="142" t="str">
         <x:v>FeasibleRate</x:v>
       </x:c>
-      <x:c r="K1" s="13" t="str">
+      <x:c r="K1" s="142" t="str">
         <x:v>Rank</x:v>
       </x:c>
     </x:row>
@@ -7641,30 +7805,30 @@
       <x:c r="A2" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B2" s="17" t="n">
+      <x:c r="B2" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="8" t="str">
         <x:v>CVF-AE</x:v>
       </x:c>
-      <x:c r="D2" s="16" t="n">
+      <x:c r="D2" s="8" t="n">
         <x:v>5.93901229333333</x:v>
       </x:c>
-      <x:c r="E2" s="20" t="n">
+      <x:c r="E2" s="8" t="n">
         <x:v>9568.9</x:v>
       </x:c>
-      <x:c r="F2" s="16" t="n">
+      <x:c r="F2" s="8" t="n">
         <x:v>23.9333333333333</x:v>
       </x:c>
-      <x:c r="G2" s="16" t="n">
+      <x:c r="G2" s="8" t="n">
         <x:v>21.8</x:v>
       </x:c>
-      <x:c r="H2" s="21" t="str"/>
-      <x:c r="I2" s="23" t="str"/>
+      <x:c r="H2" s="19" t="str"/>
+      <x:c r="I2" s="19" t="str"/>
       <x:c r="J2" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K2" s="17" t="n">
+      <x:c r="K2" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -7672,30 +7836,30 @@
       <x:c r="A3" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B3" s="17" t="n">
+      <x:c r="B3" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="8" t="str">
         <x:v>AE</x:v>
       </x:c>
-      <x:c r="D3" s="16" t="n">
+      <x:c r="D3" s="8" t="n">
         <x:v>4.41410844333333</x:v>
       </x:c>
-      <x:c r="E3" s="20" t="n">
+      <x:c r="E3" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="F3" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H3" s="21" t="str"/>
-      <x:c r="I3" s="23" t="str"/>
+      <x:c r="F3" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G3" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H3" s="19" t="str"/>
+      <x:c r="I3" s="19" t="str"/>
       <x:c r="J3" s="16" t="n">
         <x:v>0.333333333333333</x:v>
       </x:c>
-      <x:c r="K3" s="17" t="n">
+      <x:c r="K3" s="18" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -7703,30 +7867,30 @@
       <x:c r="A4" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B4" s="17" t="n">
+      <x:c r="B4" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C4" s="8" t="str">
         <x:v>PSO</x:v>
       </x:c>
-      <x:c r="D4" s="16" t="n">
+      <x:c r="D4" s="8" t="n">
         <x:v>4.25249685</x:v>
       </x:c>
-      <x:c r="E4" s="20" t="n">
+      <x:c r="E4" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="F4" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H4" s="21" t="str"/>
-      <x:c r="I4" s="23" t="str"/>
+      <x:c r="F4" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G4" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H4" s="19" t="str"/>
+      <x:c r="I4" s="19" t="str"/>
       <x:c r="J4" s="16" t="n">
         <x:v>0.866666666666667</x:v>
       </x:c>
-      <x:c r="K4" s="17" t="n">
+      <x:c r="K4" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -7734,30 +7898,30 @@
       <x:c r="A5" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B5" s="17" t="n">
+      <x:c r="B5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="8" t="str">
         <x:v>GWO</x:v>
       </x:c>
-      <x:c r="D5" s="16" t="n">
+      <x:c r="D5" s="8" t="n">
         <x:v>4.40407022333333</x:v>
       </x:c>
-      <x:c r="E5" s="20" t="n">
+      <x:c r="E5" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="F5" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H5" s="21" t="str"/>
-      <x:c r="I5" s="23" t="str"/>
+      <x:c r="F5" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G5" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H5" s="19" t="str"/>
+      <x:c r="I5" s="19" t="str"/>
       <x:c r="J5" s="16" t="n">
         <x:v>0.933333333333333</x:v>
       </x:c>
-      <x:c r="K5" s="17" t="n">
+      <x:c r="K5" s="18" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -7765,30 +7929,30 @@
       <x:c r="A6" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B6" s="17" t="n">
+      <x:c r="B6" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="8" t="str">
         <x:v>WOA</x:v>
       </x:c>
-      <x:c r="D6" s="16" t="n">
+      <x:c r="D6" s="8" t="n">
         <x:v>4.31642514333333</x:v>
       </x:c>
-      <x:c r="E6" s="20" t="n">
+      <x:c r="E6" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="F6" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H6" s="21" t="str"/>
-      <x:c r="I6" s="23" t="str"/>
+      <x:c r="F6" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H6" s="19" t="str"/>
+      <x:c r="I6" s="19" t="str"/>
       <x:c r="J6" s="16" t="n">
         <x:v>0.8</x:v>
       </x:c>
-      <x:c r="K6" s="17" t="n">
+      <x:c r="K6" s="18" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -7796,30 +7960,30 @@
       <x:c r="A7" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B7" s="17" t="n">
+      <x:c r="B7" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C7" s="8" t="str">
         <x:v>HHO</x:v>
       </x:c>
-      <x:c r="D7" s="16" t="n">
+      <x:c r="D7" s="8" t="n">
         <x:v>6.75716871666667</x:v>
       </x:c>
-      <x:c r="E7" s="20" t="n">
+      <x:c r="E7" s="8" t="n">
         <x:v>11484.2666666667</x:v>
       </x:c>
-      <x:c r="F7" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H7" s="21" t="str"/>
-      <x:c r="I7" s="23" t="str"/>
+      <x:c r="F7" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G7" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H7" s="19" t="str"/>
+      <x:c r="I7" s="19" t="str"/>
       <x:c r="J7" s="16" t="n">
         <x:v>0.8</x:v>
       </x:c>
-      <x:c r="K7" s="17" t="n">
+      <x:c r="K7" s="18" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -7827,30 +7991,30 @@
       <x:c r="A8" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B8" s="17" t="n">
+      <x:c r="B8" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C8" s="8" t="str">
         <x:v>DBO</x:v>
       </x:c>
-      <x:c r="D8" s="16" t="n">
+      <x:c r="D8" s="8" t="n">
         <x:v>6.99538198</x:v>
       </x:c>
-      <x:c r="E8" s="20" t="n">
+      <x:c r="E8" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="F8" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H8" s="21" t="str"/>
-      <x:c r="I8" s="23" t="str"/>
+      <x:c r="F8" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="19" t="str"/>
+      <x:c r="I8" s="19" t="str"/>
       <x:c r="J8" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K8" s="17" t="n">
+      <x:c r="K8" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -7858,30 +8022,30 @@
       <x:c r="A9" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B9" s="17" t="n">
+      <x:c r="B9" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C9" s="8" t="str">
         <x:v>CPO</x:v>
       </x:c>
-      <x:c r="D9" s="16" t="n">
+      <x:c r="D9" s="8" t="n">
         <x:v>4.98090939</x:v>
       </x:c>
-      <x:c r="E9" s="20" t="n">
+      <x:c r="E9" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="F9" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H9" s="21" t="str"/>
-      <x:c r="I9" s="23" t="str"/>
+      <x:c r="F9" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H9" s="19" t="str"/>
+      <x:c r="I9" s="19" t="str"/>
       <x:c r="J9" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K9" s="17" t="n">
+      <x:c r="K9" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -7889,30 +8053,30 @@
       <x:c r="A10" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B10" s="17" t="n">
+      <x:c r="B10" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C10" s="8" t="str">
         <x:v>CVF-AE</x:v>
       </x:c>
-      <x:c r="D10" s="16" t="n">
+      <x:c r="D10" s="8" t="n">
         <x:v>6.79069524666667</x:v>
       </x:c>
-      <x:c r="E10" s="20" t="n">
+      <x:c r="E10" s="8" t="n">
         <x:v>9554.2</x:v>
       </x:c>
-      <x:c r="F10" s="16" t="n">
+      <x:c r="F10" s="8" t="n">
         <x:v>13.1333333333333</x:v>
       </x:c>
-      <x:c r="G10" s="16" t="n">
+      <x:c r="G10" s="8" t="n">
         <x:v>9.76666666666667</x:v>
       </x:c>
-      <x:c r="H10" s="21" t="str"/>
-      <x:c r="I10" s="23" t="str"/>
+      <x:c r="H10" s="19" t="str"/>
+      <x:c r="I10" s="19" t="str"/>
       <x:c r="J10" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K10" s="17" t="n">
+      <x:c r="K10" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -7920,30 +8084,30 @@
       <x:c r="A11" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B11" s="17" t="n">
+      <x:c r="B11" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C11" s="8" t="str">
         <x:v>AE</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="n">
+      <x:c r="D11" s="8" t="n">
         <x:v>5.25174961</x:v>
       </x:c>
-      <x:c r="E11" s="20" t="n">
+      <x:c r="E11" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="F11" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H11" s="21" t="str"/>
-      <x:c r="I11" s="23" t="str"/>
+      <x:c r="F11" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H11" s="19" t="str"/>
+      <x:c r="I11" s="19" t="str"/>
       <x:c r="J11" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" s="17" t="n">
+      <x:c r="K11" s="18" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -7951,30 +8115,30 @@
       <x:c r="A12" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B12" s="17" t="n">
+      <x:c r="B12" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C12" s="8" t="str">
         <x:v>PSO</x:v>
       </x:c>
-      <x:c r="D12" s="16" t="n">
+      <x:c r="D12" s="8" t="n">
         <x:v>5.04003198333333</x:v>
       </x:c>
-      <x:c r="E12" s="20" t="n">
+      <x:c r="E12" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="F12" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H12" s="21" t="str"/>
-      <x:c r="I12" s="23" t="str"/>
+      <x:c r="F12" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H12" s="19" t="str"/>
+      <x:c r="I12" s="19" t="str"/>
       <x:c r="J12" s="16" t="n">
         <x:v>0.433333333333333</x:v>
       </x:c>
-      <x:c r="K12" s="17" t="n">
+      <x:c r="K12" s="18" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -7982,30 +8146,30 @@
       <x:c r="A13" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B13" s="17" t="n">
+      <x:c r="B13" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C13" s="8" t="str">
         <x:v>GWO</x:v>
       </x:c>
-      <x:c r="D13" s="16" t="n">
+      <x:c r="D13" s="8" t="n">
         <x:v>5.70009725</x:v>
       </x:c>
-      <x:c r="E13" s="20" t="n">
+      <x:c r="E13" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="F13" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H13" s="21" t="str"/>
-      <x:c r="I13" s="23" t="str"/>
+      <x:c r="F13" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H13" s="19" t="str"/>
+      <x:c r="I13" s="19" t="str"/>
       <x:c r="J13" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K13" s="17" t="n">
+      <x:c r="K13" s="18" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -8013,30 +8177,30 @@
       <x:c r="A14" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B14" s="17" t="n">
+      <x:c r="B14" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C14" s="8" t="str">
         <x:v>WOA</x:v>
       </x:c>
-      <x:c r="D14" s="16" t="n">
+      <x:c r="D14" s="8" t="n">
         <x:v>5.96214051333333</x:v>
       </x:c>
-      <x:c r="E14" s="20" t="n">
+      <x:c r="E14" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="F14" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H14" s="21" t="str"/>
-      <x:c r="I14" s="23" t="str"/>
+      <x:c r="F14" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G14" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H14" s="19" t="str"/>
+      <x:c r="I14" s="19" t="str"/>
       <x:c r="J14" s="16" t="n">
         <x:v>0.433333333333333</x:v>
       </x:c>
-      <x:c r="K14" s="17" t="n">
+      <x:c r="K14" s="18" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -8044,30 +8208,30 @@
       <x:c r="A15" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B15" s="17" t="n">
+      <x:c r="B15" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C15" s="8" t="str">
         <x:v>HHO</x:v>
       </x:c>
-      <x:c r="D15" s="16" t="n">
+      <x:c r="D15" s="8" t="n">
         <x:v>6.43362172</x:v>
       </x:c>
-      <x:c r="E15" s="20" t="n">
+      <x:c r="E15" s="8" t="n">
         <x:v>11451.7</x:v>
       </x:c>
-      <x:c r="F15" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H15" s="21" t="str"/>
-      <x:c r="I15" s="23" t="str"/>
+      <x:c r="F15" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G15" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" s="19" t="str"/>
+      <x:c r="I15" s="19" t="str"/>
       <x:c r="J15" s="16" t="n">
         <x:v>0.9</x:v>
       </x:c>
-      <x:c r="K15" s="17" t="n">
+      <x:c r="K15" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -8075,30 +8239,30 @@
       <x:c r="A16" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B16" s="17" t="n">
+      <x:c r="B16" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C16" s="8" t="str">
         <x:v>DBO</x:v>
       </x:c>
-      <x:c r="D16" s="16" t="n">
+      <x:c r="D16" s="8" t="n">
         <x:v>4.83305744333333</x:v>
       </x:c>
-      <x:c r="E16" s="20" t="n">
+      <x:c r="E16" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="F16" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H16" s="21" t="str"/>
-      <x:c r="I16" s="23" t="str"/>
+      <x:c r="F16" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="19" t="str"/>
+      <x:c r="I16" s="19" t="str"/>
       <x:c r="J16" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K16" s="17" t="n">
+      <x:c r="K16" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -8106,30 +8270,30 @@
       <x:c r="A17" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B17" s="17" t="n">
+      <x:c r="B17" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C17" s="8" t="str">
         <x:v>CPO</x:v>
       </x:c>
-      <x:c r="D17" s="16" t="n">
+      <x:c r="D17" s="8" t="n">
         <x:v>5.19165132333333</x:v>
       </x:c>
-      <x:c r="E17" s="20" t="n">
+      <x:c r="E17" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="F17" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H17" s="21" t="str"/>
-      <x:c r="I17" s="23" t="str"/>
+      <x:c r="F17" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" s="19" t="str"/>
+      <x:c r="I17" s="19" t="str"/>
       <x:c r="J17" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K17" s="17" t="n">
+      <x:c r="K17" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -8137,30 +8301,30 @@
       <x:c r="A18" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B18" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="B18" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C18" s="8" t="str">
         <x:v>CVF-AE</x:v>
       </x:c>
-      <x:c r="D18" s="16" t="n">
+      <x:c r="D18" s="8" t="n">
         <x:v>7.81631366</x:v>
       </x:c>
-      <x:c r="E18" s="20" t="n">
+      <x:c r="E18" s="8" t="n">
         <x:v>9355.2</x:v>
       </x:c>
-      <x:c r="F18" s="16" t="n">
+      <x:c r="F18" s="8" t="n">
         <x:v>88.6333333333333</x:v>
       </x:c>
-      <x:c r="G18" s="16" t="n">
+      <x:c r="G18" s="8" t="n">
         <x:v>60.1</x:v>
       </x:c>
-      <x:c r="H18" s="21" t="str"/>
-      <x:c r="I18" s="23" t="str"/>
+      <x:c r="H18" s="19" t="str"/>
+      <x:c r="I18" s="19" t="str"/>
       <x:c r="J18" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K18" s="17" t="n">
+      <x:c r="K18" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -8168,30 +8332,30 @@
       <x:c r="A19" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B19" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="B19" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C19" s="8" t="str">
         <x:v>AE</x:v>
       </x:c>
-      <x:c r="D19" s="16" t="n">
+      <x:c r="D19" s="8" t="n">
         <x:v>6.51338697666667</x:v>
       </x:c>
-      <x:c r="E19" s="20" t="n">
+      <x:c r="E19" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="F19" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H19" s="21" t="str"/>
-      <x:c r="I19" s="23" t="str"/>
+      <x:c r="F19" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G19" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H19" s="19" t="str"/>
+      <x:c r="I19" s="19" t="str"/>
       <x:c r="J19" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K19" s="17" t="n">
+      <x:c r="K19" s="18" t="n">
         <x:v>8</x:v>
       </x:c>
     </x:row>
@@ -8199,30 +8363,30 @@
       <x:c r="A20" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B20" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="B20" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C20" s="8" t="str">
         <x:v>PSO</x:v>
       </x:c>
-      <x:c r="D20" s="16" t="n">
+      <x:c r="D20" s="8" t="n">
         <x:v>5.54881991333333</x:v>
       </x:c>
-      <x:c r="E20" s="20" t="n">
+      <x:c r="E20" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="F20" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H20" s="21" t="str"/>
-      <x:c r="I20" s="23" t="str"/>
+      <x:c r="F20" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G20" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H20" s="19" t="str"/>
+      <x:c r="I20" s="19" t="str"/>
       <x:c r="J20" s="16" t="n">
         <x:v>0.0333333333333333</x:v>
       </x:c>
-      <x:c r="K20" s="17" t="n">
+      <x:c r="K20" s="18" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -8230,30 +8394,30 @@
       <x:c r="A21" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B21" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="B21" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C21" s="8" t="str">
         <x:v>GWO</x:v>
       </x:c>
-      <x:c r="D21" s="16" t="n">
+      <x:c r="D21" s="8" t="n">
         <x:v>5.95338771333333</x:v>
       </x:c>
-      <x:c r="E21" s="20" t="n">
+      <x:c r="E21" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="F21" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H21" s="21" t="str"/>
-      <x:c r="I21" s="23" t="str"/>
+      <x:c r="F21" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G21" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H21" s="19" t="str"/>
+      <x:c r="I21" s="19" t="str"/>
       <x:c r="J21" s="16" t="n">
         <x:v>0.633333333333333</x:v>
       </x:c>
-      <x:c r="K21" s="17" t="n">
+      <x:c r="K21" s="18" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -8261,30 +8425,30 @@
       <x:c r="A22" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B22" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="B22" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C22" s="8" t="str">
         <x:v>WOA</x:v>
       </x:c>
-      <x:c r="D22" s="16" t="n">
+      <x:c r="D22" s="8" t="n">
         <x:v>5.52293523666667</x:v>
       </x:c>
-      <x:c r="E22" s="20" t="n">
+      <x:c r="E22" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="F22" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H22" s="21" t="str"/>
-      <x:c r="I22" s="23" t="str"/>
+      <x:c r="F22" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G22" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H22" s="19" t="str"/>
+      <x:c r="I22" s="19" t="str"/>
       <x:c r="J22" s="16" t="n">
         <x:v>0.0666666666666667</x:v>
       </x:c>
-      <x:c r="K22" s="17" t="n">
+      <x:c r="K22" s="18" t="n">
         <x:v>7</x:v>
       </x:c>
     </x:row>
@@ -8292,30 +8456,30 @@
       <x:c r="A23" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B23" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="B23" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C23" s="8" t="str">
         <x:v>HHO</x:v>
       </x:c>
-      <x:c r="D23" s="16" t="n">
+      <x:c r="D23" s="8" t="n">
         <x:v>7.51364364333333</x:v>
       </x:c>
-      <x:c r="E23" s="20" t="n">
+      <x:c r="E23" s="8" t="n">
         <x:v>11474.9666666667</x:v>
       </x:c>
-      <x:c r="F23" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H23" s="21" t="str"/>
-      <x:c r="I23" s="23" t="str"/>
+      <x:c r="F23" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G23" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H23" s="19" t="str"/>
+      <x:c r="I23" s="19" t="str"/>
       <x:c r="J23" s="16" t="n">
         <x:v>0.366666666666667</x:v>
       </x:c>
-      <x:c r="K23" s="17" t="n">
+      <x:c r="K23" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -8323,30 +8487,30 @@
       <x:c r="A24" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B24" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="B24" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C24" s="8" t="str">
         <x:v>DBO</x:v>
       </x:c>
-      <x:c r="D24" s="16" t="n">
+      <x:c r="D24" s="8" t="n">
         <x:v>5.80182613</x:v>
       </x:c>
-      <x:c r="E24" s="20" t="n">
+      <x:c r="E24" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="F24" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H24" s="21" t="str"/>
-      <x:c r="I24" s="23" t="str"/>
+      <x:c r="F24" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G24" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H24" s="19" t="str"/>
+      <x:c r="I24" s="19" t="str"/>
       <x:c r="J24" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K24" s="17" t="n">
+      <x:c r="K24" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -8354,30 +8518,30 @@
       <x:c r="A25" s="8" t="str">
         <x:v>main-comparison</x:v>
       </x:c>
-      <x:c r="B25" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="B25" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C25" s="8" t="str">
         <x:v>CPO</x:v>
       </x:c>
-      <x:c r="D25" s="16" t="n">
+      <x:c r="D25" s="8" t="n">
         <x:v>5.56996168</x:v>
       </x:c>
-      <x:c r="E25" s="20" t="n">
+      <x:c r="E25" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="F25" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H25" s="21" t="str"/>
-      <x:c r="I25" s="23" t="str"/>
+      <x:c r="F25" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G25" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H25" s="19" t="str"/>
+      <x:c r="I25" s="19" t="str"/>
       <x:c r="J25" s="16" t="n">
         <x:v>0.733333333333333</x:v>
       </x:c>
-      <x:c r="K25" s="17" t="n">
+      <x:c r="K25" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -8385,34 +8549,34 @@
       <x:c r="A26" s="8" t="str">
         <x:v>ablation-vs-w/o-CVF</x:v>
       </x:c>
-      <x:c r="B26" s="17" t="n">
+      <x:c r="B26" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C26" s="8" t="str">
         <x:v>Base-AE</x:v>
       </x:c>
-      <x:c r="D26" s="16" t="n">
+      <x:c r="D26" s="8" t="n">
         <x:v>4.37732100666667</x:v>
       </x:c>
-      <x:c r="E26" s="20" t="n">
+      <x:c r="E26" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="F26" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H26" s="21" t="n">
+      <x:c r="F26" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G26" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H26" s="19" t="n">
         <x:v>0.17038190780257</x:v>
       </x:c>
-      <x:c r="I26" s="23" t="n">
+      <x:c r="I26" s="19" t="n">
         <x:v>0.953352923580441</x:v>
       </x:c>
       <x:c r="J26" s="16" t="n">
         <x:v>0.633333333333333</x:v>
       </x:c>
-      <x:c r="K26" s="17" t="n">
+      <x:c r="K26" s="18" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -8420,34 +8584,34 @@
       <x:c r="A27" s="8" t="str">
         <x:v>ablation-vs-w/o-CVF</x:v>
       </x:c>
-      <x:c r="B27" s="17" t="n">
+      <x:c r="B27" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C27" s="8" t="str">
         <x:v>CVF-AE-w/o-Init</x:v>
       </x:c>
-      <x:c r="D27" s="16" t="n">
+      <x:c r="D27" s="8" t="n">
         <x:v>5.78709746</x:v>
       </x:c>
-      <x:c r="E27" s="20" t="n">
+      <x:c r="E27" s="8" t="n">
         <x:v>9587.56666666667</x:v>
       </x:c>
-      <x:c r="F27" s="16" t="n">
+      <x:c r="F27" s="8" t="n">
         <x:v>140.233333333333</x:v>
       </x:c>
-      <x:c r="G27" s="16" t="n">
+      <x:c r="G27" s="8" t="n">
         <x:v>93.0666666666667</x:v>
       </x:c>
-      <x:c r="H27" s="21" t="n">
+      <x:c r="H27" s="19" t="n">
         <x:v>0.225255745322881</x:v>
       </x:c>
-      <x:c r="I27" s="23" t="n">
+      <x:c r="I27" s="19" t="n">
         <x:v>1.01221868346501</x:v>
       </x:c>
       <x:c r="J27" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K27" s="17" t="n">
+      <x:c r="K27" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -8455,34 +8619,34 @@
       <x:c r="A28" s="8" t="str">
         <x:v>ablation-vs-w/o-CVF</x:v>
       </x:c>
-      <x:c r="B28" s="17" t="n">
+      <x:c r="B28" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C28" s="8" t="str">
         <x:v>CVF-AE-w/o-StateAdaptiveCVF</x:v>
       </x:c>
-      <x:c r="D28" s="16" t="n">
+      <x:c r="D28" s="8" t="n">
         <x:v>24.53378375</x:v>
       </x:c>
-      <x:c r="E28" s="20" t="n">
+      <x:c r="E28" s="8" t="n">
         <x:v>9565.96666666667</x:v>
       </x:c>
-      <x:c r="F28" s="16" t="n">
+      <x:c r="F28" s="8" t="n">
         <x:v>20.6333333333333</x:v>
       </x:c>
-      <x:c r="G28" s="16" t="n">
+      <x:c r="G28" s="8" t="n">
         <x:v>19.6666666666667</x:v>
       </x:c>
-      <x:c r="H28" s="21" t="n">
+      <x:c r="H28" s="19" t="n">
         <x:v>0.954947757903605</x:v>
       </x:c>
-      <x:c r="I28" s="23" t="n">
+      <x:c r="I28" s="19" t="n">
         <x:v>1.00993823793352</x:v>
       </x:c>
       <x:c r="J28" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K28" s="17" t="n">
+      <x:c r="K28" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -8490,34 +8654,34 @@
       <x:c r="A29" s="8" t="str">
         <x:v>ablation-vs-w/o-CVF</x:v>
       </x:c>
-      <x:c r="B29" s="17" t="n">
+      <x:c r="B29" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C29" s="8" t="str">
         <x:v>CVF-AE-w/o-SparsePreservation</x:v>
       </x:c>
-      <x:c r="D29" s="16" t="n">
+      <x:c r="D29" s="8" t="n">
         <x:v>20.64546617</x:v>
       </x:c>
-      <x:c r="E29" s="20" t="n">
+      <x:c r="E29" s="8" t="n">
         <x:v>9140.13333333333</x:v>
       </x:c>
-      <x:c r="F29" s="16" t="n">
+      <x:c r="F29" s="8" t="n">
         <x:v>110.133333333333</x:v>
       </x:c>
-      <x:c r="G29" s="16" t="n">
+      <x:c r="G29" s="8" t="n">
         <x:v>90.6666666666667</x:v>
       </x:c>
-      <x:c r="H29" s="21" t="n">
+      <x:c r="H29" s="19" t="n">
         <x:v>0.803599715022198</x:v>
       </x:c>
-      <x:c r="I29" s="23" t="n">
+      <x:c r="I29" s="19" t="n">
         <x:v>0.964980380426176</x:v>
       </x:c>
       <x:c r="J29" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K29" s="17" t="n">
+      <x:c r="K29" s="18" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -8525,34 +8689,34 @@
       <x:c r="A30" s="8" t="str">
         <x:v>ablation-vs-w/o-CVF</x:v>
       </x:c>
-      <x:c r="B30" s="17" t="n">
+      <x:c r="B30" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C30" s="8" t="str">
         <x:v>CVF-AE-w/o-CVF</x:v>
       </x:c>
-      <x:c r="D30" s="16" t="n">
+      <x:c r="D30" s="8" t="n">
         <x:v>25.6912313233333</x:v>
       </x:c>
-      <x:c r="E30" s="20" t="n">
+      <x:c r="E30" s="8" t="n">
         <x:v>9471.83333333333</x:v>
       </x:c>
-      <x:c r="F30" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G30" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H30" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I30" s="23" t="n">
+      <x:c r="F30" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G30" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H30" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I30" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J30" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K30" s="17" t="n">
+      <x:c r="K30" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -8560,34 +8724,34 @@
       <x:c r="A31" s="8" t="str">
         <x:v>ablation-vs-w/o-CVF</x:v>
       </x:c>
-      <x:c r="B31" s="17" t="n">
+      <x:c r="B31" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C31" s="8" t="str">
         <x:v>CVF-AE</x:v>
       </x:c>
-      <x:c r="D31" s="16" t="n">
+      <x:c r="D31" s="8" t="n">
         <x:v>27.4089501233333</x:v>
       </x:c>
-      <x:c r="E31" s="20" t="n">
+      <x:c r="E31" s="8" t="n">
         <x:v>9566.36666666667</x:v>
       </x:c>
-      <x:c r="F31" s="16" t="n">
+      <x:c r="F31" s="8" t="n">
         <x:v>21.1333333333333</x:v>
       </x:c>
-      <x:c r="G31" s="16" t="n">
+      <x:c r="G31" s="8" t="n">
         <x:v>19.1666666666667</x:v>
       </x:c>
-      <x:c r="H31" s="21" t="n">
+      <x:c r="H31" s="19" t="n">
         <x:v>1.0668601196409</x:v>
       </x:c>
-      <x:c r="I31" s="23" t="n">
+      <x:c r="I31" s="19" t="n">
         <x:v>1.00998046840633</x:v>
       </x:c>
       <x:c r="J31" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K31" s="17" t="n">
+      <x:c r="K31" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -8595,34 +8759,34 @@
       <x:c r="A32" s="8" t="str">
         <x:v>ablation-vs-w/o-CVF</x:v>
       </x:c>
-      <x:c r="B32" s="17" t="n">
+      <x:c r="B32" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C32" s="8" t="str">
         <x:v>Base-AE</x:v>
       </x:c>
-      <x:c r="D32" s="16" t="n">
+      <x:c r="D32" s="8" t="n">
         <x:v>18.1763893466667</x:v>
       </x:c>
-      <x:c r="E32" s="20" t="n">
+      <x:c r="E32" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="F32" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G32" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H32" s="21" t="n">
+      <x:c r="F32" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G32" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H32" s="19" t="n">
         <x:v>0.702267883292841</x:v>
       </x:c>
-      <x:c r="I32" s="23" t="n">
+      <x:c r="I32" s="19" t="n">
         <x:v>0.957331768996444</x:v>
       </x:c>
       <x:c r="J32" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K32" s="17" t="n">
+      <x:c r="K32" s="18" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -8630,34 +8794,34 @@
       <x:c r="A33" s="8" t="str">
         <x:v>ablation-vs-w/o-CVF</x:v>
       </x:c>
-      <x:c r="B33" s="17" t="n">
+      <x:c r="B33" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C33" s="8" t="str">
         <x:v>CVF-AE-w/o-Init</x:v>
       </x:c>
-      <x:c r="D33" s="16" t="n">
+      <x:c r="D33" s="8" t="n">
         <x:v>28.7959834</x:v>
       </x:c>
-      <x:c r="E33" s="20" t="n">
+      <x:c r="E33" s="8" t="n">
         <x:v>9592.43333333333</x:v>
       </x:c>
-      <x:c r="F33" s="16" t="n">
+      <x:c r="F33" s="8" t="n">
         <x:v>153.733333333333</x:v>
       </x:c>
-      <x:c r="G33" s="16" t="n">
+      <x:c r="G33" s="8" t="n">
         <x:v>107.433333333333</x:v>
       </x:c>
-      <x:c r="H33" s="21" t="n">
+      <x:c r="H33" s="19" t="n">
         <x:v>1.11256938459906</x:v>
       </x:c>
-      <x:c r="I33" s="23" t="n">
+      <x:c r="I33" s="19" t="n">
         <x:v>1.01695915525808</x:v>
       </x:c>
       <x:c r="J33" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K33" s="17" t="n">
+      <x:c r="K33" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -8665,34 +8829,34 @@
       <x:c r="A34" s="8" t="str">
         <x:v>ablation-vs-w/o-CVF</x:v>
       </x:c>
-      <x:c r="B34" s="17" t="n">
+      <x:c r="B34" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C34" s="8" t="str">
         <x:v>CVF-AE-w/o-StateAdaptiveCVF</x:v>
       </x:c>
-      <x:c r="D34" s="16" t="n">
+      <x:c r="D34" s="8" t="n">
         <x:v>28.8627510466667</x:v>
       </x:c>
-      <x:c r="E34" s="20" t="n">
+      <x:c r="E34" s="8" t="n">
         <x:v>9560.86666666667</x:v>
       </x:c>
-      <x:c r="F34" s="16" t="n">
+      <x:c r="F34" s="8" t="n">
         <x:v>20.4333333333333</x:v>
       </x:c>
-      <x:c r="G34" s="16" t="n">
+      <x:c r="G34" s="8" t="n">
         <x:v>14.5666666666667</x:v>
       </x:c>
-      <x:c r="H34" s="21" t="n">
+      <x:c r="H34" s="19" t="n">
         <x:v>1.11514903741144</x:v>
       </x:c>
-      <x:c r="I34" s="23" t="n">
+      <x:c r="I34" s="19" t="n">
         <x:v>1.0136125580442</x:v>
       </x:c>
       <x:c r="J34" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K34" s="17" t="n">
+      <x:c r="K34" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -8700,34 +8864,34 @@
       <x:c r="A35" s="8" t="str">
         <x:v>ablation-vs-w/o-CVF</x:v>
       </x:c>
-      <x:c r="B35" s="17" t="n">
+      <x:c r="B35" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C35" s="8" t="str">
         <x:v>CVF-AE-w/o-SparsePreservation</x:v>
       </x:c>
-      <x:c r="D35" s="16" t="n">
+      <x:c r="D35" s="8" t="n">
         <x:v>20.91003299</x:v>
       </x:c>
-      <x:c r="E35" s="20" t="n">
+      <x:c r="E35" s="8" t="n">
         <x:v>9107.83333333333</x:v>
       </x:c>
-      <x:c r="F35" s="16" t="n">
+      <x:c r="F35" s="8" t="n">
         <x:v>77.8333333333333</x:v>
       </x:c>
-      <x:c r="G35" s="16" t="n">
+      <x:c r="G35" s="8" t="n">
         <x:v>51.5</x:v>
       </x:c>
-      <x:c r="H35" s="21" t="n">
+      <x:c r="H35" s="19" t="n">
         <x:v>0.807885676709698</x:v>
       </x:c>
-      <x:c r="I35" s="23" t="n">
+      <x:c r="I35" s="19" t="n">
         <x:v>0.965583410490009</x:v>
       </x:c>
       <x:c r="J35" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K35" s="17" t="n">
+      <x:c r="K35" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -8735,34 +8899,34 @@
       <x:c r="A36" s="8" t="str">
         <x:v>ablation-vs-w/o-CVF</x:v>
       </x:c>
-      <x:c r="B36" s="17" t="n">
+      <x:c r="B36" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C36" s="8" t="str">
         <x:v>CVF-AE-w/o-CVF</x:v>
       </x:c>
-      <x:c r="D36" s="16" t="n">
+      <x:c r="D36" s="8" t="n">
         <x:v>25.8824157833333</x:v>
       </x:c>
-      <x:c r="E36" s="20" t="n">
+      <x:c r="E36" s="8" t="n">
         <x:v>9432.46666666667</x:v>
       </x:c>
-      <x:c r="F36" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G36" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H36" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I36" s="23" t="n">
+      <x:c r="F36" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G36" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H36" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I36" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J36" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K36" s="17" t="n">
+      <x:c r="K36" s="18" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -8770,34 +8934,34 @@
       <x:c r="A37" s="8" t="str">
         <x:v>ablation-vs-w/o-CVF</x:v>
       </x:c>
-      <x:c r="B37" s="17" t="n">
+      <x:c r="B37" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C37" s="8" t="str">
         <x:v>CVF-AE</x:v>
       </x:c>
-      <x:c r="D37" s="16" t="n">
+      <x:c r="D37" s="8" t="n">
         <x:v>28.3060269366667</x:v>
       </x:c>
-      <x:c r="E37" s="20" t="n">
+      <x:c r="E37" s="8" t="n">
         <x:v>9551.6</x:v>
       </x:c>
-      <x:c r="F37" s="16" t="n">
+      <x:c r="F37" s="8" t="n">
         <x:v>10.6</x:v>
       </x:c>
-      <x:c r="G37" s="16" t="n">
+      <x:c r="G37" s="8" t="n">
         <x:v>7.9</x:v>
       </x:c>
-      <x:c r="H37" s="21" t="n">
+      <x:c r="H37" s="19" t="n">
         <x:v>1.09363929447784</x:v>
       </x:c>
-      <x:c r="I37" s="23" t="n">
+      <x:c r="I37" s="19" t="n">
         <x:v>1.01263013563083</x:v>
       </x:c>
       <x:c r="J37" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K37" s="17" t="n">
+      <x:c r="K37" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
@@ -8805,34 +8969,34 @@
       <x:c r="A38" s="8" t="str">
         <x:v>ablation-vs-w/o-CVF</x:v>
       </x:c>
-      <x:c r="B38" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="B38" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C38" s="8" t="str">
         <x:v>Base-AE</x:v>
       </x:c>
-      <x:c r="D38" s="16" t="n">
+      <x:c r="D38" s="8" t="n">
         <x:v>11.5175831466667</x:v>
       </x:c>
-      <x:c r="E38" s="20" t="n">
+      <x:c r="E38" s="8" t="n">
         <x:v>9030</x:v>
       </x:c>
-      <x:c r="F38" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G38" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H38" s="21" t="n">
+      <x:c r="F38" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G38" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H38" s="19" t="n">
         <x:v>0.476460642936158</x:v>
       </x:c>
-      <x:c r="I38" s="23" t="n">
+      <x:c r="I38" s="19" t="n">
         <x:v>0.975319976238052</x:v>
       </x:c>
       <x:c r="J38" s="16" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K38" s="17" t="n">
+      <x:c r="K38" s="18" t="n">
         <x:v>6</x:v>
       </x:c>
     </x:row>
@@ -8840,34 +9004,34 @@
       <x:c r="A39" s="8" t="str">
         <x:v>ablation-vs-w/o-CVF</x:v>
       </x:c>
-      <x:c r="B39" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="B39" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C39" s="8" t="str">
         <x:v>CVF-AE-w/o-Init</x:v>
       </x:c>
-      <x:c r="D39" s="16" t="n">
+      <x:c r="D39" s="8" t="n">
         <x:v>32.5411983966667</x:v>
       </x:c>
-      <x:c r="E39" s="20" t="n">
+      <x:c r="E39" s="8" t="n">
         <x:v>9802.7</x:v>
       </x:c>
-      <x:c r="F39" s="16" t="n">
+      <x:c r="F39" s="8" t="n">
         <x:v>417.9</x:v>
       </x:c>
-      <x:c r="G39" s="16" t="n">
+      <x:c r="G39" s="8" t="n">
         <x:v>336.466666666667</x:v>
       </x:c>
-      <x:c r="H39" s="21" t="n">
+      <x:c r="H39" s="19" t="n">
         <x:v>1.34616786460761</x:v>
       </x:c>
-      <x:c r="I39" s="23" t="n">
+      <x:c r="I39" s="19" t="n">
         <x:v>1.05877841983043</x:v>
       </x:c>
       <x:c r="J39" s="16" t="n">
         <x:v>0.7</x:v>
       </x:c>
-      <x:c r="K39" s="17" t="n">
+      <x:c r="K39" s="18" t="n">
         <x:v>5</x:v>
       </x:c>
     </x:row>
@@ -8875,34 +9039,34 @@
       <x:c r="A40" s="8" t="str">
         <x:v>ablation-vs-w/o-CVF</x:v>
       </x:c>
-      <x:c r="B40" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="B40" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C40" s="8" t="str">
         <x:v>CVF-AE-w/o-StateAdaptiveCVF</x:v>
       </x:c>
-      <x:c r="D40" s="16" t="n">
+      <x:c r="D40" s="8" t="n">
         <x:v>26.13774229</x:v>
       </x:c>
-      <x:c r="E40" s="20" t="n">
+      <x:c r="E40" s="8" t="n">
         <x:v>9321.83333333333</x:v>
       </x:c>
-      <x:c r="F40" s="16" t="n">
+      <x:c r="F40" s="8" t="n">
         <x:v>72.4666666666667</x:v>
       </x:c>
-      <x:c r="G40" s="16" t="n">
+      <x:c r="G40" s="8" t="n">
         <x:v>46.2666666666667</x:v>
       </x:c>
-      <x:c r="H40" s="21" t="n">
+      <x:c r="H40" s="19" t="n">
         <x:v>1.08126899001352</x:v>
       </x:c>
-      <x:c r="I40" s="23" t="n">
+      <x:c r="I40" s="19" t="n">
         <x:v>1.006840560926</x:v>
       </x:c>
       <x:c r="J40" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K40" s="17" t="n">
+      <x:c r="K40" s="18" t="n">
         <x:v>3</x:v>
       </x:c>
     </x:row>
@@ -8910,34 +9074,34 @@
       <x:c r="A41" s="8" t="str">
         <x:v>ablation-vs-w/o-CVF</x:v>
       </x:c>
-      <x:c r="B41" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="B41" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C41" s="8" t="str">
         <x:v>CVF-AE-w/o-SparsePreservation</x:v>
       </x:c>
-      <x:c r="D41" s="16" t="n">
+      <x:c r="D41" s="8" t="n">
         <x:v>20.7890775266667</x:v>
       </x:c>
-      <x:c r="E41" s="20" t="n">
+      <x:c r="E41" s="8" t="n">
         <x:v>9118.7</x:v>
       </x:c>
-      <x:c r="F41" s="16" t="n">
+      <x:c r="F41" s="8" t="n">
         <x:v>88.7</x:v>
       </x:c>
-      <x:c r="G41" s="16" t="n">
+      <x:c r="G41" s="8" t="n">
         <x:v>56.6</x:v>
       </x:c>
-      <x:c r="H41" s="21" t="n">
+      <x:c r="H41" s="19" t="n">
         <x:v>0.860004839406946</x:v>
       </x:c>
-      <x:c r="I41" s="23" t="n">
+      <x:c r="I41" s="19" t="n">
         <x:v>0.98490036182967</x:v>
       </x:c>
       <x:c r="J41" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K41" s="17" t="n">
+      <x:c r="K41" s="18" t="n">
         <x:v>4</x:v>
       </x:c>
     </x:row>
@@ -8945,34 +9109,34 @@
       <x:c r="A42" s="8" t="str">
         <x:v>ablation-vs-w/o-CVF</x:v>
       </x:c>
-      <x:c r="B42" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="B42" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C42" s="8" t="str">
         <x:v>CVF-AE-w/o-CVF</x:v>
       </x:c>
-      <x:c r="D42" s="16" t="n">
+      <x:c r="D42" s="8" t="n">
         <x:v>24.1732099333333</x:v>
       </x:c>
-      <x:c r="E42" s="20" t="n">
+      <x:c r="E42" s="8" t="n">
         <x:v>9258.5</x:v>
       </x:c>
-      <x:c r="F42" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G42" s="16" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H42" s="21" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I42" s="23" t="n">
+      <x:c r="F42" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G42" s="8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H42" s="19" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I42" s="19" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J42" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K42" s="17" t="n">
+      <x:c r="K42" s="18" t="n">
         <x:v>2</x:v>
       </x:c>
     </x:row>
@@ -8980,41 +9144,41 @@
       <x:c r="A43" s="8" t="str">
         <x:v>ablation-vs-w/o-CVF</x:v>
       </x:c>
-      <x:c r="B43" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="B43" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C43" s="8" t="str">
         <x:v>CVF-AE</x:v>
       </x:c>
-      <x:c r="D43" s="16" t="n">
+      <x:c r="D43" s="8" t="n">
         <x:v>18.5574635633333</x:v>
       </x:c>
-      <x:c r="E43" s="20" t="n">
+      <x:c r="E43" s="8" t="n">
         <x:v>9367.06666666667</x:v>
       </x:c>
-      <x:c r="F43" s="16" t="n">
+      <x:c r="F43" s="8" t="n">
         <x:v>86.8</x:v>
       </x:c>
-      <x:c r="G43" s="16" t="n">
+      <x:c r="G43" s="8" t="n">
         <x:v>59.5333333333333</x:v>
       </x:c>
-      <x:c r="H43" s="21" t="n">
+      <x:c r="H43" s="19" t="n">
         <x:v>0.767687188193561</x:v>
       </x:c>
-      <x:c r="I43" s="23" t="n">
+      <x:c r="I43" s="19" t="n">
         <x:v>1.01172616154525</x:v>
       </x:c>
       <x:c r="J43" s="16" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K43" s="17" t="n">
+      <x:c r="K43" s="18" t="n">
         <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d96c7e129434459"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb62fb46ef09a41d4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9023,60 +9187,60 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="13" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="11" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="13.75" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="13" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="13.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="11" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="11.380000114440918" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="11.880000114440918" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="14" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="14" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="14" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="14" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15" hidden="0" customHeight="1">
-      <x:c r="A1" s="13" t="str">
+      <x:c r="A1" s="142" t="str">
         <x:v>Scene</x:v>
       </x:c>
-      <x:c r="B1" s="13" t="str">
+      <x:c r="B1" s="142" t="str">
         <x:v>Algorithm</x:v>
       </x:c>
-      <x:c r="C1" s="13" t="str">
+      <x:c r="C1" s="142" t="str">
         <x:v>FeasibleRate</x:v>
       </x:c>
-      <x:c r="D1" s="13" t="str">
+      <x:c r="D1" s="142" t="str">
         <x:v>MeanFitness</x:v>
       </x:c>
-      <x:c r="E1" s="13" t="str">
+      <x:c r="E1" s="142" t="str">
         <x:v>High-Altitude Frac</x:v>
       </x:c>
-      <x:c r="F1" s="13" t="str">
+      <x:c r="F1" s="142" t="str">
         <x:v>DetourRatio</x:v>
       </x:c>
-      <x:c r="G1" s="13" t="str">
+      <x:c r="G1" s="142" t="str">
         <x:v>Boundary-Hug Frac</x:v>
       </x:c>
-      <x:c r="H1" s="13" t="str">
-        <x:v>High-Altitude Flag</x:v>
-      </x:c>
-      <x:c r="I1" s="13" t="str">
-        <x:v>Boundary-Hug Flag</x:v>
-      </x:c>
-      <x:c r="J1" s="13" t="str">
-        <x:v>Detour Flag</x:v>
-      </x:c>
-      <x:c r="K1" s="13" t="str">
+      <x:c r="H1" s="142" t="str">
+        <x:v>HighAltitudeFlagRate</x:v>
+      </x:c>
+      <x:c r="I1" s="142" t="str">
+        <x:v>BoundaryHugFlagRate</x:v>
+      </x:c>
+      <x:c r="J1" s="142" t="str">
+        <x:v>ExcessiveDetourFlagRate</x:v>
+      </x:c>
+      <x:c r="K1" s="142" t="str">
         <x:v>Visual Flag Rate</x:v>
       </x:c>
-      <x:c r="L1" s="13" t="str">
+      <x:c r="L1" s="142" t="str">
         <x:v>Source</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="15" hidden="0" customHeight="1">
-      <x:c r="A2" s="17" t="n">
+      <x:c r="A2" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="8" t="str">
@@ -9114,7 +9278,7 @@
       </x:c>
     </x:row>
     <x:row r="3" ht="15" hidden="0" customHeight="1">
-      <x:c r="A3" s="17" t="n">
+      <x:c r="A3" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="8" t="str">
@@ -9152,7 +9316,7 @@
       </x:c>
     </x:row>
     <x:row r="4" ht="15" hidden="0" customHeight="1">
-      <x:c r="A4" s="17" t="n">
+      <x:c r="A4" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="8" t="str">
@@ -9190,7 +9354,7 @@
       </x:c>
     </x:row>
     <x:row r="5" ht="15" hidden="0" customHeight="1">
-      <x:c r="A5" s="17" t="n">
+      <x:c r="A5" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" s="8" t="str">
@@ -9228,7 +9392,7 @@
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
-      <x:c r="A6" s="17" t="n">
+      <x:c r="A6" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="8" t="str">
@@ -9266,7 +9430,7 @@
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
-      <x:c r="A7" s="17" t="n">
+      <x:c r="A7" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B7" s="8" t="str">
@@ -9304,7 +9468,7 @@
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
-      <x:c r="A8" s="17" t="n">
+      <x:c r="A8" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B8" s="8" t="str">
@@ -9342,7 +9506,7 @@
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
-      <x:c r="A9" s="17" t="n">
+      <x:c r="A9" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" s="8" t="str">
@@ -9380,7 +9544,7 @@
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
-      <x:c r="A10" s="17" t="n">
+      <x:c r="A10" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B10" s="8" t="str">
@@ -9418,7 +9582,7 @@
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
-      <x:c r="A11" s="17" t="n">
+      <x:c r="A11" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B11" s="8" t="str">
@@ -9456,7 +9620,7 @@
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
-      <x:c r="A12" s="17" t="n">
+      <x:c r="A12" s="8" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B12" s="8" t="str">
@@ -9494,7 +9658,7 @@
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
-      <x:c r="A13" s="17" t="n">
+      <x:c r="A13" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B13" s="8" t="str">
@@ -9532,7 +9696,7 @@
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
-      <x:c r="A14" s="17" t="n">
+      <x:c r="A14" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B14" s="8" t="str">
@@ -9570,7 +9734,7 @@
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
-      <x:c r="A15" s="17" t="n">
+      <x:c r="A15" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B15" s="8" t="str">
@@ -9608,7 +9772,7 @@
       </x:c>
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
-      <x:c r="A16" s="17" t="n">
+      <x:c r="A16" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B16" s="8" t="str">
@@ -9646,7 +9810,7 @@
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
-      <x:c r="A17" s="17" t="n">
+      <x:c r="A17" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B17" s="8" t="str">
@@ -9684,7 +9848,7 @@
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
-      <x:c r="A18" s="17" t="n">
+      <x:c r="A18" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B18" s="8" t="str">
@@ -9722,7 +9886,7 @@
       </x:c>
     </x:row>
     <x:row r="19" ht="15" hidden="0" customHeight="1">
-      <x:c r="A19" s="17" t="n">
+      <x:c r="A19" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B19" s="8" t="str">
@@ -9760,7 +9924,7 @@
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
-      <x:c r="A20" s="17" t="n">
+      <x:c r="A20" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B20" s="8" t="str">
@@ -9798,7 +9962,7 @@
       </x:c>
     </x:row>
     <x:row r="21" ht="15" hidden="0" customHeight="1">
-      <x:c r="A21" s="17" t="n">
+      <x:c r="A21" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B21" s="8" t="str">
@@ -9836,7 +10000,7 @@
       </x:c>
     </x:row>
     <x:row r="22" ht="15" hidden="0" customHeight="1">
-      <x:c r="A22" s="17" t="n">
+      <x:c r="A22" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B22" s="8" t="str">
@@ -9874,7 +10038,7 @@
       </x:c>
     </x:row>
     <x:row r="23" ht="15" hidden="0" customHeight="1">
-      <x:c r="A23" s="17" t="n">
+      <x:c r="A23" s="8" t="n">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B23" s="8" t="str">
@@ -9912,8 +10076,8 @@
       </x:c>
     </x:row>
     <x:row r="24" ht="15" hidden="0" customHeight="1">
-      <x:c r="A24" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A24" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B24" s="8" t="str">
         <x:v>CPO</x:v>
@@ -9950,8 +10114,8 @@
       </x:c>
     </x:row>
     <x:row r="25" ht="15" hidden="0" customHeight="1">
-      <x:c r="A25" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A25" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B25" s="8" t="str">
         <x:v>DBO</x:v>
@@ -9988,8 +10152,8 @@
       </x:c>
     </x:row>
     <x:row r="26" ht="15" hidden="0" customHeight="1">
-      <x:c r="A26" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A26" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B26" s="8" t="str">
         <x:v>GDSAO</x:v>
@@ -10026,8 +10190,8 @@
       </x:c>
     </x:row>
     <x:row r="27" ht="15" hidden="0" customHeight="1">
-      <x:c r="A27" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A27" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B27" s="8" t="str">
         <x:v>GWO</x:v>
@@ -10064,8 +10228,8 @@
       </x:c>
     </x:row>
     <x:row r="28" ht="15" hidden="0" customHeight="1">
-      <x:c r="A28" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A28" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B28" s="8" t="str">
         <x:v>ERIME</x:v>
@@ -10102,8 +10266,8 @@
       </x:c>
     </x:row>
     <x:row r="29" ht="15" hidden="0" customHeight="1">
-      <x:c r="A29" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A29" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B29" s="8" t="str">
         <x:v>HHO</x:v>
@@ -10140,8 +10304,8 @@
       </x:c>
     </x:row>
     <x:row r="30" ht="15" hidden="0" customHeight="1">
-      <x:c r="A30" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A30" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B30" s="8" t="str">
         <x:v>WOA</x:v>
@@ -10178,8 +10342,8 @@
       </x:c>
     </x:row>
     <x:row r="31" ht="15" hidden="0" customHeight="1">
-      <x:c r="A31" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A31" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B31" s="8" t="str">
         <x:v>MSCSO</x:v>
@@ -10216,8 +10380,8 @@
       </x:c>
     </x:row>
     <x:row r="32" ht="15" hidden="0" customHeight="1">
-      <x:c r="A32" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A32" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B32" s="8" t="str">
         <x:v>CVF-AE</x:v>
@@ -10254,8 +10418,8 @@
       </x:c>
     </x:row>
     <x:row r="33" ht="15" hidden="0" customHeight="1">
-      <x:c r="A33" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A33" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B33" s="8" t="str">
         <x:v>PSO</x:v>
@@ -10292,8 +10456,8 @@
       </x:c>
     </x:row>
     <x:row r="34" ht="15" hidden="0" customHeight="1">
-      <x:c r="A34" s="17" t="n">
-        <x:v>4</x:v>
+      <x:c r="A34" s="8" t="n">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B34" s="8" t="str">
         <x:v>AE</x:v>
@@ -10332,7 +10496,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c1ce9f32408407b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ce0853de0de4f0d"/>
   </x:tableParts>
 </x:worksheet>
 </file>